--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I173"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2982,12 +2982,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3000,31 +3000,31 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>7455900</v>
+        <v>6431400</v>
       </c>
       <c r="G70" t="n">
-        <v>8801415000</v>
+        <v>7591952000</v>
       </c>
       <c r="H70" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I70" t="n">
-        <v>14.79</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3033,403 +3033,405 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G71" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H71" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G72" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H72" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I72" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G73" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H73" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G74" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H74" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I74" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H75" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I75" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G76" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H76" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G77" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H77" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G78" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H78" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I78" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G79" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H79" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I79" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G81" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H81" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I81" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3438,368 +3440,366 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H82" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G83" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H83" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I83" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G84" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H84" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I84" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4619</v>
+        <v>9302</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G85" t="n">
-        <v>119000</v>
+        <v>5671170000</v>
       </c>
       <c r="H85" t="n">
-        <v>1190</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G86" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H86" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G87" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H87" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I87" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G88" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H88" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I88" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G89" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H89" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G90" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H90" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I90" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H91" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I91" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3808,257 +3808,257 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G92" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H92" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G93" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H93" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I93" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G94" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H94" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I94" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G95" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H95" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I95" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G96" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H96" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I96" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G97" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H97" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G98" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H98" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I98" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4067,442 +4067,442 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G99" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H99" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I99" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G100" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H100" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G101" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H101" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G102" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H102" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I102" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G103" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H103" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I103" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G104" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H104" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I104" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G105" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H105" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I105" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G106" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H106" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G107" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H107" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I107" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G108" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H108" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I108" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G109" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H109" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I109" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G110" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H110" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I110" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4511,109 +4511,109 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G111" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H111" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I111" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G112" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H112" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I112" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G113" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H113" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I113" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4622,109 +4622,109 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G114" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H114" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I114" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G115" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H115" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G116" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H116" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I116" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4733,21 +4733,21 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F117" t="n">
         <v>100</v>
       </c>
       <c r="G117" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H117" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -4756,456 +4756,456 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G118" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H118" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I118" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G119" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H119" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I119" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G120" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H120" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I120" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2327</v>
+        <v>3569</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>9154320</v>
+        <v>4271704</v>
       </c>
       <c r="G121" t="n">
-        <v>23450671000</v>
+        <v>5808044000</v>
       </c>
       <c r="H121" t="n">
-        <v>2561.705402476645</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G122" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H122" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G123" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H123" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G124" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H124" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I124" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G125" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H125" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I125" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G126" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H126" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I126" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G127" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H127" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G128" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H128" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I128" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G129" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H129" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5214,44 +5214,44 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G130" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H130" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I130" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5259,249 +5259,249 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G131" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H131" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G132" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H132" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I132" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G133" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H133" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I133" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G134" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H134" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I134" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G135" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H135" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I135" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G136" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H136" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I136" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G137" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H137" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I137" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5510,775 +5510,775 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G138" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H138" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I138" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G139" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H139" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I139" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G140" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H140" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I140" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G141" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H141" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I141" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G142" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H142" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G143" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H143" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I143" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G144" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H144" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I144" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G145" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H145" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I145" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G146" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H146" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G147" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H147" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I147" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G148" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H148" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I148" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G149" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H149" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G150" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H150" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I150" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G151" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H151" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I151" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G152" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H152" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G153" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H153" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I153" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G154" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H154" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I154" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G155" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H155" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I155" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G156" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H156" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G157" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H157" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I157" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G158" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H158" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I158" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6287,35 +6287,35 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G159" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H159" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I159" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6324,72 +6324,72 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G160" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H160" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I160" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G161" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H161" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I161" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6398,426 +6398,500 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G162" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H162" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I162" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G163" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H163" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I163" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G164" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H164" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I164" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G165" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H165" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I165" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G166" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H166" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I166" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G167" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H167" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G168" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H168" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I168" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G169" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H169" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I169" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G170" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H170" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I170" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G171" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H171" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I171" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2812</v>
+        <v>5186</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
+        <v>1536900</v>
+      </c>
+      <c r="G172" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H172" t="n">
+        <v>3096.322467304314</v>
+      </c>
       <c r="I172" t="n">
-        <v>9.779999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G173" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H173" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I173" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>S100RVIC.zip</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2812</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t>S100RU33.zip</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
-      <c r="D173" t="n">
+      <c r="D175" t="n">
         <v>5451</v>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="F173" t="n">
+      <c r="F175" t="n">
         <v>1752800</v>
       </c>
-      <c r="G173" t="n">
+      <c r="G175" t="n">
         <v>5669831000</v>
       </c>
-      <c r="H173" t="n">
+      <c r="H175" t="n">
         <v>3234.727863989046</v>
       </c>
-      <c r="I173" t="n">
+      <c r="I175" t="n">
         <v>5.029999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2945,86 +2945,86 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1297500</v>
+        <v>5295000</v>
       </c>
       <c r="G69" t="n">
-        <v>4476090000</v>
+        <v>6250386000</v>
       </c>
       <c r="H69" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I69" t="n">
-        <v>5.23</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G70" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H70" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I70" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3037,31 +3037,31 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6942800</v>
+        <v>5865200</v>
       </c>
       <c r="G71" t="n">
-        <v>8195680000</v>
+        <v>6923530000</v>
       </c>
       <c r="H71" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I71" t="n">
-        <v>13.78</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3074,31 +3074,31 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>7455900</v>
+        <v>6431400</v>
       </c>
       <c r="G72" t="n">
-        <v>8801415000</v>
+        <v>7591952000</v>
       </c>
       <c r="H72" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I72" t="n">
-        <v>14.79</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3107,403 +3107,405 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G73" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H73" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G74" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H74" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I74" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G75" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H75" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G76" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H76" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I76" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G77" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H77" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I77" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G78" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H78" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G79" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H79" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G80" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H80" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I80" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G81" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H81" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I81" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G83" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H83" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I83" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3512,368 +3514,366 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H84" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G85" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H85" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I85" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G86" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H86" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I86" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4619</v>
+        <v>9302</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G87" t="n">
-        <v>119000</v>
+        <v>5671170000</v>
       </c>
       <c r="H87" t="n">
-        <v>1190</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G88" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H88" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H89" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I89" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G90" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H90" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I90" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G91" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H91" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G92" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H92" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I92" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G93" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H93" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I93" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3882,257 +3882,257 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G94" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H94" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G95" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H95" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G96" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H96" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I96" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G97" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H97" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I97" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G98" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H98" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I98" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G99" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H99" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G100" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H100" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4141,442 +4141,442 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G101" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H101" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I101" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G102" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H102" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G103" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H103" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G104" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H104" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I104" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G105" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H105" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I105" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G106" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H106" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I106" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G107" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H107" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I107" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G108" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H108" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G109" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H109" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I109" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H110" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I110" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G111" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H111" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I111" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G112" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H112" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I112" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4585,109 +4585,109 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G113" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H113" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I113" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G114" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H114" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I114" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G115" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H115" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I115" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4696,109 +4696,109 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G116" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H116" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I116" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G117" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H117" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G118" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H118" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I118" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4807,21 +4807,21 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F119" t="n">
         <v>100</v>
       </c>
       <c r="G119" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H119" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -4830,456 +4830,456 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G120" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H120" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I120" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G121" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H121" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I121" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G122" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H122" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I122" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2327</v>
+        <v>3569</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>9154320</v>
+        <v>4271704</v>
       </c>
       <c r="G123" t="n">
-        <v>23450671000</v>
+        <v>5808044000</v>
       </c>
       <c r="H123" t="n">
-        <v>2561.705402476645</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G124" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H124" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I124" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G125" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H125" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G126" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H126" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I126" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G127" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H127" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I127" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G128" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H128" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I128" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G129" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H129" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G130" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H130" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I130" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G131" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H131" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5288,44 +5288,44 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G132" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H132" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I132" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5333,249 +5333,249 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G133" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H133" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G134" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H134" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I134" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G135" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H135" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I135" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G136" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H136" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I136" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G137" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H137" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I137" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G138" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H138" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I138" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G139" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H139" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I139" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5584,775 +5584,775 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G140" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H140" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I140" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G141" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H141" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I141" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G142" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H142" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I142" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G143" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H143" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I143" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G144" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H144" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G145" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H145" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I145" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G146" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H146" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I146" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G147" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H147" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I147" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G148" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H148" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G149" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H149" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I149" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G150" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H150" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I150" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G151" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H151" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G152" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H152" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I152" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G153" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H153" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I153" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G154" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H154" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G155" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H155" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I155" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G156" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H156" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I156" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G157" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H157" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I157" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G158" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H158" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G159" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H159" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I159" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G160" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H160" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I160" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6361,35 +6361,35 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G161" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H161" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I161" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6398,72 +6398,72 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G162" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H162" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I162" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G163" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H163" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6472,426 +6472,500 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G164" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H164" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I164" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G165" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H165" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I165" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G166" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H166" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I166" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G167" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H167" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I167" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G168" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H168" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I168" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G169" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H169" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G170" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H170" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I170" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G171" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H171" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I171" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G172" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H172" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I172" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G173" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H173" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I173" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2812</v>
+        <v>5186</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
+        <v>1536900</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H174" t="n">
+        <v>3096.322467304314</v>
+      </c>
       <c r="I174" t="n">
-        <v>9.779999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G175" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I175" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>S100RVIC.zip</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>2812</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
           <t>S100RU33.zip</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
-      <c r="D175" t="n">
+      <c r="D177" t="n">
         <v>5451</v>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="F175" t="n">
+      <c r="F177" t="n">
         <v>1752800</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G177" t="n">
         <v>5669831000</v>
       </c>
-      <c r="H175" t="n">
+      <c r="H177" t="n">
         <v>3234.727863989046</v>
       </c>
-      <c r="I175" t="n">
+      <c r="I177" t="n">
         <v>5.029999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2871,49 +2871,49 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G67" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H67" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I67" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2945,86 +2945,86 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G69" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H69" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I69" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1297500</v>
+        <v>4783700</v>
       </c>
       <c r="G70" t="n">
-        <v>4476090000</v>
+        <v>5646776000</v>
       </c>
       <c r="H70" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I70" t="n">
-        <v>5.23</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3037,68 +3037,68 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>5865200</v>
+        <v>5295000</v>
       </c>
       <c r="G71" t="n">
-        <v>6923530000</v>
+        <v>6250386000</v>
       </c>
       <c r="H71" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I71" t="n">
-        <v>11.64</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G72" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H72" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I72" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3111,31 +3111,31 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6942800</v>
+        <v>5865200</v>
       </c>
       <c r="G73" t="n">
-        <v>8195680000</v>
+        <v>6923530000</v>
       </c>
       <c r="H73" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I73" t="n">
-        <v>13.78</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3148,31 +3148,31 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>7455900</v>
+        <v>6431400</v>
       </c>
       <c r="G74" t="n">
-        <v>8801415000</v>
+        <v>7591952000</v>
       </c>
       <c r="H74" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I74" t="n">
-        <v>14.79</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3181,403 +3181,405 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G75" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H75" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G76" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H76" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I76" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G77" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H77" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G78" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H78" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I78" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H79" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I79" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G80" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H80" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G81" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H81" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G82" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H82" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I82" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G83" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H83" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I83" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G85" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H85" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I85" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3586,368 +3588,366 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H86" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G87" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H87" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I87" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G88" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H88" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I88" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4619</v>
+        <v>9302</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G89" t="n">
-        <v>119000</v>
+        <v>5671170000</v>
       </c>
       <c r="H89" t="n">
-        <v>1190</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G90" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H90" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H91" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I91" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G92" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H92" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I92" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G93" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H93" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G94" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H94" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I94" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H95" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I95" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3956,257 +3956,257 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G96" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H96" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G97" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H97" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I97" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G98" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H98" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I98" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G99" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H99" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I99" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G100" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H100" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I100" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G101" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H101" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G102" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H102" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4215,442 +4215,442 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G103" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H103" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I103" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G104" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H104" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G105" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H105" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G106" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H106" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I106" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H107" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I107" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G108" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H108" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I108" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G109" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H109" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I109" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G110" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H110" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G111" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H111" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I111" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H112" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I112" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G113" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H113" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I113" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G114" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H114" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I114" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4659,109 +4659,109 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G115" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H115" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I115" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G116" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H116" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I116" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G117" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H117" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I117" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4770,109 +4770,109 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G118" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H118" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I118" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G119" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H119" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G120" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H120" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I120" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>100</v>
       </c>
       <c r="G121" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H121" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -4904,456 +4904,456 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G122" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H122" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I122" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G123" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H123" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I123" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G124" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H124" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I124" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2327</v>
+        <v>3569</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>9154320</v>
+        <v>4271704</v>
       </c>
       <c r="G125" t="n">
-        <v>23450671000</v>
+        <v>5808044000</v>
       </c>
       <c r="H125" t="n">
-        <v>2561.705402476645</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I125" t="n">
-        <v>5</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G126" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H126" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I126" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G127" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H127" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G128" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H128" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I128" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G129" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H129" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I129" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G130" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H130" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I130" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G131" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H131" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G132" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H132" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I132" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G133" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H133" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5362,44 +5362,44 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G134" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H134" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I134" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5407,249 +5407,249 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G135" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H135" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G136" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H136" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I136" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G137" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H137" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I137" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G138" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H138" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I138" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G139" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H139" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I139" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G140" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H140" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I140" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G141" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H141" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I141" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5658,775 +5658,775 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G142" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H142" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I142" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G143" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H143" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I143" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G144" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H144" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I144" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G145" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H145" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I145" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G146" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H146" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G147" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H147" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I147" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G148" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H148" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I148" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G149" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H149" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I149" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G150" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H150" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G151" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H151" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I151" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G152" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H152" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I152" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G153" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H153" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G154" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H154" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I154" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G155" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H155" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I155" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G156" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H156" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G157" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H157" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I157" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G158" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H158" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I158" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G159" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H159" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I159" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G160" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H160" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G161" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H161" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I161" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G162" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H162" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I162" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6435,35 +6435,35 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G163" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H163" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I163" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6472,72 +6472,72 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G164" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H164" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I164" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G165" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H165" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I165" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6546,426 +6546,500 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G166" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H166" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I166" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G167" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H167" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I167" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G168" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H168" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I168" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G169" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H169" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I169" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G170" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H170" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I170" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G171" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H171" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G172" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H172" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I172" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G173" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H173" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I173" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G174" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H174" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I174" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G175" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H175" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I175" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2812</v>
+        <v>5186</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
+        <v>1536900</v>
+      </c>
+      <c r="G176" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H176" t="n">
+        <v>3096.322467304314</v>
+      </c>
       <c r="I176" t="n">
-        <v>9.779999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G177" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I177" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>S100RVIC.zip</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2812</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
           <t>S100RU33.zip</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
-      <c r="D177" t="n">
+      <c r="D179" t="n">
         <v>5451</v>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="F177" t="n">
+      <c r="F179" t="n">
         <v>1752800</v>
       </c>
-      <c r="G177" t="n">
+      <c r="G179" t="n">
         <v>5669831000</v>
       </c>
-      <c r="H177" t="n">
+      <c r="H179" t="n">
         <v>3234.727863989046</v>
       </c>
-      <c r="I177" t="n">
+      <c r="I179" t="n">
         <v>5.029999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,49 +2649,49 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6890</v>
+        <v>1882</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G61" t="n">
-        <v>203000</v>
+        <v>2984068000</v>
       </c>
       <c r="H61" t="n">
-        <v>2030</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2700,21 +2700,21 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H62" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -2723,12 +2723,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H63" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H64" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -2797,12 +2797,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2811,81 +2811,81 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H65" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I65" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G66" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H66" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I66" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1882</v>
+        <v>2229</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2893,64 +2893,64 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4275700</v>
+        <v>8012900</v>
       </c>
       <c r="G67" t="n">
-        <v>5047062000</v>
+        <v>23390757000</v>
       </c>
       <c r="H67" t="n">
-        <v>1180.406015389293</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I67" t="n">
-        <v>8.48</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G68" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H68" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I68" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2982,49 +2982,49 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G70" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H70" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I70" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3037,105 +3037,105 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>5295000</v>
+        <v>4783700</v>
       </c>
       <c r="G71" t="n">
-        <v>6250386000</v>
+        <v>5646776000</v>
       </c>
       <c r="H71" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I71" t="n">
-        <v>10.51</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1297500</v>
+        <v>5295000</v>
       </c>
       <c r="G72" t="n">
-        <v>4476090000</v>
+        <v>6250386000</v>
       </c>
       <c r="H72" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I72" t="n">
-        <v>5.23</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>5865200</v>
+        <v>1297500</v>
       </c>
       <c r="G73" t="n">
-        <v>6923530000</v>
+        <v>4476090000</v>
       </c>
       <c r="H73" t="n">
-        <v>1180.442269658324</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I73" t="n">
-        <v>11.64</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3148,31 +3148,31 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6431400</v>
+        <v>5865200</v>
       </c>
       <c r="G74" t="n">
-        <v>7591952000</v>
+        <v>6923530000</v>
       </c>
       <c r="H74" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I74" t="n">
-        <v>12.76</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3185,31 +3185,31 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6942800</v>
+        <v>6431400</v>
       </c>
       <c r="G75" t="n">
-        <v>8195680000</v>
+        <v>7591952000</v>
       </c>
       <c r="H75" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I75" t="n">
-        <v>13.78</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3222,31 +3222,31 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>7455900</v>
+        <v>6942800</v>
       </c>
       <c r="G76" t="n">
-        <v>8801415000</v>
+        <v>8195680000</v>
       </c>
       <c r="H76" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I76" t="n">
-        <v>14.79</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3255,257 +3255,257 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1481600</v>
+        <v>7455900</v>
       </c>
       <c r="G77" t="n">
-        <v>5294365000</v>
+        <v>8801415000</v>
       </c>
       <c r="H77" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6952</v>
+        <v>5331</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>12332900</v>
+        <v>1481600</v>
       </c>
       <c r="G78" t="n">
-        <v>14653495000</v>
+        <v>5294365000</v>
       </c>
       <c r="H78" t="n">
-        <v>1188.162962482466</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I78" t="n">
-        <v>5.19</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6145</v>
+        <v>6952</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>100</v>
+        <v>12332900</v>
       </c>
       <c r="G79" t="n">
-        <v>171000</v>
+        <v>14653495000</v>
       </c>
       <c r="H79" t="n">
-        <v>1710</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8715</v>
+        <v>6145</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3810400</v>
+        <v>100</v>
       </c>
       <c r="G80" t="n">
-        <v>2500615000</v>
+        <v>171000</v>
       </c>
       <c r="H80" t="n">
-        <v>656.2604975855553</v>
+        <v>1710</v>
       </c>
       <c r="I80" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8585</v>
+        <v>8715</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>8986800</v>
+        <v>3810400</v>
       </c>
       <c r="G81" t="n">
-        <v>7174886000</v>
+        <v>2500615000</v>
       </c>
       <c r="H81" t="n">
-        <v>798.3805136422309</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I81" t="n">
-        <v>5.23</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6908</v>
+        <v>8585</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>400</v>
+        <v>8986800</v>
       </c>
       <c r="G82" t="n">
-        <v>992000</v>
+        <v>7174886000</v>
       </c>
       <c r="H82" t="n">
-        <v>2480</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8923</v>
+        <v>6908</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2434800</v>
+        <v>400</v>
       </c>
       <c r="G83" t="n">
-        <v>4266809000</v>
+        <v>992000</v>
       </c>
       <c r="H83" t="n">
-        <v>1752.426893379333</v>
+        <v>2480</v>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3514,190 +3514,190 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>9069</v>
+        <v>8923</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8793900</v>
+        <v>2434800</v>
       </c>
       <c r="G84" t="n">
-        <v>13684104000</v>
+        <v>4266809000</v>
       </c>
       <c r="H84" t="n">
-        <v>1556.090471804319</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I84" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1878</v>
+        <v>9069</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3475000</v>
+        <v>8793900</v>
       </c>
       <c r="G85" t="n">
-        <v>47745269000</v>
+        <v>13684104000</v>
       </c>
       <c r="H85" t="n">
-        <v>13739.64575539568</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I85" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3328</v>
+        <v>1878</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>3475000</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>47745269000</v>
+      </c>
+      <c r="H86" t="n">
+        <v>13739.64575539568</v>
+      </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3076</v>
+        <v>3328</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2841700</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>5705436000</v>
-      </c>
-      <c r="H87" t="n">
-        <v>2007.754513143541</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G88" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H88" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>9302</v>
+        <v>3106</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3705,27 +3705,27 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3799000</v>
+        <v>900156</v>
       </c>
       <c r="G89" t="n">
-        <v>5671170000</v>
+        <v>4095263000</v>
       </c>
       <c r="H89" t="n">
-        <v>1492.806001579363</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I89" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3734,72 +3734,72 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G90" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H90" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I90" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4619</v>
+        <v>9684</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G91" t="n">
-        <v>119000</v>
+        <v>42054369000</v>
       </c>
       <c r="H91" t="n">
-        <v>1190</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6332</v>
+        <v>4619</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>100</v>
       </c>
       <c r="G92" t="n">
-        <v>141000</v>
+        <v>119000</v>
       </c>
       <c r="H92" t="n">
-        <v>1410</v>
+        <v>1190</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -3831,58 +3831,58 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4849</v>
+        <v>6332</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G93" t="n">
-        <v>5148132000</v>
+        <v>141000</v>
       </c>
       <c r="H93" t="n">
-        <v>1746.940387696806</v>
+        <v>1410</v>
       </c>
       <c r="I93" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6927</v>
+        <v>4849</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3890,175 +3890,175 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1142700</v>
+        <v>2946942</v>
       </c>
       <c r="G94" t="n">
-        <v>1023871000</v>
+        <v>5148132000</v>
       </c>
       <c r="H94" t="n">
-        <v>896.0103264198827</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I94" t="n">
-        <v>5.01</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4676</v>
+        <v>6927</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G95" t="n">
-        <v>242000</v>
+        <v>1023871000</v>
       </c>
       <c r="H95" t="n">
-        <v>2420</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1776</v>
+        <v>4676</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G96" t="n">
-        <v>153399000</v>
+        <v>242000</v>
       </c>
       <c r="H96" t="n">
-        <v>1212.640316205534</v>
+        <v>2420</v>
       </c>
       <c r="I96" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3963</v>
+        <v>1776</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1507900</v>
+        <v>126500</v>
       </c>
       <c r="G97" t="n">
-        <v>635874000</v>
+        <v>153399000</v>
       </c>
       <c r="H97" t="n">
-        <v>421.6950726175476</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I97" t="n">
-        <v>5.18</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6923</v>
+        <v>3963</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>100</v>
+        <v>1507900</v>
       </c>
       <c r="G98" t="n">
-        <v>256000</v>
+        <v>635874000</v>
       </c>
       <c r="H98" t="n">
-        <v>2560</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4067,192 +4067,192 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6890</v>
+        <v>6923</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G99" t="n">
-        <v>71610000</v>
+        <v>256000</v>
       </c>
       <c r="H99" t="n">
-        <v>2387</v>
+        <v>2560</v>
       </c>
       <c r="I99" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3132</v>
+        <v>6890</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>8970900</v>
+        <v>30000</v>
       </c>
       <c r="G100" t="n">
-        <v>10240398000</v>
+        <v>71610000</v>
       </c>
       <c r="H100" t="n">
-        <v>1141.512891683109</v>
+        <v>2387</v>
       </c>
       <c r="I100" t="n">
-        <v>5.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4512</v>
+        <v>3132</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2137400</v>
+        <v>8970900</v>
       </c>
       <c r="G101" t="n">
-        <v>620573000</v>
+        <v>10240398000</v>
       </c>
       <c r="H101" t="n">
-        <v>290.3401328717133</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I101" t="n">
-        <v>6.140000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9006</v>
+        <v>4512</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>30000</v>
+        <v>2137400</v>
       </c>
       <c r="G102" t="n">
-        <v>34824000</v>
+        <v>620573000</v>
       </c>
       <c r="H102" t="n">
-        <v>1160.8</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I102" t="n">
-        <v>0.01</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G103" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H103" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9987</v>
+        <v>4626</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4260,101 +4260,101 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3888200</v>
+        <v>4670190</v>
       </c>
       <c r="G104" t="n">
-        <v>16086019000</v>
+        <v>16652257000</v>
       </c>
       <c r="H104" t="n">
-        <v>4137.137750115735</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G105" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H105" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I105" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3861</v>
+        <v>7732</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G106" t="n">
-        <v>59000</v>
+        <v>16678425000</v>
       </c>
       <c r="H106" t="n">
-        <v>590</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5715</v>
+        <v>3861</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>160000</v>
+        <v>59000</v>
       </c>
       <c r="H107" t="n">
-        <v>1600</v>
+        <v>590</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -4386,49 +4386,49 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G108" t="n">
-        <v>9401444000</v>
+        <v>160000</v>
       </c>
       <c r="H108" t="n">
-        <v>1170.279952698077</v>
+        <v>1600</v>
       </c>
       <c r="I108" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4441,68 +4441,68 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>8007300</v>
+        <v>8033500</v>
       </c>
       <c r="G109" t="n">
-        <v>9367939000</v>
+        <v>9401444000</v>
       </c>
       <c r="H109" t="n">
-        <v>1169.924818603025</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I109" t="n">
-        <v>15.89</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2891700</v>
+        <v>8007300</v>
       </c>
       <c r="G110" t="n">
-        <v>3425686000</v>
+        <v>9367939000</v>
       </c>
       <c r="H110" t="n">
-        <v>1184.661617733513</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I110" t="n">
-        <v>7.12</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4511,183 +4511,183 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4452</v>
+        <v>3978</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>24347342</v>
+        <v>2891700</v>
       </c>
       <c r="G111" t="n">
-        <v>148917027000</v>
+        <v>3425686000</v>
       </c>
       <c r="H111" t="n">
-        <v>6116.356643776557</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I111" t="n">
-        <v>5.23</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9257</v>
+        <v>4452</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>100</v>
+        <v>24347342</v>
       </c>
       <c r="G112" t="n">
-        <v>57000</v>
+        <v>148917027000</v>
       </c>
       <c r="H112" t="n">
-        <v>570</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1882</v>
+        <v>9257</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>7914900</v>
+        <v>100</v>
       </c>
       <c r="G113" t="n">
-        <v>9250219000</v>
+        <v>57000</v>
       </c>
       <c r="H113" t="n">
-        <v>1168.709522546084</v>
+        <v>570</v>
       </c>
       <c r="I113" t="n">
-        <v>15.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>9531</v>
+        <v>1882</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>19554300</v>
+        <v>7914900</v>
       </c>
       <c r="G114" t="n">
-        <v>64960321000</v>
+        <v>9250219000</v>
       </c>
       <c r="H114" t="n">
-        <v>3322.047887165483</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I114" t="n">
-        <v>5.029999999999999</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4385</v>
+        <v>9531</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>8815360</v>
+        <v>19554300</v>
       </c>
       <c r="G115" t="n">
-        <v>17684138000</v>
+        <v>64960321000</v>
       </c>
       <c r="H115" t="n">
-        <v>2006.059650428343</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I115" t="n">
-        <v>5.37</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4696,35 +4696,35 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>7984</v>
+        <v>4385</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6096500</v>
+        <v>8815360</v>
       </c>
       <c r="G116" t="n">
-        <v>13153972000</v>
+        <v>17684138000</v>
       </c>
       <c r="H116" t="n">
-        <v>2157.626835069302</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I116" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4733,146 +4733,146 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1973</v>
+        <v>7984</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>8973383</v>
+        <v>6096500</v>
       </c>
       <c r="G117" t="n">
-        <v>24947403000</v>
+        <v>13153972000</v>
       </c>
       <c r="H117" t="n">
-        <v>2780.155823060266</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I117" t="n">
-        <v>6.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>6908</v>
+        <v>1973</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>502000</v>
+        <v>8973383</v>
       </c>
       <c r="G118" t="n">
-        <v>1257178000</v>
+        <v>24947403000</v>
       </c>
       <c r="H118" t="n">
-        <v>2504.338645418327</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I118" t="n">
-        <v>2.04</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3765</v>
+        <v>6908</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>4552900</v>
+        <v>502000</v>
       </c>
       <c r="G119" t="n">
-        <v>13383536000</v>
+        <v>1257178000</v>
       </c>
       <c r="H119" t="n">
-        <v>2939.562915943684</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I119" t="n">
-        <v>5.47</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5482</v>
+        <v>3765</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>433300</v>
+        <v>4552900</v>
       </c>
       <c r="G120" t="n">
-        <v>1367192000</v>
+        <v>13383536000</v>
       </c>
       <c r="H120" t="n">
-        <v>3155.301177013616</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I120" t="n">
-        <v>2.18</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4881,44 +4881,44 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>8141</v>
+        <v>5482</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>100</v>
+        <v>433300</v>
       </c>
       <c r="G121" t="n">
-        <v>93000</v>
+        <v>1367192000</v>
       </c>
       <c r="H121" t="n">
-        <v>930</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4272</v>
+        <v>8141</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4926,96 +4926,96 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>26855100</v>
+        <v>100</v>
       </c>
       <c r="G122" t="n">
-        <v>29860350000</v>
+        <v>93000</v>
       </c>
       <c r="H122" t="n">
-        <v>1111.90611839092</v>
+        <v>930</v>
       </c>
       <c r="I122" t="n">
-        <v>15.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6145</v>
+        <v>4272</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>100</v>
+        <v>26855100</v>
       </c>
       <c r="G123" t="n">
-        <v>171000</v>
+        <v>29860350000</v>
       </c>
       <c r="H123" t="n">
-        <v>1710</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G124" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H124" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I124" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>3569</v>
+        <v>4205</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -5037,175 +5037,175 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>4271704</v>
+        <v>14426600</v>
       </c>
       <c r="G125" t="n">
-        <v>5808044000</v>
+        <v>24829312000</v>
       </c>
       <c r="H125" t="n">
-        <v>1359.655069733296</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I125" t="n">
-        <v>6.279999999999999</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G126" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H126" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I126" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2327</v>
+        <v>6516</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>9154320</v>
+        <v>679500</v>
       </c>
       <c r="G127" t="n">
-        <v>23450671000</v>
+        <v>4792335000</v>
       </c>
       <c r="H127" t="n">
-        <v>2561.705402476645</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3989</v>
+        <v>2327</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1206000</v>
+        <v>9154320</v>
       </c>
       <c r="G128" t="n">
-        <v>787604000</v>
+        <v>23450671000</v>
       </c>
       <c r="H128" t="n">
-        <v>653.0713101160862</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I128" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6908</v>
+        <v>3989</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>100</v>
+        <v>1206000</v>
       </c>
       <c r="G129" t="n">
-        <v>288000</v>
+        <v>787604000</v>
       </c>
       <c r="H129" t="n">
-        <v>2880</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5214,72 +5214,72 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5988</v>
+        <v>6908</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>527300</v>
+        <v>100</v>
       </c>
       <c r="G130" t="n">
-        <v>1212090000</v>
+        <v>288000</v>
       </c>
       <c r="H130" t="n">
-        <v>2298.672482457804</v>
+        <v>2880</v>
       </c>
       <c r="I130" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3529</v>
+        <v>5988</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>998000</v>
+        <v>527300</v>
       </c>
       <c r="G131" t="n">
-        <v>667598000</v>
+        <v>1212090000</v>
       </c>
       <c r="H131" t="n">
-        <v>668.9358717434869</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I131" t="n">
-        <v>5.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5288,81 +5288,81 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7305</v>
+        <v>3529</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>309800</v>
+        <v>998000</v>
       </c>
       <c r="G132" t="n">
-        <v>1321438000</v>
+        <v>667598000</v>
       </c>
       <c r="H132" t="n">
-        <v>4265.455132343447</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I132" t="n">
-        <v>5.12</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5541</v>
+        <v>7305</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>100</v>
+        <v>309800</v>
       </c>
       <c r="G133" t="n">
-        <v>127000</v>
+        <v>1321438000</v>
       </c>
       <c r="H133" t="n">
-        <v>1270</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2168</v>
+        <v>5541</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5370,27 +5370,27 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2094200</v>
+        <v>100</v>
       </c>
       <c r="G134" t="n">
-        <v>4445105000</v>
+        <v>127000</v>
       </c>
       <c r="H134" t="n">
-        <v>2122.579027791042</v>
+        <v>1270</v>
       </c>
       <c r="I134" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5399,35 +5399,35 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G135" t="n">
-        <v>8729143000</v>
+        <v>4445105000</v>
       </c>
       <c r="H135" t="n">
-        <v>2148.936934940886</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I135" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5447,10 +5447,10 @@
         <v>4062075</v>
       </c>
       <c r="G136" t="n">
-        <v>20578848000</v>
+        <v>8729143000</v>
       </c>
       <c r="H136" t="n">
-        <v>5066.092575838703</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I136" t="n">
         <v>5.2</v>
@@ -5459,21 +5459,21 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5481,175 +5481,175 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G137" t="n">
-        <v>361000</v>
+        <v>20578848000</v>
       </c>
       <c r="H137" t="n">
-        <v>3610</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>9882</v>
+        <v>8803</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>2505000</v>
+        <v>100</v>
       </c>
       <c r="G138" t="n">
-        <v>5292086000</v>
+        <v>361000</v>
       </c>
       <c r="H138" t="n">
-        <v>2112.609181636727</v>
+        <v>3610</v>
       </c>
       <c r="I138" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8129</v>
+        <v>9882</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>7258230</v>
+        <v>2505000</v>
       </c>
       <c r="G139" t="n">
-        <v>24720910000</v>
+        <v>5292086000</v>
       </c>
       <c r="H139" t="n">
-        <v>3405.914389596362</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I139" t="n">
-        <v>9.460000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2206</v>
+        <v>8129</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3462600</v>
+        <v>7258230</v>
       </c>
       <c r="G140" t="n">
-        <v>14385811000</v>
+        <v>24720910000</v>
       </c>
       <c r="H140" t="n">
-        <v>4154.626869982095</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I140" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3666</v>
+        <v>2206</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1053200</v>
+        <v>3462600</v>
       </c>
       <c r="G141" t="n">
-        <v>663809000</v>
+        <v>14385811000</v>
       </c>
       <c r="H141" t="n">
-        <v>630.278199772123</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I141" t="n">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5658,192 +5658,192 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4347</v>
+        <v>3666</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>614893</v>
+        <v>1053200</v>
       </c>
       <c r="G142" t="n">
-        <v>940560000</v>
+        <v>663809000</v>
       </c>
       <c r="H142" t="n">
-        <v>1529.631984751819</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I142" t="n">
-        <v>8.200000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>8129</v>
+        <v>4347</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3886330</v>
+        <v>614893</v>
       </c>
       <c r="G143" t="n">
-        <v>10549885000</v>
+        <v>940560000</v>
       </c>
       <c r="H143" t="n">
-        <v>2714.613787300615</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I143" t="n">
-        <v>5.06</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8929</v>
+        <v>8129</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1260812</v>
+        <v>3886330</v>
       </c>
       <c r="G144" t="n">
-        <v>1699255000</v>
+        <v>10549885000</v>
       </c>
       <c r="H144" t="n">
-        <v>1347.74653160027</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I144" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>7278</v>
+        <v>8929</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>115400</v>
+        <v>1260812</v>
       </c>
       <c r="G145" t="n">
-        <v>302115000</v>
+        <v>1699255000</v>
       </c>
       <c r="H145" t="n">
-        <v>2617.980935875217</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I145" t="n">
-        <v>0.24</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3591</v>
+        <v>7278</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2846091</v>
+        <v>115400</v>
       </c>
       <c r="G146" t="n">
-        <v>6888596000</v>
+        <v>302115000</v>
       </c>
       <c r="H146" t="n">
-        <v>2420.370957920882</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I146" t="n">
-        <v>5.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4042</v>
+        <v>3591</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5851,249 +5851,249 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>16459200</v>
+        <v>2846091</v>
       </c>
       <c r="G147" t="n">
-        <v>33451116000</v>
+        <v>6888596000</v>
       </c>
       <c r="H147" t="n">
-        <v>2032.365850102071</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I147" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4521</v>
+        <v>4042</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>100</v>
+        <v>16459200</v>
       </c>
       <c r="G148" t="n">
-        <v>353000</v>
+        <v>33451116000</v>
       </c>
       <c r="H148" t="n">
-        <v>3530</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>8923</v>
+        <v>4521</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2445600</v>
+        <v>100</v>
       </c>
       <c r="G149" t="n">
-        <v>3856031000</v>
+        <v>353000</v>
       </c>
       <c r="H149" t="n">
-        <v>1576.721867844292</v>
+        <v>3530</v>
       </c>
       <c r="I149" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4347</v>
+        <v>8923</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>400493</v>
+        <v>2445600</v>
       </c>
       <c r="G150" t="n">
-        <v>580713000</v>
+        <v>3856031000</v>
       </c>
       <c r="H150" t="n">
-        <v>1449.995380693296</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I150" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>9024</v>
+        <v>4347</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>16207437</v>
+        <v>400493</v>
       </c>
       <c r="G151" t="n">
-        <v>27823532000</v>
+        <v>580713000</v>
       </c>
       <c r="H151" t="n">
-        <v>1716.713876475349</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I151" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1518</v>
+        <v>9024</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G152" t="n">
-        <v>292000</v>
+        <v>27823532000</v>
       </c>
       <c r="H152" t="n">
-        <v>2920</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>7731</v>
+        <v>1518</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>17639800</v>
+        <v>100</v>
       </c>
       <c r="G153" t="n">
-        <v>26675255000</v>
+        <v>292000</v>
       </c>
       <c r="H153" t="n">
-        <v>1512.21980974841</v>
+        <v>2920</v>
       </c>
       <c r="I153" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6102,21 +6102,21 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4536</v>
+        <v>7731</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>18290500</v>
+        <v>17639800</v>
       </c>
       <c r="G154" t="n">
-        <v>24591924000</v>
+        <v>26675255000</v>
       </c>
       <c r="H154" t="n">
-        <v>1344.518957928979</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I154" t="n">
         <v>5.02</v>
@@ -6125,197 +6125,197 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4185</v>
+        <v>4536</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G155" t="n">
-        <v>405000</v>
+        <v>24591924000</v>
       </c>
       <c r="H155" t="n">
-        <v>4050</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4549</v>
+        <v>4185</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G156" t="n">
-        <v>3367745000</v>
+        <v>405000</v>
       </c>
       <c r="H156" t="n">
-        <v>1678.083113259255</v>
+        <v>4050</v>
       </c>
       <c r="I156" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>9627</v>
+        <v>4549</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3401100</v>
+        <v>2006900</v>
       </c>
       <c r="G157" t="n">
-        <v>9648726000</v>
+        <v>3367745000</v>
       </c>
       <c r="H157" t="n">
-        <v>2836.942753814942</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I157" t="n">
-        <v>9.6</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>8304</v>
+        <v>9627</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>100</v>
+        <v>3401100</v>
       </c>
       <c r="G158" t="n">
-        <v>219000</v>
+        <v>9648726000</v>
       </c>
       <c r="H158" t="n">
-        <v>2190</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G159" t="n">
-        <v>1219326000</v>
+        <v>219000</v>
       </c>
       <c r="H159" t="n">
-        <v>1442.477227019993</v>
+        <v>2190</v>
       </c>
       <c r="I159" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6328,142 +6328,142 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>675500</v>
+        <v>845300</v>
       </c>
       <c r="G160" t="n">
-        <v>976503000</v>
+        <v>1219326000</v>
       </c>
       <c r="H160" t="n">
-        <v>1445.60029607698</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I160" t="n">
-        <v>5.220000000000001</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2505000</v>
+        <v>675500</v>
       </c>
       <c r="G161" t="n">
-        <v>3361654000</v>
+        <v>976503000</v>
       </c>
       <c r="H161" t="n">
-        <v>1341.977644710579</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I161" t="n">
-        <v>5.09</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5541</v>
+        <v>8818</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>100</v>
+        <v>2505000</v>
       </c>
       <c r="G162" t="n">
-        <v>117000</v>
+        <v>3361654000</v>
       </c>
       <c r="H162" t="n">
-        <v>1170</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>7315</v>
+        <v>5541</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>6994900</v>
+        <v>100</v>
       </c>
       <c r="G163" t="n">
-        <v>5874641000</v>
+        <v>117000</v>
       </c>
       <c r="H163" t="n">
-        <v>839.8463166020958</v>
+        <v>1170</v>
       </c>
       <c r="I163" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6472,35 +6472,35 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4837</v>
+        <v>7315</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>5428600</v>
+        <v>6994900</v>
       </c>
       <c r="G164" t="n">
-        <v>4378021000</v>
+        <v>5874641000</v>
       </c>
       <c r="H164" t="n">
-        <v>806.4733080352208</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I164" t="n">
-        <v>9.74</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6509,30 +6509,30 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4293</v>
+        <v>4837</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>20896886</v>
+        <v>5428600</v>
       </c>
       <c r="G165" t="n">
-        <v>9376038000</v>
+        <v>4378021000</v>
       </c>
       <c r="H165" t="n">
-        <v>448.6811097117532</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I165" t="n">
-        <v>9.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4631</v>
+        <v>4293</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6554,355 +6554,355 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>6563759</v>
+        <v>20896886</v>
       </c>
       <c r="G166" t="n">
-        <v>16844475000</v>
+        <v>9376038000</v>
       </c>
       <c r="H166" t="n">
-        <v>2566.284807227078</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I166" t="n">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5449</v>
+        <v>4631</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2114100</v>
+        <v>6563759</v>
       </c>
       <c r="G167" t="n">
-        <v>3695597000</v>
+        <v>16844475000</v>
       </c>
       <c r="H167" t="n">
-        <v>1748.071046781136</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>6232</v>
+        <v>5449</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1499000</v>
+        <v>2114100</v>
       </c>
       <c r="G168" t="n">
-        <v>1369002000</v>
+        <v>3695597000</v>
       </c>
       <c r="H168" t="n">
-        <v>913.2768512341561</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I168" t="n">
-        <v>10.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6237</v>
+        <v>6232</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1129500</v>
+        <v>1499000</v>
       </c>
       <c r="G169" t="n">
-        <v>1537738000</v>
+        <v>1369002000</v>
       </c>
       <c r="H169" t="n">
-        <v>1361.432492253209</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I169" t="n">
-        <v>5.02</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4987</v>
+        <v>6237</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1543800</v>
+        <v>1129500</v>
       </c>
       <c r="G170" t="n">
-        <v>874286000</v>
+        <v>1537738000</v>
       </c>
       <c r="H170" t="n">
-        <v>566.3207669387226</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I170" t="n">
-        <v>5.779999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4739</v>
+        <v>4987</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>15400600</v>
+        <v>1543800</v>
       </c>
       <c r="G171" t="n">
-        <v>66216726000</v>
+        <v>874286000</v>
       </c>
       <c r="H171" t="n">
-        <v>4299.619884939548</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I171" t="n">
-        <v>6.419999999999999</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2501</v>
+        <v>4739</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>4010500</v>
+        <v>15400600</v>
       </c>
       <c r="G172" t="n">
-        <v>10817766000</v>
+        <v>66216726000</v>
       </c>
       <c r="H172" t="n">
-        <v>2697.360927565142</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I172" t="n">
-        <v>5.09</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4023</v>
+        <v>2501</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>100</v>
+        <v>4010500</v>
       </c>
       <c r="G173" t="n">
-        <v>796000</v>
+        <v>10817766000</v>
       </c>
       <c r="H173" t="n">
-        <v>7960</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5844</v>
+        <v>4023</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>4998800</v>
+        <v>100</v>
       </c>
       <c r="G174" t="n">
-        <v>24949147000</v>
+        <v>796000</v>
       </c>
       <c r="H174" t="n">
-        <v>4991.027246539169</v>
+        <v>7960</v>
       </c>
       <c r="I174" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G175" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H175" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I175" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5186</v>
+        <v>5947</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6924,122 +6924,159 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1536900</v>
+        <v>7446200</v>
       </c>
       <c r="G176" t="n">
-        <v>4758738000</v>
+        <v>21182239000</v>
       </c>
       <c r="H176" t="n">
-        <v>3096.322467304314</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I176" t="n">
-        <v>5.08</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>8303</v>
+        <v>5186</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>20000000</v>
+        <v>1536900</v>
       </c>
       <c r="G177" t="n">
-        <v>56014500000</v>
+        <v>4758738000</v>
       </c>
       <c r="H177" t="n">
-        <v>2800.725</v>
+        <v>3096.322467304314</v>
       </c>
       <c r="I177" t="n">
-        <v>9.75</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2812</v>
+        <v>8303</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
+        <v>20000000</v>
+      </c>
+      <c r="G178" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H178" t="n">
+        <v>2800.725</v>
+      </c>
       <c r="I178" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>S100RVIC.zip</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>2812</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
           <t>S100RU33.zip</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
-      <c r="D179" t="n">
+      <c r="D180" t="n">
         <v>5451</v>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="F179" t="n">
+      <c r="F180" t="n">
         <v>1752800</v>
       </c>
-      <c r="G179" t="n">
+      <c r="G180" t="n">
         <v>5669831000</v>
       </c>
-      <c r="H179" t="n">
+      <c r="H180" t="n">
         <v>3234.727863989046</v>
       </c>
-      <c r="I179" t="n">
+      <c r="I180" t="n">
         <v>5.029999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,160 +910,160 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100YG8O.zip</t>
+          <t>S100Z17N.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-06-16_01_2026-06-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9854</v>
+        <v>2001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1054100</v>
+        <v>4316500</v>
       </c>
       <c r="G14" t="n">
-        <v>260332000</v>
+        <v>11637840000</v>
       </c>
       <c r="H14" t="n">
-        <v>246.9708756284982</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100YD9N.zip</t>
+          <t>S100YG8O.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-15_01_2026-06-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-06-16_01_2026-06-23.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4088</v>
+        <v>9854</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>13900548</v>
+        <v>1054100</v>
       </c>
       <c r="G15" t="n">
-        <v>31441383000</v>
+        <v>260332000</v>
       </c>
       <c r="H15" t="n">
-        <v>2261.880826568852</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="I15" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100YFL5.zip</t>
+          <t>S100YD9N.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-06-12_01_2026-06-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-15_01_2026-06-22.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3086</v>
+        <v>4088</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>13792100</v>
+        <v>13900548</v>
       </c>
       <c r="G16" t="n">
-        <v>25198319000</v>
+        <v>31441383000</v>
       </c>
       <c r="H16" t="n">
-        <v>1827.011042553346</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100YB6N.zip</t>
+          <t>S100YFL5.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-10_01_2026-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-06-12_01_2026-06-19.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7122</v>
+        <v>3086</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>480500</v>
+        <v>13792100</v>
       </c>
       <c r="G17" t="n">
-        <v>1030622000</v>
+        <v>25198319000</v>
       </c>
       <c r="H17" t="n">
-        <v>2144.894901144641</v>
+        <v>1827.011042553346</v>
       </c>
       <c r="I17" t="n">
-        <v>6.959999999999999</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100YIZN.zip</t>
+          <t>S100YB6N.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-09_02_2026-06-25.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-10_01_2026-06-17.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1072,35 +1072,35 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6890</v>
+        <v>7122</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4020953</v>
+        <v>480500</v>
       </c>
       <c r="G18" t="n">
-        <v>16234608000</v>
+        <v>1030622000</v>
       </c>
       <c r="H18" t="n">
-        <v>4037.502552255647</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="I18" t="n">
-        <v>7.630000000000001</v>
+        <v>6.959999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100Y85I.zip</t>
+          <t>S100YIZN.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-01_01_2026-06-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-09_02_2026-06-25.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1109,35 +1109,35 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3905</v>
+        <v>6890</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3115000</v>
+        <v>4020953</v>
       </c>
       <c r="G19" t="n">
-        <v>16021306000</v>
+        <v>16234608000</v>
       </c>
       <c r="H19" t="n">
-        <v>5143.276404494382</v>
+        <v>4037.502552255647</v>
       </c>
       <c r="I19" t="n">
-        <v>9.76</v>
+        <v>7.630000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100Y79Q.zip</t>
+          <t>S100Y85I.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-01_01_2026-06-02.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1146,72 +1146,72 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2871</v>
+        <v>3905</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12872200</v>
+        <v>3115000</v>
       </c>
       <c r="G20" t="n">
-        <v>23365599000</v>
+        <v>16021306000</v>
       </c>
       <c r="H20" t="n">
-        <v>1815.198567455447</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="I20" t="n">
-        <v>5.01</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100Y5E5.zip</t>
+          <t>S100Y79Q.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9274</v>
+        <v>2871</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>100</v>
+        <v>12872200</v>
       </c>
       <c r="G21" t="n">
-        <v>73000</v>
+        <v>23365599000</v>
       </c>
       <c r="H21" t="n">
-        <v>730</v>
+        <v>1815.198567455447</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100Y3QD.zip</t>
+          <t>S100Y5E5.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1220,21 +1220,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4088</v>
+        <v>9274</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>197000</v>
+        <v>73000</v>
       </c>
       <c r="H22" t="n">
-        <v>1970</v>
+        <v>730</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1243,58 +1243,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100Y2BG.zip</t>
+          <t>S100Y3QD.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7244</v>
+        <v>4088</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5197900</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>2856142000</v>
+        <v>197000</v>
       </c>
       <c r="H23" t="n">
-        <v>549.4799823005444</v>
+        <v>1970</v>
       </c>
       <c r="I23" t="n">
-        <v>5.390000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100Y2OE.zip</t>
+          <t>S100Y2BG.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3863</v>
+        <v>7244</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1302,36 +1302,36 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>5197900</v>
       </c>
       <c r="G24" t="n">
-        <v>125000</v>
+        <v>2856142000</v>
       </c>
       <c r="H24" t="n">
-        <v>1250</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5.390000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100Y2B5.zip</t>
+          <t>S100Y2OE.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7004</v>
+        <v>3863</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1339,27 +1339,27 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9267600</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>9449965000</v>
+        <v>125000</v>
       </c>
       <c r="H25" t="n">
-        <v>1019.677694332945</v>
+        <v>1250</v>
       </c>
       <c r="I25" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100Y25J.zip</t>
+          <t>S100Y2B5.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1368,35 +1368,35 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7242</v>
+        <v>7004</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2841100</v>
+        <v>9267600</v>
       </c>
       <c r="G26" t="n">
-        <v>8024171000</v>
+        <v>9449965000</v>
       </c>
       <c r="H26" t="n">
-        <v>2824.318397803668</v>
+        <v>1019.677694332945</v>
       </c>
       <c r="I26" t="n">
-        <v>5.63</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100Y1ML.zip</t>
+          <t>S100Y25J.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1405,35 +1405,35 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3774</v>
+        <v>7242</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13723994</v>
+        <v>2841100</v>
       </c>
       <c r="G27" t="n">
-        <v>36441482000</v>
+        <v>8024171000</v>
       </c>
       <c r="H27" t="n">
-        <v>2655.311711736394</v>
+        <v>2824.318397803668</v>
       </c>
       <c r="I27" t="n">
-        <v>7.48</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100Y12P.zip</t>
+          <t>S100Y1ML.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1442,192 +1442,192 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4071</v>
+        <v>3774</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3400107</v>
+        <v>13723994</v>
       </c>
       <c r="G28" t="n">
-        <v>7823559000</v>
+        <v>36441482000</v>
       </c>
       <c r="H28" t="n">
-        <v>2300.974351689521</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="I28" t="n">
-        <v>8.02</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100Y15W.zip</t>
+          <t>S100Y12P.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9147</v>
+        <v>4071</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>12252200</v>
+        <v>3400107</v>
       </c>
       <c r="G29" t="n">
-        <v>40939867000</v>
+        <v>7823559000</v>
       </c>
       <c r="H29" t="n">
-        <v>3341.42986565678</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="I29" t="n">
-        <v>5.04</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100XXO7.zip</t>
+          <t>S100Y15W.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4626</v>
+        <v>9147</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>17384460</v>
+        <v>12252200</v>
       </c>
       <c r="G30" t="n">
-        <v>38239610000</v>
+        <v>40939867000</v>
       </c>
       <c r="H30" t="n">
-        <v>2199.643244598912</v>
+        <v>3341.42986565678</v>
       </c>
       <c r="I30" t="n">
-        <v>14.88</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100XW5T.zip</t>
+          <t>S100XXO7.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4613</v>
+        <v>4626</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>8982300</v>
+        <v>17384460</v>
       </c>
       <c r="G31" t="n">
-        <v>21391558000</v>
+        <v>38239610000</v>
       </c>
       <c r="H31" t="n">
-        <v>2381.523440544182</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="I31" t="n">
-        <v>5.050000000000001</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5423</v>
+        <v>4613</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6884398</v>
+        <v>8982300</v>
       </c>
       <c r="G32" t="n">
-        <v>11052572000</v>
+        <v>21391558000</v>
       </c>
       <c r="H32" t="n">
-        <v>1605.452212379354</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I32" t="n">
-        <v>6.25</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6952</v>
+        <v>5423</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1635,73 +1635,73 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>11964800</v>
+        <v>6884398</v>
       </c>
       <c r="G33" t="n">
-        <v>14335634000</v>
+        <v>11052572000</v>
       </c>
       <c r="H33" t="n">
-        <v>1198.150742177053</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I33" t="n">
-        <v>5.029999999999999</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9468</v>
+        <v>6952</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>13197300</v>
+        <v>11964800</v>
       </c>
       <c r="G34" t="n">
-        <v>39531520000</v>
+        <v>14335634000</v>
       </c>
       <c r="H34" t="n">
-        <v>2995.424821743842</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I34" t="n">
-        <v>8.859999999999999</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4676</v>
+        <v>9468</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1709,101 +1709,101 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2662900</v>
+        <v>13197300</v>
       </c>
       <c r="G35" t="n">
-        <v>8365298000</v>
+        <v>39531520000</v>
       </c>
       <c r="H35" t="n">
-        <v>3141.424011416125</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I35" t="n">
-        <v>1.57</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3132</v>
+        <v>4676</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>14653542</v>
+        <v>2662900</v>
       </c>
       <c r="G36" t="n">
-        <v>23038030000</v>
+        <v>8365298000</v>
       </c>
       <c r="H36" t="n">
-        <v>1572.181660925393</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I36" t="n">
-        <v>8.18</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6594</v>
+        <v>3132</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>80322406</v>
+        <v>14653542</v>
       </c>
       <c r="G37" t="n">
-        <v>178330543000</v>
+        <v>23038030000</v>
       </c>
       <c r="H37" t="n">
-        <v>2220.184278344451</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I37" t="n">
-        <v>6.74</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1812,81 +1812,81 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1721</v>
+        <v>6594</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>7462000</v>
+        <v>80322406</v>
       </c>
       <c r="G38" t="n">
-        <v>27875864000</v>
+        <v>178330543000</v>
       </c>
       <c r="H38" t="n">
-        <v>3735.709461270437</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I38" t="n">
-        <v>5.609999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6675</v>
+        <v>1721</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>314400</v>
+        <v>7462000</v>
       </c>
       <c r="G39" t="n">
-        <v>1717778000</v>
+        <v>27875864000</v>
       </c>
       <c r="H39" t="n">
-        <v>5463.67048346056</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I39" t="n">
-        <v>5.029999999999999</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1894,406 +1894,406 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G40" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H40" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I40" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7745</v>
+        <v>3549</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1458700</v>
+        <v>13408159</v>
       </c>
       <c r="G41" t="n">
-        <v>3040190000</v>
+        <v>40855887000</v>
       </c>
       <c r="H41" t="n">
-        <v>2084.177692465894</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I41" t="n">
-        <v>5.24</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G42" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H42" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G43" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H43" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I43" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G44" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H44" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I44" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G45" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H45" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H46" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I46" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G47" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H47" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I47" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G48" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H48" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I48" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G49" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H49" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I49" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G50" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H50" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2301,64 +2301,64 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G51" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H51" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I51" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G52" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H52" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2367,109 +2367,109 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G53" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H53" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I53" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G54" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H54" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I54" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G55" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H55" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I55" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2489,10 +2489,10 @@
         <v>16322100</v>
       </c>
       <c r="G56" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H56" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I56" t="n">
         <v>5.01</v>
@@ -2501,58 +2501,58 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G57" t="n">
-        <v>1831405000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H57" t="n">
-        <v>3321.975331035734</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I57" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2560,138 +2560,138 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G58" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H58" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I58" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4549</v>
+        <v>6856</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2546351</v>
+        <v>4180400</v>
       </c>
       <c r="G59" t="n">
-        <v>4958319000</v>
+        <v>49662804000</v>
       </c>
       <c r="H59" t="n">
-        <v>1947.225264702313</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I59" t="n">
-        <v>7.37</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7940</v>
+        <v>1882</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>100</v>
+        <v>1998200</v>
       </c>
       <c r="G60" t="n">
-        <v>101000</v>
+        <v>2358382000</v>
       </c>
       <c r="H60" t="n">
-        <v>1010</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1882</v>
+        <v>4549</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2528200</v>
+        <v>2546351</v>
       </c>
       <c r="G61" t="n">
-        <v>2984068000</v>
+        <v>4958319000</v>
       </c>
       <c r="H61" t="n">
-        <v>1180.31326635551</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I61" t="n">
-        <v>5.02</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2700,21 +2700,21 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H62" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -2723,49 +2723,49 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2432</v>
+        <v>1882</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G63" t="n">
-        <v>226000</v>
+        <v>2984068000</v>
       </c>
       <c r="H63" t="n">
-        <v>2260</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H64" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -2797,12 +2797,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H65" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -2834,12 +2834,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2848,294 +2848,294 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H66" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I66" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2229</v>
+        <v>4917</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>23390757000</v>
+        <v>204000</v>
       </c>
       <c r="H67" t="n">
-        <v>2919.137515755844</v>
+        <v>2040</v>
       </c>
       <c r="I67" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1882</v>
+        <v>8233</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>4275700</v>
+        <v>261400</v>
       </c>
       <c r="G68" t="n">
-        <v>5047062000</v>
+        <v>287906000</v>
       </c>
       <c r="H68" t="n">
-        <v>1180.406015389293</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I68" t="n">
-        <v>8.48</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G69" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H69" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I69" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G70" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H70" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I70" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G71" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H71" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I71" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G72" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H72" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I72" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1297500</v>
+        <v>4783700</v>
       </c>
       <c r="G73" t="n">
-        <v>4476090000</v>
+        <v>5646776000</v>
       </c>
       <c r="H73" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I73" t="n">
-        <v>5.23</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3148,68 +3148,68 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5865200</v>
+        <v>5295000</v>
       </c>
       <c r="G74" t="n">
-        <v>6923530000</v>
+        <v>6250386000</v>
       </c>
       <c r="H74" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I74" t="n">
-        <v>11.64</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G75" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H75" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I75" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3222,31 +3222,31 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6942800</v>
+        <v>5865200</v>
       </c>
       <c r="G76" t="n">
-        <v>8195680000</v>
+        <v>6923530000</v>
       </c>
       <c r="H76" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I76" t="n">
-        <v>13.78</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3259,31 +3259,31 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>7455900</v>
+        <v>6431400</v>
       </c>
       <c r="G77" t="n">
-        <v>8801415000</v>
+        <v>7591952000</v>
       </c>
       <c r="H77" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I77" t="n">
-        <v>14.79</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3292,403 +3292,405 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G78" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H78" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G79" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H79" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I79" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G80" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H80" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G81" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H81" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I81" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G82" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H82" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I82" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G83" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H83" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G84" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H84" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G85" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H85" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I85" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G86" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H86" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I86" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G88" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H88" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I88" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3697,368 +3699,366 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H89" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G90" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H90" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I90" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G91" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H91" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I91" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4619</v>
+        <v>9302</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G92" t="n">
-        <v>119000</v>
+        <v>5671170000</v>
       </c>
       <c r="H92" t="n">
-        <v>1190</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G93" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H93" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G94" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H94" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I94" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H95" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I95" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G96" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H96" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G97" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H97" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I97" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G98" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H98" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I98" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4067,257 +4067,257 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G99" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H99" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G100" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H100" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I100" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G101" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H101" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I101" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G102" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H102" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I102" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G103" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H103" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I103" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G104" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H104" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I104" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G105" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H105" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4326,442 +4326,442 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G106" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H106" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I106" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G107" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H107" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G108" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H108" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G109" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H109" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I109" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H110" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I110" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G111" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H111" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I111" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G112" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H112" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I112" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G113" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H113" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G114" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H114" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I114" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G115" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H115" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I115" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G116" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H116" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I116" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G117" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H117" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I117" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4770,109 +4770,109 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G118" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H118" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I118" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G119" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H119" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I119" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G120" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H120" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I120" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4881,109 +4881,109 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G121" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H121" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I121" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G122" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H122" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G123" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H123" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I123" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4992,21 +4992,21 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>100</v>
       </c>
       <c r="G124" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H124" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5015,456 +5015,456 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G125" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H125" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I125" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H126" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I126" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G127" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H127" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I127" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2327</v>
+        <v>3569</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>9154320</v>
+        <v>4271704</v>
       </c>
       <c r="G128" t="n">
-        <v>23450671000</v>
+        <v>5808044000</v>
       </c>
       <c r="H128" t="n">
-        <v>2561.705402476645</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G129" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H129" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G130" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H130" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G131" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H131" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I131" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G132" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H132" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I132" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G133" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H133" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I133" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G134" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H134" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G135" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H135" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I135" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G136" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H136" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I136" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5473,44 +5473,44 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G137" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H137" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5518,249 +5518,249 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G138" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H138" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G139" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H139" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I139" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G140" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H140" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I140" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G141" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H141" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I141" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G142" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H142" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I142" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G143" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H143" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I143" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G144" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H144" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I144" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5769,775 +5769,775 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G145" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H145" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I145" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G146" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H146" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I146" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G147" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H147" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I147" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G148" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H148" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I148" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G149" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H149" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G150" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H150" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I150" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G151" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H151" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I151" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G152" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H152" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I152" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G153" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H153" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G154" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H154" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I154" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G155" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H155" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I155" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G156" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H156" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G157" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H157" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I157" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G158" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H158" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I158" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G159" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H159" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G160" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H160" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I160" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G161" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H161" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I161" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G162" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H162" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I162" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G163" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H163" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G164" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H164" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I164" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G165" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H165" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I165" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6546,35 +6546,35 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G166" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H166" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I166" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6583,72 +6583,72 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G167" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H167" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I167" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G168" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H168" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I168" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6657,426 +6657,500 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G169" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H169" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I169" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G170" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H170" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I170" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G171" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H171" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I171" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G172" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H172" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I172" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G173" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H173" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I173" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G174" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H174" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G175" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H175" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I175" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G176" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H176" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I176" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G177" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H177" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I177" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G178" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H178" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I178" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2812</v>
+        <v>5186</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
+        <v>1536900</v>
+      </c>
+      <c r="G179" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H179" t="n">
+        <v>3096.322467304314</v>
+      </c>
       <c r="I179" t="n">
-        <v>9.779999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G180" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H180" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I180" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>S100RVIC.zip</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>2812</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="n">
+        <v>9.779999999999999</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>S100RU33.zip</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
-      <c r="D180" t="n">
+      <c r="D182" t="n">
         <v>5451</v>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="F180" t="n">
+      <c r="F182" t="n">
         <v>1752800</v>
       </c>
-      <c r="G180" t="n">
+      <c r="G182" t="n">
         <v>5669831000</v>
       </c>
-      <c r="H180" t="n">
+      <c r="H182" t="n">
         <v>3234.727863989046</v>
       </c>
-      <c r="I180" t="n">
+      <c r="I182" t="n">
         <v>5.029999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,58 +651,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100YR5Q.zip</t>
+          <t>S100Z1H2.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-07-17_02_2026-09-14.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4025</v>
+        <v>2001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>473300</v>
+        <v>6010300</v>
       </c>
       <c r="G7" t="n">
-        <v>2222596000</v>
+        <v>16368563000</v>
       </c>
       <c r="H7" t="n">
-        <v>4695.956053243186</v>
+        <v>2723.418631349517</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>7.090000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100YR7M.zip</t>
+          <t>S100YR5Q.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3864</v>
+        <v>4025</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -710,27 +710,27 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
+        <v>473300</v>
       </c>
       <c r="G8" t="n">
-        <v>81000</v>
+        <v>2222596000</v>
       </c>
       <c r="H8" t="n">
-        <v>810</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100YR7O.zip</t>
+          <t>S100YR7M.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9831</v>
+        <v>3864</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -750,10 +750,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>53000</v>
+        <v>81000</v>
       </c>
       <c r="H9" t="n">
-        <v>530</v>
+        <v>810</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -762,86 +762,86 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100YMTO.zip</t>
+          <t>S100YR7O.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-25_01_2026-07-02.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2492</v>
+        <v>9831</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13568100</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>5494195000</v>
+        <v>53000</v>
       </c>
       <c r="H10" t="n">
-        <v>404.9347366248775</v>
+        <v>530</v>
       </c>
       <c r="I10" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100YN6B.zip</t>
+          <t>S100Z1FS.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-06-24_01_2026-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-07-01_02_2026-09-14.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2432</v>
+        <v>2001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2829400</v>
+        <v>5159600</v>
       </c>
       <c r="G11" t="n">
-        <v>7218042000</v>
+        <v>13978038000</v>
       </c>
       <c r="H11" t="n">
-        <v>2551.08574256026</v>
+        <v>2709.132103263819</v>
       </c>
       <c r="I11" t="n">
-        <v>2.32</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100YKJU.zip</t>
+          <t>S100YMTO.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-23_01_2026-06-30.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-25_01_2026-07-02.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -850,220 +850,220 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8698</v>
+        <v>2492</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>12953688</v>
+        <v>13568100</v>
       </c>
       <c r="G12" t="n">
-        <v>6608778000</v>
+        <v>5494195000</v>
       </c>
       <c r="H12" t="n">
-        <v>510.1850530906719</v>
+        <v>404.9347366248775</v>
       </c>
       <c r="I12" t="n">
-        <v>5.149999999999999</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100YG6L.zip</t>
+          <t>S100YN6B.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_01_2026-06-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-06-24_01_2026-07-01.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2001</v>
+        <v>2432</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4316500</v>
+        <v>2829400</v>
       </c>
       <c r="G13" t="n">
-        <v>11637840000</v>
+        <v>7218042000</v>
       </c>
       <c r="H13" t="n">
-        <v>2696.128808062088</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="I13" t="n">
-        <v>5.09</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100Z17N.zip</t>
+          <t>S100YKJU.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-23_01_2026-06-30.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2001</v>
+        <v>8698</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4316500</v>
+        <v>12953688</v>
       </c>
       <c r="G14" t="n">
-        <v>11637840000</v>
+        <v>6608778000</v>
       </c>
       <c r="H14" t="n">
-        <v>2696.128808062088</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="I14" t="n">
-        <v>5.09</v>
+        <v>5.149999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100YG8O.zip</t>
+          <t>S100YG6L.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-06-16_01_2026-06-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_01_2026-06-25.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9854</v>
+        <v>2001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1054100</v>
+        <v>4316500</v>
       </c>
       <c r="G15" t="n">
-        <v>260332000</v>
+        <v>11637840000</v>
       </c>
       <c r="H15" t="n">
-        <v>246.9708756284982</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100YD9N.zip</t>
+          <t>S100Z17N.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-15_01_2026-06-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4088</v>
+        <v>2001</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>13900548</v>
+        <v>4316500</v>
       </c>
       <c r="G16" t="n">
-        <v>31441383000</v>
+        <v>11637840000</v>
       </c>
       <c r="H16" t="n">
-        <v>2261.880826568852</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="I16" t="n">
-        <v>6.05</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100YFL5.zip</t>
+          <t>S100YG8O.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-06-12_01_2026-06-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-06-16_01_2026-06-23.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3086</v>
+        <v>9854</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13792100</v>
+        <v>1054100</v>
       </c>
       <c r="G17" t="n">
-        <v>25198319000</v>
+        <v>260332000</v>
       </c>
       <c r="H17" t="n">
-        <v>1827.011042553346</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100YB6N.zip</t>
+          <t>S100YD9N.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-10_01_2026-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-15_01_2026-06-22.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1072,72 +1072,72 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7122</v>
+        <v>4088</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>480500</v>
+        <v>13900548</v>
       </c>
       <c r="G18" t="n">
-        <v>1030622000</v>
+        <v>31441383000</v>
       </c>
       <c r="H18" t="n">
-        <v>2144.894901144641</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="I18" t="n">
-        <v>6.959999999999999</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100YIZN.zip</t>
+          <t>S100YFL5.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-09_02_2026-06-25.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-06-12_01_2026-06-19.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6890</v>
+        <v>3086</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4020953</v>
+        <v>13792100</v>
       </c>
       <c r="G19" t="n">
-        <v>16234608000</v>
+        <v>25198319000</v>
       </c>
       <c r="H19" t="n">
-        <v>4037.502552255647</v>
+        <v>1827.011042553346</v>
       </c>
       <c r="I19" t="n">
-        <v>7.630000000000001</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100Y85I.zip</t>
+          <t>S100YB6N.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-01_01_2026-06-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-10_01_2026-06-17.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1146,35 +1146,35 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3905</v>
+        <v>7122</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3115000</v>
+        <v>480500</v>
       </c>
       <c r="G20" t="n">
-        <v>16021306000</v>
+        <v>1030622000</v>
       </c>
       <c r="H20" t="n">
-        <v>5143.276404494382</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="I20" t="n">
-        <v>9.76</v>
+        <v>6.959999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100Y79Q.zip</t>
+          <t>S100YIZN.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-09_02_2026-06-25.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1183,146 +1183,146 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2871</v>
+        <v>6890</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>12872200</v>
+        <v>4020953</v>
       </c>
       <c r="G21" t="n">
-        <v>23365599000</v>
+        <v>16234608000</v>
       </c>
       <c r="H21" t="n">
-        <v>1815.198567455447</v>
+        <v>4037.502552255647</v>
       </c>
       <c r="I21" t="n">
-        <v>5.01</v>
+        <v>7.630000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100Y5E5.zip</t>
+          <t>S100Y85I.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-01_01_2026-06-02.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9274</v>
+        <v>3905</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>3115000</v>
       </c>
       <c r="G22" t="n">
-        <v>73000</v>
+        <v>16021306000</v>
       </c>
       <c r="H22" t="n">
-        <v>730</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100Y3QD.zip</t>
+          <t>S100Y79Q.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4088</v>
+        <v>2871</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>12872200</v>
       </c>
       <c r="G23" t="n">
-        <v>197000</v>
+        <v>23365599000</v>
       </c>
       <c r="H23" t="n">
-        <v>1970</v>
+        <v>1815.198567455447</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100Y2BG.zip</t>
+          <t>S100Y5E5.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7244</v>
+        <v>9274</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5197900</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>2856142000</v>
+        <v>73000</v>
       </c>
       <c r="H24" t="n">
-        <v>549.4799823005444</v>
+        <v>730</v>
       </c>
       <c r="I24" t="n">
-        <v>5.390000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100Y2OE.zip</t>
+          <t>S100Y3QD.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3863</v>
+        <v>4088</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>125000</v>
+        <v>197000</v>
       </c>
       <c r="H25" t="n">
-        <v>1250</v>
+        <v>1970</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100Y2B5.zip</t>
+          <t>S100Y2BG.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7004</v>
+        <v>7244</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1376,64 +1376,64 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9267600</v>
+        <v>5197900</v>
       </c>
       <c r="G26" t="n">
-        <v>9449965000</v>
+        <v>2856142000</v>
       </c>
       <c r="H26" t="n">
-        <v>1019.677694332945</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="I26" t="n">
-        <v>5.44</v>
+        <v>5.390000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100Y25J.zip</t>
+          <t>S100Y2OE.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7242</v>
+        <v>3863</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2841100</v>
+        <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>8024171000</v>
+        <v>125000</v>
       </c>
       <c r="H27" t="n">
-        <v>2824.318397803668</v>
+        <v>1250</v>
       </c>
       <c r="I27" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100Y1ML.zip</t>
+          <t>S100Y2B5.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1442,35 +1442,35 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3774</v>
+        <v>7004</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>13723994</v>
+        <v>9267600</v>
       </c>
       <c r="G28" t="n">
-        <v>36441482000</v>
+        <v>9449965000</v>
       </c>
       <c r="H28" t="n">
-        <v>2655.311711736394</v>
+        <v>1019.677694332945</v>
       </c>
       <c r="I28" t="n">
-        <v>7.48</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100Y12P.zip</t>
+          <t>S100Y25J.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1479,72 +1479,72 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4071</v>
+        <v>7242</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3400107</v>
+        <v>2841100</v>
       </c>
       <c r="G29" t="n">
-        <v>7823559000</v>
+        <v>8024171000</v>
       </c>
       <c r="H29" t="n">
-        <v>2300.974351689521</v>
+        <v>2824.318397803668</v>
       </c>
       <c r="I29" t="n">
-        <v>8.02</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100Y15W.zip</t>
+          <t>S100Y1ML.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9147</v>
+        <v>3774</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>12252200</v>
+        <v>13723994</v>
       </c>
       <c r="G30" t="n">
-        <v>40939867000</v>
+        <v>36441482000</v>
       </c>
       <c r="H30" t="n">
-        <v>3341.42986565678</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="I30" t="n">
-        <v>5.04</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100XXO7.zip</t>
+          <t>S100Y12P.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1553,72 +1553,72 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4626</v>
+        <v>4071</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>17384460</v>
+        <v>3400107</v>
       </c>
       <c r="G31" t="n">
-        <v>38239610000</v>
+        <v>7823559000</v>
       </c>
       <c r="H31" t="n">
-        <v>2199.643244598912</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="I31" t="n">
-        <v>14.88</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100XW5T.zip</t>
+          <t>S100Y15W.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4613</v>
+        <v>9147</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8982300</v>
+        <v>12252200</v>
       </c>
       <c r="G32" t="n">
-        <v>21391558000</v>
+        <v>40939867000</v>
       </c>
       <c r="H32" t="n">
-        <v>2381.523440544182</v>
+        <v>3341.42986565678</v>
       </c>
       <c r="I32" t="n">
-        <v>5.050000000000001</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XXO7.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1627,72 +1627,72 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5423</v>
+        <v>4626</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6884398</v>
+        <v>17384460</v>
       </c>
       <c r="G33" t="n">
-        <v>11052572000</v>
+        <v>38239610000</v>
       </c>
       <c r="H33" t="n">
-        <v>1605.452212379354</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="I33" t="n">
-        <v>6.25</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6952</v>
+        <v>4613</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11964800</v>
+        <v>8982300</v>
       </c>
       <c r="G34" t="n">
-        <v>14335634000</v>
+        <v>21391558000</v>
       </c>
       <c r="H34" t="n">
-        <v>1198.150742177053</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I34" t="n">
-        <v>5.029999999999999</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1701,220 +1701,220 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9468</v>
+        <v>5423</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>13197300</v>
+        <v>6884398</v>
       </c>
       <c r="G35" t="n">
-        <v>39531520000</v>
+        <v>11052572000</v>
       </c>
       <c r="H35" t="n">
-        <v>2995.424821743842</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I35" t="n">
-        <v>8.859999999999999</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4676</v>
+        <v>6952</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2662900</v>
+        <v>11964800</v>
       </c>
       <c r="G36" t="n">
-        <v>8365298000</v>
+        <v>14335634000</v>
       </c>
       <c r="H36" t="n">
-        <v>3141.424011416125</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I36" t="n">
-        <v>1.57</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3132</v>
+        <v>9468</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>14653542</v>
+        <v>13197300</v>
       </c>
       <c r="G37" t="n">
-        <v>23038030000</v>
+        <v>39531520000</v>
       </c>
       <c r="H37" t="n">
-        <v>1572.181660925393</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I37" t="n">
-        <v>8.18</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6594</v>
+        <v>4676</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>80322406</v>
+        <v>2662900</v>
       </c>
       <c r="G38" t="n">
-        <v>178330543000</v>
+        <v>8365298000</v>
       </c>
       <c r="H38" t="n">
-        <v>2220.184278344451</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I38" t="n">
-        <v>6.74</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1721</v>
+        <v>3132</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>7462000</v>
+        <v>14653542</v>
       </c>
       <c r="G39" t="n">
-        <v>27875864000</v>
+        <v>23038030000</v>
       </c>
       <c r="H39" t="n">
-        <v>3735.709461270437</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I39" t="n">
-        <v>5.609999999999999</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6675</v>
+        <v>6594</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>314400</v>
+        <v>80322406</v>
       </c>
       <c r="G40" t="n">
-        <v>1717778000</v>
+        <v>178330543000</v>
       </c>
       <c r="H40" t="n">
-        <v>5463.67048346056</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I40" t="n">
-        <v>5.029999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1923,72 +1923,72 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3549</v>
+        <v>1721</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>13408159</v>
+        <v>7462000</v>
       </c>
       <c r="G41" t="n">
-        <v>40855887000</v>
+        <v>27875864000</v>
       </c>
       <c r="H41" t="n">
-        <v>3047.091476167608</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I41" t="n">
-        <v>14.02</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7745</v>
+        <v>6675</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1458700</v>
+        <v>314400</v>
       </c>
       <c r="G42" t="n">
-        <v>3040190000</v>
+        <v>1717778000</v>
       </c>
       <c r="H42" t="n">
-        <v>2084.177692465894</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I42" t="n">
-        <v>5.24</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1997,35 +1997,35 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9072</v>
+        <v>3549</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>8985002</v>
+        <v>13408159</v>
       </c>
       <c r="G43" t="n">
-        <v>24970571000</v>
+        <v>40855887000</v>
       </c>
       <c r="H43" t="n">
-        <v>2779.139169918938</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I43" t="n">
-        <v>7.1</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2034,257 +2034,257 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4189</v>
+        <v>7745</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2040400</v>
+        <v>1458700</v>
       </c>
       <c r="G44" t="n">
-        <v>5203426000</v>
+        <v>3040190000</v>
       </c>
       <c r="H44" t="n">
-        <v>2550.198980592041</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I44" t="n">
-        <v>5.489999999999999</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6794</v>
+        <v>9072</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1252600</v>
+        <v>8985002</v>
       </c>
       <c r="G45" t="n">
-        <v>3359425000</v>
+        <v>24970571000</v>
       </c>
       <c r="H45" t="n">
-        <v>2681.96152003832</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I45" t="n">
-        <v>5.01</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2972</v>
+        <v>4189</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2040400</v>
       </c>
       <c r="G46" t="n">
-        <v>125000</v>
+        <v>5203426000</v>
       </c>
       <c r="H46" t="n">
-        <v>125000</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G47" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H47" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I47" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3106</v>
+        <v>2972</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>853156</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>4849339000</v>
+        <v>125000</v>
       </c>
       <c r="H48" t="n">
-        <v>5684.0003469471</v>
+        <v>125000</v>
       </c>
       <c r="I48" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8233</v>
+        <v>2175</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>261400</v>
+        <v>6792424</v>
       </c>
       <c r="G49" t="n">
-        <v>287906000</v>
+        <v>10040067000</v>
       </c>
       <c r="H49" t="n">
-        <v>1101.400153022188</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I49" t="n">
-        <v>0.08</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2371</v>
+        <v>3106</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>10372003</v>
+        <v>853156</v>
       </c>
       <c r="G50" t="n">
-        <v>24045569000</v>
+        <v>4849339000</v>
       </c>
       <c r="H50" t="n">
-        <v>2318.314890576102</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I50" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2293,479 +2293,479 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2432</v>
+        <v>8233</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>261400</v>
       </c>
       <c r="G51" t="n">
-        <v>226000</v>
+        <v>287906000</v>
       </c>
       <c r="H51" t="n">
-        <v>2260</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G52" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H52" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I52" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8570</v>
+        <v>2432</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>11014402</v>
+        <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>14194389000</v>
+        <v>226000</v>
       </c>
       <c r="H53" t="n">
-        <v>1288.711724885291</v>
+        <v>2260</v>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6890</v>
+        <v>7378</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4038389</v>
+        <v>500400</v>
       </c>
       <c r="G54" t="n">
-        <v>15954609000</v>
+        <v>698873000</v>
       </c>
       <c r="H54" t="n">
-        <v>3950.736048458928</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I54" t="n">
-        <v>8.5</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9742</v>
+        <v>8570</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1048500</v>
+        <v>11014402</v>
       </c>
       <c r="G55" t="n">
-        <v>1970276000</v>
+        <v>14194389000</v>
       </c>
       <c r="H55" t="n">
-        <v>1879.137815927515</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I55" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G56" t="n">
-        <v>268179335000</v>
+        <v>15954609000</v>
       </c>
       <c r="H56" t="n">
-        <v>16430.4430802409</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I56" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G57" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H57" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I57" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G58" t="n">
-        <v>1831405000</v>
+        <v>268179335000</v>
       </c>
       <c r="H58" t="n">
-        <v>3321.975331035734</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I58" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G59" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H59" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I59" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1882</v>
+        <v>8011</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1998200</v>
+        <v>551300</v>
       </c>
       <c r="G60" t="n">
-        <v>2358382000</v>
+        <v>1831405000</v>
       </c>
       <c r="H60" t="n">
-        <v>1180.253227905114</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I60" t="n">
-        <v>3.97</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4549</v>
+        <v>6856</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2546351</v>
+        <v>4180400</v>
       </c>
       <c r="G61" t="n">
-        <v>4958319000</v>
+        <v>49662804000</v>
       </c>
       <c r="H61" t="n">
-        <v>1947.225264702313</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I61" t="n">
-        <v>7.37</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7940</v>
+        <v>1882</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>1998200</v>
       </c>
       <c r="G62" t="n">
-        <v>101000</v>
+        <v>2358382000</v>
       </c>
       <c r="H62" t="n">
-        <v>1010</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1882</v>
+        <v>4549</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2528200</v>
+        <v>2546351</v>
       </c>
       <c r="G63" t="n">
-        <v>2984068000</v>
+        <v>4958319000</v>
       </c>
       <c r="H63" t="n">
-        <v>1180.31326635551</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I63" t="n">
-        <v>5.02</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H64" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -2797,49 +2797,49 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2432</v>
+        <v>1882</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G65" t="n">
-        <v>226000</v>
+        <v>2984068000</v>
       </c>
       <c r="H65" t="n">
-        <v>2260</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H66" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -2871,12 +2871,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H67" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -2908,12 +2908,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2922,294 +2922,294 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H68" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2229</v>
+        <v>4917</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>23390757000</v>
+        <v>204000</v>
       </c>
       <c r="H69" t="n">
-        <v>2919.137515755844</v>
+        <v>2040</v>
       </c>
       <c r="I69" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1882</v>
+        <v>8233</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4275700</v>
+        <v>261400</v>
       </c>
       <c r="G70" t="n">
-        <v>5047062000</v>
+        <v>287906000</v>
       </c>
       <c r="H70" t="n">
-        <v>1180.406015389293</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I70" t="n">
-        <v>8.48</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G71" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H71" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I71" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G72" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H72" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I72" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G73" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H73" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I73" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G74" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H74" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I74" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1297500</v>
+        <v>4783700</v>
       </c>
       <c r="G75" t="n">
-        <v>4476090000</v>
+        <v>5646776000</v>
       </c>
       <c r="H75" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I75" t="n">
-        <v>5.23</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3222,68 +3222,68 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>5865200</v>
+        <v>5295000</v>
       </c>
       <c r="G76" t="n">
-        <v>6923530000</v>
+        <v>6250386000</v>
       </c>
       <c r="H76" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I76" t="n">
-        <v>11.64</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G77" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H77" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I77" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3296,31 +3296,31 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>6942800</v>
+        <v>5865200</v>
       </c>
       <c r="G78" t="n">
-        <v>8195680000</v>
+        <v>6923530000</v>
       </c>
       <c r="H78" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I78" t="n">
-        <v>13.78</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3333,31 +3333,31 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>7455900</v>
+        <v>6431400</v>
       </c>
       <c r="G79" t="n">
-        <v>8801415000</v>
+        <v>7591952000</v>
       </c>
       <c r="H79" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I79" t="n">
-        <v>14.79</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3366,403 +3366,405 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G80" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H80" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G81" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H81" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I81" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G82" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H82" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G83" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H83" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I83" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G84" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H84" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I84" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G85" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H85" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G86" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H86" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G87" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H87" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I87" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G88" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H88" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I88" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G90" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H90" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I90" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3771,368 +3773,366 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H91" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G92" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H92" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I92" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G93" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H93" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I93" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4619</v>
+        <v>9302</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G94" t="n">
-        <v>119000</v>
+        <v>5671170000</v>
       </c>
       <c r="H94" t="n">
-        <v>1190</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G95" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H95" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G96" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H96" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I96" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G97" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H97" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I97" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G98" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H98" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G99" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H99" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I99" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G100" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H100" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I100" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4141,257 +4141,257 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G101" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H101" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G102" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H102" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I102" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G103" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H103" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I103" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G104" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H104" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I104" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G105" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H105" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I105" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G106" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H106" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I106" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G107" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H107" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4400,442 +4400,442 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G108" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H108" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I108" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G109" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H109" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G110" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H110" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H111" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I111" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H112" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I112" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G113" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H113" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I113" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G114" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H114" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I114" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G115" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H115" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G116" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H116" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I116" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G117" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H117" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I117" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G118" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H118" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I118" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G119" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H119" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I119" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4844,109 +4844,109 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G120" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H120" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I120" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G121" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H121" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I121" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G122" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H122" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I122" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4955,109 +4955,109 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G123" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H123" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I123" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G124" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H124" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G125" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H125" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I125" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5066,21 +5066,21 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F126" t="n">
         <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H126" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -5089,456 +5089,456 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G127" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H127" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I127" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G128" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H128" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I128" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G129" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H129" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I129" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2327</v>
+        <v>3569</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>9154320</v>
+        <v>4271704</v>
       </c>
       <c r="G130" t="n">
-        <v>23450671000</v>
+        <v>5808044000</v>
       </c>
       <c r="H130" t="n">
-        <v>2561.705402476645</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I130" t="n">
-        <v>5</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G131" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H131" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G132" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H132" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G133" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H133" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I133" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G134" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H134" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I134" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G135" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H135" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I135" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G136" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H136" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G137" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H137" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I137" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G138" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H138" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I138" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5547,44 +5547,44 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G139" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H139" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I139" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5592,249 +5592,249 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G140" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H140" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G141" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H141" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I141" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G142" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H142" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I142" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G143" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H143" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I143" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G144" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H144" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I144" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G145" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H145" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I145" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G146" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H146" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I146" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5843,775 +5843,775 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G147" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H147" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I147" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G148" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H148" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I148" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G149" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H149" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I149" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G150" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H150" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I150" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G151" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H151" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G152" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H152" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I152" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G153" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H153" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I153" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G154" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H154" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I154" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G155" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H155" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G156" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H156" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I156" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G157" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H157" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I157" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G158" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H158" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G159" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H159" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I159" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G160" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H160" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I160" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G161" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H161" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G162" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H162" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I162" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G163" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H163" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I163" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G164" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H164" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I164" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G165" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H165" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G166" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H166" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I166" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G167" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H167" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I167" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6620,35 +6620,35 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G168" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H168" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I168" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6657,72 +6657,72 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G169" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H169" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I169" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G170" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H170" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I170" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6731,427 +6731,464 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G171" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H171" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I171" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G172" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H172" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I172" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G173" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H173" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I173" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G174" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H174" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I174" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G175" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H175" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I175" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G176" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H176" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G177" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H177" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I177" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G178" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H178" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I178" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G179" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H179" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I179" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G180" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H180" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I180" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2812</v>
+        <v>5186</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
+        <v>1536900</v>
+      </c>
+      <c r="G181" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H181" t="n">
+        <v>3096.322467304314</v>
+      </c>
       <c r="I181" t="n">
-        <v>9.779999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S100RU33.zip</t>
+          <t>S100RX5R.zip</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-09-08_01_2023-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>5451</v>
+        <v>8303</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1752800</v>
+        <v>20000000</v>
       </c>
       <c r="G182" t="n">
-        <v>5669831000</v>
+        <v>56014500000</v>
       </c>
       <c r="H182" t="n">
-        <v>3234.727863989046</v>
+        <v>2800.725</v>
       </c>
       <c r="I182" t="n">
-        <v>5.029999999999999</v>
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>S100RVIC.zip</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>2812</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="n">
+        <v>9.779999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I183"/>
+  <dimension ref="A1:I187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,86 +503,86 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S100YXOD.zip</t>
+          <t>S100Z28H.zip</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-08-18_01_2026-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-08-19_01_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2433</v>
+        <v>1721</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18451800</v>
+        <v>8681700</v>
       </c>
       <c r="G3" t="n">
-        <v>20504594000</v>
+        <v>34320897000</v>
       </c>
       <c r="H3" t="n">
-        <v>1111.251693601708</v>
+        <v>3953.24613842911</v>
       </c>
       <c r="I3" t="n">
-        <v>5.07</v>
+        <v>7.359999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S100YW1L.zip</t>
+          <t>S100YXOD.zip</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-08-07_01_2026-08-17.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-08-18_01_2026-08-20.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4812</v>
+        <v>2433</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9786228</v>
+        <v>18451800</v>
       </c>
       <c r="G4" t="n">
-        <v>18695874000</v>
+        <v>20504594000</v>
       </c>
       <c r="H4" t="n">
-        <v>1910.426979628923</v>
+        <v>1111.251693601708</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S100YUTR.zip</t>
+          <t>S100YW1L.zip</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-08-04_01_2026-08-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-08-07_01_2026-08-17.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,35 +591,35 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4043</v>
+        <v>4812</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3612700</v>
+        <v>9786228</v>
       </c>
       <c r="G5" t="n">
-        <v>10346665000</v>
+        <v>18695874000</v>
       </c>
       <c r="H5" t="n">
-        <v>2863.970160821546</v>
+        <v>1910.426979628923</v>
       </c>
       <c r="I5" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S100YVP6.zip</t>
+          <t>S100YUTR.zip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-08-03_01_2026-08-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-08-04_01_2026-08-12.csv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -628,118 +628,118 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2413</v>
+        <v>4043</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>34160200</v>
+        <v>3612700</v>
       </c>
       <c r="G6" t="n">
-        <v>55974415000</v>
+        <v>10346665000</v>
       </c>
       <c r="H6" t="n">
-        <v>1638.585693292194</v>
+        <v>2863.970160821546</v>
       </c>
       <c r="I6" t="n">
-        <v>5.029999999999999</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S100Z1H2.zip</t>
+          <t>S100YVP6.zip</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-07-17_02_2026-09-14.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-08-03_01_2026-08-10.csv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2001</v>
+        <v>2413</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6010300</v>
+        <v>34160200</v>
       </c>
       <c r="G7" t="n">
-        <v>16368563000</v>
+        <v>55974415000</v>
       </c>
       <c r="H7" t="n">
-        <v>2723.418631349517</v>
+        <v>1638.585693292194</v>
       </c>
       <c r="I7" t="n">
-        <v>7.090000000000001</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S100YR5Q.zip</t>
+          <t>S100Z1H2.zip</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-07-17_02_2026-09-14.csv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4025</v>
+        <v>2001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>473300</v>
+        <v>6010300</v>
       </c>
       <c r="G8" t="n">
-        <v>2222596000</v>
+        <v>16368563000</v>
       </c>
       <c r="H8" t="n">
-        <v>4695.956053243186</v>
+        <v>2723.418631349517</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>7.090000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S100YR7M.zip</t>
+          <t>S100YR5Q.zip</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3864</v>
+        <v>4025</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -747,27 +747,27 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>473300</v>
       </c>
       <c r="G9" t="n">
-        <v>81000</v>
+        <v>2222596000</v>
       </c>
       <c r="H9" t="n">
-        <v>810</v>
+        <v>4695.956053243186</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100YR7O.zip</t>
+          <t>S100YR7M.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9831</v>
+        <v>3864</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>53000</v>
+        <v>81000</v>
       </c>
       <c r="H10" t="n">
-        <v>530</v>
+        <v>810</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -799,197 +799,197 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100Z1FS.zip</t>
+          <t>S100YR7O.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-07-01_02_2026-09-14.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2001</v>
+        <v>9831</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5159600</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>13978038000</v>
+        <v>53000</v>
       </c>
       <c r="H11" t="n">
-        <v>2709.132103263819</v>
+        <v>530</v>
       </c>
       <c r="I11" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S100YMTO.zip</t>
+          <t>S100Z1FS.zip</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-25_01_2026-07-02.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-07-01_02_2026-09-14.csv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2492</v>
+        <v>2001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13568100</v>
+        <v>5159600</v>
       </c>
       <c r="G12" t="n">
-        <v>5494195000</v>
+        <v>13978038000</v>
       </c>
       <c r="H12" t="n">
-        <v>404.9347366248775</v>
+        <v>2709.132103263819</v>
       </c>
       <c r="I12" t="n">
-        <v>5.07</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S100YN6B.zip</t>
+          <t>S100YMTO.zip</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-06-24_01_2026-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-25_01_2026-07-02.csv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2432</v>
+        <v>2492</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2829400</v>
+        <v>13568100</v>
       </c>
       <c r="G13" t="n">
-        <v>7218042000</v>
+        <v>5494195000</v>
       </c>
       <c r="H13" t="n">
-        <v>2551.08574256026</v>
+        <v>404.9347366248775</v>
       </c>
       <c r="I13" t="n">
-        <v>2.32</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S100YKJU.zip</t>
+          <t>S100YN6B.zip</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-23_01_2026-06-30.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-06-24_01_2026-07-01.csv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8698</v>
+        <v>2432</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>12953688</v>
+        <v>2829400</v>
       </c>
       <c r="G14" t="n">
-        <v>6608778000</v>
+        <v>7218042000</v>
       </c>
       <c r="H14" t="n">
-        <v>510.1850530906719</v>
+        <v>2551.08574256026</v>
       </c>
       <c r="I14" t="n">
-        <v>5.149999999999999</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S100YG6L.zip</t>
+          <t>S100YKJU.zip</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_01_2026-06-25.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-23_01_2026-06-30.csv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2001</v>
+        <v>8698</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4316500</v>
+        <v>12953688</v>
       </c>
       <c r="G15" t="n">
-        <v>11637840000</v>
+        <v>6608778000</v>
       </c>
       <c r="H15" t="n">
-        <v>2696.128808062088</v>
+        <v>510.1850530906719</v>
       </c>
       <c r="I15" t="n">
-        <v>5.09</v>
+        <v>5.149999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S100Z17N.zip</t>
+          <t>S100YG6L.zip</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_01_2026-06-25.csv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1021,160 +1021,160 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S100YG8O.zip</t>
+          <t>S100Z17N.zip</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-06-16_01_2026-06-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-06-18_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9854</v>
+        <v>2001</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1054100</v>
+        <v>4316500</v>
       </c>
       <c r="G17" t="n">
-        <v>260332000</v>
+        <v>11637840000</v>
       </c>
       <c r="H17" t="n">
-        <v>246.9708756284982</v>
+        <v>2696.128808062088</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S100YD9N.zip</t>
+          <t>S100YG8O.zip</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-15_01_2026-06-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-06-16_01_2026-06-23.csv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4088</v>
+        <v>9854</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13900548</v>
+        <v>1054100</v>
       </c>
       <c r="G18" t="n">
-        <v>31441383000</v>
+        <v>260332000</v>
       </c>
       <c r="H18" t="n">
-        <v>2261.880826568852</v>
+        <v>246.9708756284982</v>
       </c>
       <c r="I18" t="n">
-        <v>6.05</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S100YFL5.zip</t>
+          <t>S100YD9N.zip</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-06-12_01_2026-06-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-15_01_2026-06-22.csv</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3086</v>
+        <v>4088</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13792100</v>
+        <v>13900548</v>
       </c>
       <c r="G19" t="n">
-        <v>25198319000</v>
+        <v>31441383000</v>
       </c>
       <c r="H19" t="n">
-        <v>1827.011042553346</v>
+        <v>2261.880826568852</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S100YB6N.zip</t>
+          <t>S100YFL5.zip</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-10_01_2026-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-06-12_01_2026-06-19.csv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7122</v>
+        <v>3086</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>480500</v>
+        <v>13792100</v>
       </c>
       <c r="G20" t="n">
-        <v>1030622000</v>
+        <v>25198319000</v>
       </c>
       <c r="H20" t="n">
-        <v>2144.894901144641</v>
+        <v>1827.011042553346</v>
       </c>
       <c r="I20" t="n">
-        <v>6.959999999999999</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S100YIZN.zip</t>
+          <t>S100YB6N.zip</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-09_02_2026-06-25.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-10_01_2026-06-17.csv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1183,35 +1183,35 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6890</v>
+        <v>7122</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4020953</v>
+        <v>480500</v>
       </c>
       <c r="G21" t="n">
-        <v>16234608000</v>
+        <v>1030622000</v>
       </c>
       <c r="H21" t="n">
-        <v>4037.502552255647</v>
+        <v>2144.894901144641</v>
       </c>
       <c r="I21" t="n">
-        <v>7.630000000000001</v>
+        <v>6.959999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S100Y85I.zip</t>
+          <t>S100YIZN.zip</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-06-01_01_2026-06-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-09_02_2026-06-25.csv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1220,35 +1220,35 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3905</v>
+        <v>6890</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3115000</v>
+        <v>4020953</v>
       </c>
       <c r="G22" t="n">
-        <v>16021306000</v>
+        <v>16234608000</v>
       </c>
       <c r="H22" t="n">
-        <v>5143.276404494382</v>
+        <v>4037.502552255647</v>
       </c>
       <c r="I22" t="n">
-        <v>9.76</v>
+        <v>7.630000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S100Y79Q.zip</t>
+          <t>S100Y85I.zip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-06-01_01_2026-06-02.csv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1257,72 +1257,72 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2871</v>
+        <v>3905</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12872200</v>
+        <v>3115000</v>
       </c>
       <c r="G23" t="n">
-        <v>23365599000</v>
+        <v>16021306000</v>
       </c>
       <c r="H23" t="n">
-        <v>1815.198567455447</v>
+        <v>5143.276404494382</v>
       </c>
       <c r="I23" t="n">
-        <v>5.01</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100Y5E5.zip</t>
+          <t>S100Y79Q.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9274</v>
+        <v>2871</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>12872200</v>
       </c>
       <c r="G24" t="n">
-        <v>73000</v>
+        <v>23365599000</v>
       </c>
       <c r="H24" t="n">
-        <v>730</v>
+        <v>1815.198567455447</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100Y3QD.zip</t>
+          <t>S100Y5E5.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4088</v>
+        <v>9274</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>197000</v>
+        <v>73000</v>
       </c>
       <c r="H25" t="n">
-        <v>1970</v>
+        <v>730</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1354,58 +1354,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100Y2BG.zip</t>
+          <t>S100Y3QD.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7244</v>
+        <v>4088</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5197900</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>2856142000</v>
+        <v>197000</v>
       </c>
       <c r="H26" t="n">
-        <v>549.4799823005444</v>
+        <v>1970</v>
       </c>
       <c r="I26" t="n">
-        <v>5.390000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100Y2OE.zip</t>
+          <t>S100Y2BG.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3863</v>
+        <v>7244</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1413,36 +1413,36 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>5197900</v>
       </c>
       <c r="G27" t="n">
-        <v>125000</v>
+        <v>2856142000</v>
       </c>
       <c r="H27" t="n">
-        <v>1250</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5.390000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100Y2B5.zip</t>
+          <t>S100Y2OE.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7004</v>
+        <v>3863</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1450,27 +1450,27 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9267600</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>9449965000</v>
+        <v>125000</v>
       </c>
       <c r="H28" t="n">
-        <v>1019.677694332945</v>
+        <v>1250</v>
       </c>
       <c r="I28" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100Y25J.zip</t>
+          <t>S100Y2B5.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1479,35 +1479,35 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7242</v>
+        <v>7004</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2841100</v>
+        <v>9267600</v>
       </c>
       <c r="G29" t="n">
-        <v>8024171000</v>
+        <v>9449965000</v>
       </c>
       <c r="H29" t="n">
-        <v>2824.318397803668</v>
+        <v>1019.677694332945</v>
       </c>
       <c r="I29" t="n">
-        <v>5.63</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100Y1ML.zip</t>
+          <t>S100Y25J.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1516,35 +1516,35 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3774</v>
+        <v>7242</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13723994</v>
+        <v>2841100</v>
       </c>
       <c r="G30" t="n">
-        <v>36441482000</v>
+        <v>8024171000</v>
       </c>
       <c r="H30" t="n">
-        <v>2655.311711736394</v>
+        <v>2824.318397803668</v>
       </c>
       <c r="I30" t="n">
-        <v>7.48</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100Y12P.zip</t>
+          <t>S100Y1ML.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1553,192 +1553,192 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4071</v>
+        <v>3774</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3400107</v>
+        <v>13723994</v>
       </c>
       <c r="G31" t="n">
-        <v>7823559000</v>
+        <v>36441482000</v>
       </c>
       <c r="H31" t="n">
-        <v>2300.974351689521</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="I31" t="n">
-        <v>8.02</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100Y15W.zip</t>
+          <t>S100Y12P.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9147</v>
+        <v>4071</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>12252200</v>
+        <v>3400107</v>
       </c>
       <c r="G32" t="n">
-        <v>40939867000</v>
+        <v>7823559000</v>
       </c>
       <c r="H32" t="n">
-        <v>3341.42986565678</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="I32" t="n">
-        <v>5.04</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100XXO7.zip</t>
+          <t>S100Y15W.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4626</v>
+        <v>9147</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>17384460</v>
+        <v>12252200</v>
       </c>
       <c r="G33" t="n">
-        <v>38239610000</v>
+        <v>40939867000</v>
       </c>
       <c r="H33" t="n">
-        <v>2199.643244598912</v>
+        <v>3341.42986565678</v>
       </c>
       <c r="I33" t="n">
-        <v>14.88</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100XW5T.zip</t>
+          <t>S100XXO7.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4613</v>
+        <v>4626</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8982300</v>
+        <v>17384460</v>
       </c>
       <c r="G34" t="n">
-        <v>21391558000</v>
+        <v>38239610000</v>
       </c>
       <c r="H34" t="n">
-        <v>2381.523440544182</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="I34" t="n">
-        <v>5.050000000000001</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5423</v>
+        <v>4613</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6884398</v>
+        <v>8982300</v>
       </c>
       <c r="G35" t="n">
-        <v>11052572000</v>
+        <v>21391558000</v>
       </c>
       <c r="H35" t="n">
-        <v>1605.452212379354</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I35" t="n">
-        <v>6.25</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6952</v>
+        <v>5423</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1746,73 +1746,73 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11964800</v>
+        <v>6884398</v>
       </c>
       <c r="G36" t="n">
-        <v>14335634000</v>
+        <v>11052572000</v>
       </c>
       <c r="H36" t="n">
-        <v>1198.150742177053</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I36" t="n">
-        <v>5.029999999999999</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9468</v>
+        <v>6952</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>13197300</v>
+        <v>11964800</v>
       </c>
       <c r="G37" t="n">
-        <v>39531520000</v>
+        <v>14335634000</v>
       </c>
       <c r="H37" t="n">
-        <v>2995.424821743842</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I37" t="n">
-        <v>8.859999999999999</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4676</v>
+        <v>9468</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1820,101 +1820,101 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2662900</v>
+        <v>13197300</v>
       </c>
       <c r="G38" t="n">
-        <v>8365298000</v>
+        <v>39531520000</v>
       </c>
       <c r="H38" t="n">
-        <v>3141.424011416125</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I38" t="n">
-        <v>1.57</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3132</v>
+        <v>4676</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>14653542</v>
+        <v>2662900</v>
       </c>
       <c r="G39" t="n">
-        <v>23038030000</v>
+        <v>8365298000</v>
       </c>
       <c r="H39" t="n">
-        <v>1572.181660925393</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I39" t="n">
-        <v>8.18</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6594</v>
+        <v>3132</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>80322406</v>
+        <v>14653542</v>
       </c>
       <c r="G40" t="n">
-        <v>178330543000</v>
+        <v>23038030000</v>
       </c>
       <c r="H40" t="n">
-        <v>2220.184278344451</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I40" t="n">
-        <v>6.74</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1923,81 +1923,81 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1721</v>
+        <v>6594</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7462000</v>
+        <v>80322406</v>
       </c>
       <c r="G41" t="n">
-        <v>27875864000</v>
+        <v>178330543000</v>
       </c>
       <c r="H41" t="n">
-        <v>3735.709461270437</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I41" t="n">
-        <v>5.609999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6675</v>
+        <v>1721</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>314400</v>
+        <v>7462000</v>
       </c>
       <c r="G42" t="n">
-        <v>1717778000</v>
+        <v>27875864000</v>
       </c>
       <c r="H42" t="n">
-        <v>5463.67048346056</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I42" t="n">
-        <v>5.029999999999999</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2005,406 +2005,406 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G43" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H43" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I43" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>7745</v>
+        <v>3549</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1458700</v>
+        <v>13408159</v>
       </c>
       <c r="G44" t="n">
-        <v>3040190000</v>
+        <v>40855887000</v>
       </c>
       <c r="H44" t="n">
-        <v>2084.177692465894</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I44" t="n">
-        <v>5.24</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G45" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H45" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I45" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G46" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H46" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I46" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G47" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H47" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I47" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2972</v>
+        <v>6794</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>1252600</v>
       </c>
       <c r="G48" t="n">
-        <v>125000</v>
+        <v>3359425000</v>
       </c>
       <c r="H48" t="n">
-        <v>125000</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2175</v>
+        <v>2972</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6792424</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>10040067000</v>
+        <v>125000</v>
       </c>
       <c r="H49" t="n">
-        <v>1478.127248828989</v>
+        <v>125000</v>
       </c>
       <c r="I49" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G50" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H50" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I50" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8233</v>
+        <v>3106</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>261400</v>
+        <v>853156</v>
       </c>
       <c r="G51" t="n">
-        <v>287906000</v>
+        <v>4849339000</v>
       </c>
       <c r="H51" t="n">
-        <v>1101.400153022188</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I51" t="n">
-        <v>0.08</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2371</v>
+        <v>8233</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>10372003</v>
+        <v>261400</v>
       </c>
       <c r="G52" t="n">
-        <v>24045569000</v>
+        <v>287906000</v>
       </c>
       <c r="H52" t="n">
-        <v>2318.314890576102</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I52" t="n">
-        <v>5.23</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G53" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H53" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7378</v>
+        <v>2432</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2412,64 +2412,64 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>500400</v>
+        <v>100</v>
       </c>
       <c r="G54" t="n">
-        <v>698873000</v>
+        <v>226000</v>
       </c>
       <c r="H54" t="n">
-        <v>1396.628697042366</v>
+        <v>2260</v>
       </c>
       <c r="I54" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G55" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H55" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2478,109 +2478,109 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6890</v>
+        <v>8570</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4038389</v>
+        <v>11014402</v>
       </c>
       <c r="G56" t="n">
-        <v>15954609000</v>
+        <v>14194389000</v>
       </c>
       <c r="H56" t="n">
-        <v>3950.736048458928</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9742</v>
+        <v>6890</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1048500</v>
+        <v>4038389</v>
       </c>
       <c r="G57" t="n">
-        <v>1970276000</v>
+        <v>15954609000</v>
       </c>
       <c r="H57" t="n">
-        <v>1879.137815927515</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I57" t="n">
-        <v>5.02</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G58" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H58" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I58" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2600,10 +2600,10 @@
         <v>16322100</v>
       </c>
       <c r="G59" t="n">
-        <v>268179335457000</v>
+        <v>268179335000</v>
       </c>
       <c r="H59" t="n">
-        <v>16430443.10823975</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I59" t="n">
         <v>5.01</v>
@@ -2612,58 +2612,58 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G60" t="n">
-        <v>1831405000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H60" t="n">
-        <v>3321.975331035734</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I60" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6856</v>
+        <v>8011</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2671,73 +2671,73 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4180400</v>
+        <v>551300</v>
       </c>
       <c r="G61" t="n">
-        <v>49662804000</v>
+        <v>1831405000</v>
       </c>
       <c r="H61" t="n">
-        <v>11879.91675437757</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I61" t="n">
-        <v>9.9</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1882</v>
+        <v>6856</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1998200</v>
+        <v>4180400</v>
       </c>
       <c r="G62" t="n">
-        <v>2358382000</v>
+        <v>49662804000</v>
       </c>
       <c r="H62" t="n">
-        <v>1180.253227905114</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I62" t="n">
-        <v>3.97</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4549</v>
+        <v>1882</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2745,138 +2745,138 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2546351</v>
+        <v>1998200</v>
       </c>
       <c r="G63" t="n">
-        <v>4958319000</v>
+        <v>2358382000</v>
       </c>
       <c r="H63" t="n">
-        <v>1947.225264702313</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I63" t="n">
-        <v>7.37</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7940</v>
+        <v>4549</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G64" t="n">
-        <v>101000</v>
+        <v>4958319000</v>
       </c>
       <c r="H64" t="n">
-        <v>1010</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1882</v>
+        <v>7940</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2528200</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
-        <v>2984068000</v>
+        <v>101000</v>
       </c>
       <c r="H65" t="n">
-        <v>1180.31326635551</v>
+        <v>1010</v>
       </c>
       <c r="I65" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6890</v>
+        <v>1882</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G66" t="n">
-        <v>203000</v>
+        <v>2984068000</v>
       </c>
       <c r="H66" t="n">
-        <v>2030</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2432</v>
+        <v>6890</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>100</v>
       </c>
       <c r="G67" t="n">
-        <v>226000</v>
+        <v>203000</v>
       </c>
       <c r="H67" t="n">
-        <v>2260</v>
+        <v>2030</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -2908,12 +2908,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6875</v>
+        <v>2432</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>487000</v>
+        <v>226000</v>
       </c>
       <c r="H68" t="n">
-        <v>4870</v>
+        <v>2260</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -2945,12 +2945,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4917</v>
+        <v>6875</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>204000</v>
+        <v>487000</v>
       </c>
       <c r="H69" t="n">
-        <v>2040</v>
+        <v>4870</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -2982,12 +2982,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2996,81 +2996,81 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8233</v>
+        <v>4917</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>287906000</v>
+        <v>204000</v>
       </c>
       <c r="H70" t="n">
-        <v>1101.400153022188</v>
+        <v>2040</v>
       </c>
       <c r="I70" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G71" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H71" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I71" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1882</v>
+        <v>2229</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3078,64 +3078,64 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4275700</v>
+        <v>8012900</v>
       </c>
       <c r="G72" t="n">
-        <v>5047062000</v>
+        <v>23390757000</v>
       </c>
       <c r="H72" t="n">
-        <v>1180.406015389293</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I72" t="n">
-        <v>8.48</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G73" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H73" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I73" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3167,49 +3167,49 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G75" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H75" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I75" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3222,105 +3222,105 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>5295000</v>
+        <v>4783700</v>
       </c>
       <c r="G76" t="n">
-        <v>6250386000</v>
+        <v>5646776000</v>
       </c>
       <c r="H76" t="n">
-        <v>1180.431728045326</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I76" t="n">
-        <v>10.51</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1297500</v>
+        <v>5295000</v>
       </c>
       <c r="G77" t="n">
-        <v>4476090000</v>
+        <v>6250386000</v>
       </c>
       <c r="H77" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I77" t="n">
-        <v>5.23</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5865200</v>
+        <v>1297500</v>
       </c>
       <c r="G78" t="n">
-        <v>6923530000</v>
+        <v>4476090000</v>
       </c>
       <c r="H78" t="n">
-        <v>1180.442269658324</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I78" t="n">
-        <v>11.64</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3333,31 +3333,31 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6431400</v>
+        <v>5865200</v>
       </c>
       <c r="G79" t="n">
-        <v>7591952000</v>
+        <v>6923530000</v>
       </c>
       <c r="H79" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I79" t="n">
-        <v>12.76</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3370,31 +3370,31 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>6942800</v>
+        <v>6431400</v>
       </c>
       <c r="G80" t="n">
-        <v>8195680000</v>
+        <v>7591952000</v>
       </c>
       <c r="H80" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I80" t="n">
-        <v>13.78</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z1UE.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3403,35 +3403,35 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1882</v>
+        <v>3765</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>7455900</v>
+        <v>5883300</v>
       </c>
       <c r="G81" t="n">
-        <v>8801415000</v>
+        <v>17576858000</v>
       </c>
       <c r="H81" t="n">
-        <v>1180.463123164206</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="I81" t="n">
-        <v>14.79</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3440,403 +3440,405 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G82" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H82" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G83" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H83" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I83" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G84" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H84" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G85" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H85" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I85" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G86" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H86" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I86" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G87" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H87" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G88" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H88" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G89" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H89" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I89" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G90" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H90" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I90" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G92" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H92" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I92" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3845,280 +3847,278 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H93" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G94" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H94" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I94" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100Z1T1.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>9684</v>
+        <v>3765</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>6704059</v>
+        <v>5187300</v>
       </c>
       <c r="G95" t="n">
-        <v>42054369000</v>
+        <v>15645357000</v>
       </c>
       <c r="H95" t="n">
-        <v>6272.971195510064</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="I95" t="n">
-        <v>5.47</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4619</v>
+        <v>3106</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>100</v>
+        <v>900156</v>
       </c>
       <c r="G96" t="n">
-        <v>119000</v>
+        <v>4095263000</v>
       </c>
       <c r="H96" t="n">
-        <v>1190</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6332</v>
+        <v>9302</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G97" t="n">
-        <v>141000</v>
+        <v>5671170000</v>
       </c>
       <c r="H97" t="n">
-        <v>1410</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100Z1P1.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4849</v>
+        <v>3765</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2946942</v>
+        <v>5186300</v>
       </c>
       <c r="G98" t="n">
-        <v>5148132000</v>
+        <v>15642334000</v>
       </c>
       <c r="H98" t="n">
-        <v>1746.940387696806</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="I98" t="n">
-        <v>5.93</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6927</v>
+        <v>9684</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1142700</v>
+        <v>6704059</v>
       </c>
       <c r="G99" t="n">
-        <v>1023871000</v>
+        <v>42054369000</v>
       </c>
       <c r="H99" t="n">
-        <v>896.0103264198827</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I99" t="n">
-        <v>5.01</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4676</v>
+        <v>4619</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>100</v>
       </c>
       <c r="G100" t="n">
-        <v>242000</v>
+        <v>119000</v>
       </c>
       <c r="H100" t="n">
-        <v>2420</v>
+        <v>1190</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -4127,12 +4127,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4141,183 +4141,183 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1776</v>
+        <v>6332</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>126500</v>
+        <v>100</v>
       </c>
       <c r="G101" t="n">
-        <v>153399000</v>
+        <v>141000</v>
       </c>
       <c r="H101" t="n">
-        <v>1212.640316205534</v>
+        <v>1410</v>
       </c>
       <c r="I101" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3963</v>
+        <v>4849</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1507900</v>
+        <v>2946942</v>
       </c>
       <c r="G102" t="n">
-        <v>635874000</v>
+        <v>5148132000</v>
       </c>
       <c r="H102" t="n">
-        <v>421.6950726175476</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I102" t="n">
-        <v>5.18</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6923</v>
+        <v>6927</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>100</v>
+        <v>1142700</v>
       </c>
       <c r="G103" t="n">
-        <v>256000</v>
+        <v>1023871000</v>
       </c>
       <c r="H103" t="n">
-        <v>2560</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6890</v>
+        <v>4676</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G104" t="n">
-        <v>71610000</v>
+        <v>242000</v>
       </c>
       <c r="H104" t="n">
-        <v>2387</v>
+        <v>2420</v>
       </c>
       <c r="I104" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3132</v>
+        <v>1776</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8970900</v>
+        <v>126500</v>
       </c>
       <c r="G105" t="n">
-        <v>10240398000</v>
+        <v>153399000</v>
       </c>
       <c r="H105" t="n">
-        <v>1141.512891683109</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I105" t="n">
-        <v>5.01</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4326,35 +4326,35 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4512</v>
+        <v>3963</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2137400</v>
+        <v>1507900</v>
       </c>
       <c r="G106" t="n">
-        <v>620573000</v>
+        <v>635874000</v>
       </c>
       <c r="H106" t="n">
-        <v>290.3401328717133</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I106" t="n">
-        <v>6.140000000000001</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4363,146 +4363,146 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9006</v>
+        <v>6923</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>30000</v>
+        <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>34824000</v>
+        <v>256000</v>
       </c>
       <c r="H107" t="n">
-        <v>1160.8</v>
+        <v>2560</v>
       </c>
       <c r="I107" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4626</v>
+        <v>6890</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G108" t="n">
-        <v>16652257000</v>
+        <v>71610000</v>
       </c>
       <c r="H108" t="n">
-        <v>3565.648720929983</v>
+        <v>2387</v>
       </c>
       <c r="I108" t="n">
-        <v>8</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9987</v>
+        <v>3132</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3888200</v>
+        <v>8970900</v>
       </c>
       <c r="G109" t="n">
-        <v>16086019000</v>
+        <v>10240398000</v>
       </c>
       <c r="H109" t="n">
-        <v>4137.137750115735</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>7732</v>
+        <v>4512</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>7995900</v>
+        <v>2137400</v>
       </c>
       <c r="G110" t="n">
-        <v>16678425000</v>
+        <v>620573000</v>
       </c>
       <c r="H110" t="n">
-        <v>2085.872134468915</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I110" t="n">
-        <v>7.380000000000001</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4511,257 +4511,257 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3861</v>
+        <v>9006</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>100</v>
+        <v>30000</v>
       </c>
       <c r="G111" t="n">
-        <v>59000</v>
+        <v>34824000</v>
       </c>
       <c r="H111" t="n">
-        <v>590</v>
+        <v>1160.8</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5715</v>
+        <v>4626</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>100</v>
+        <v>4670190</v>
       </c>
       <c r="G112" t="n">
-        <v>160000</v>
+        <v>16652257000</v>
       </c>
       <c r="H112" t="n">
-        <v>1600</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1882</v>
+        <v>9987</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>8033500</v>
+        <v>3888200</v>
       </c>
       <c r="G113" t="n">
-        <v>9401444000</v>
+        <v>16086019000</v>
       </c>
       <c r="H113" t="n">
-        <v>1170.279952698077</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I113" t="n">
-        <v>15.94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1882</v>
+        <v>7732</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>8007300</v>
+        <v>7995900</v>
       </c>
       <c r="G114" t="n">
-        <v>9367939000</v>
+        <v>16678425000</v>
       </c>
       <c r="H114" t="n">
-        <v>1169.924818603025</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I114" t="n">
-        <v>15.89</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3978</v>
+        <v>3861</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G115" t="n">
-        <v>3425686000</v>
+        <v>59000</v>
       </c>
       <c r="H115" t="n">
-        <v>1184.661617733513</v>
+        <v>590</v>
       </c>
       <c r="I115" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>4452</v>
+        <v>5715</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>24347342</v>
+        <v>100</v>
       </c>
       <c r="G116" t="n">
-        <v>148917027000</v>
+        <v>160000</v>
       </c>
       <c r="H116" t="n">
-        <v>6116.356643776557</v>
+        <v>1600</v>
       </c>
       <c r="I116" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>9257</v>
+        <v>1882</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>100</v>
+        <v>8033500</v>
       </c>
       <c r="G117" t="n">
-        <v>57000</v>
+        <v>9401444000</v>
       </c>
       <c r="H117" t="n">
-        <v>570</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4774,68 +4774,68 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>7914900</v>
+        <v>8007300</v>
       </c>
       <c r="G118" t="n">
-        <v>9250219000</v>
+        <v>9367939000</v>
       </c>
       <c r="H118" t="n">
-        <v>1168.709522546084</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I118" t="n">
-        <v>15.71</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>9531</v>
+        <v>3978</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>19554300</v>
+        <v>2891700</v>
       </c>
       <c r="G119" t="n">
-        <v>64960321000</v>
+        <v>3425686000</v>
       </c>
       <c r="H119" t="n">
-        <v>3322.047887165483</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I119" t="n">
-        <v>5.029999999999999</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4844,627 +4844,627 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4385</v>
+        <v>4452</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>8815360</v>
+        <v>24347342</v>
       </c>
       <c r="G120" t="n">
-        <v>17684138000</v>
+        <v>148917027000</v>
       </c>
       <c r="H120" t="n">
-        <v>2006.059650428343</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I120" t="n">
-        <v>5.37</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>7984</v>
+        <v>9257</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6096500</v>
+        <v>100</v>
       </c>
       <c r="G121" t="n">
-        <v>13153972000</v>
+        <v>57000</v>
       </c>
       <c r="H121" t="n">
-        <v>2157.626835069302</v>
+        <v>570</v>
       </c>
       <c r="I121" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1973</v>
+        <v>1882</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>8973383</v>
+        <v>7914900</v>
       </c>
       <c r="G122" t="n">
-        <v>24947403000</v>
+        <v>9250219000</v>
       </c>
       <c r="H122" t="n">
-        <v>2780.155823060266</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I122" t="n">
-        <v>6.01</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6908</v>
+        <v>9531</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>502000</v>
+        <v>19554300</v>
       </c>
       <c r="G123" t="n">
-        <v>1257178000</v>
+        <v>64960321000</v>
       </c>
       <c r="H123" t="n">
-        <v>2504.338645418327</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I123" t="n">
-        <v>2.04</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3765</v>
+        <v>4385</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>4552900</v>
+        <v>8815360</v>
       </c>
       <c r="G124" t="n">
-        <v>13383536000</v>
+        <v>17684138000</v>
       </c>
       <c r="H124" t="n">
-        <v>2939.562915943684</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I124" t="n">
-        <v>5.47</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5482</v>
+        <v>7984</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>433300</v>
+        <v>6096500</v>
       </c>
       <c r="G125" t="n">
-        <v>1367192000</v>
+        <v>13153972000</v>
       </c>
       <c r="H125" t="n">
-        <v>3155.301177013616</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I125" t="n">
-        <v>2.18</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>8141</v>
+        <v>1973</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>100</v>
+        <v>8973383</v>
       </c>
       <c r="G126" t="n">
-        <v>93000</v>
+        <v>24947403000</v>
       </c>
       <c r="H126" t="n">
-        <v>930</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4272</v>
+        <v>6908</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>26855100</v>
+        <v>502000</v>
       </c>
       <c r="G127" t="n">
-        <v>29860350000</v>
+        <v>1257178000</v>
       </c>
       <c r="H127" t="n">
-        <v>1111.90611839092</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I127" t="n">
-        <v>15.75</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>6145</v>
+        <v>3765</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G128" t="n">
-        <v>171000</v>
+        <v>13383536000</v>
       </c>
       <c r="H128" t="n">
-        <v>1710</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4205</v>
+        <v>5482</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>14426600</v>
+        <v>433300</v>
       </c>
       <c r="G129" t="n">
-        <v>24829312000</v>
+        <v>1367192000</v>
       </c>
       <c r="H129" t="n">
-        <v>1721.078563209627</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I129" t="n">
-        <v>6.29</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>3569</v>
+        <v>8141</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G130" t="n">
-        <v>5808044000</v>
+        <v>93000</v>
       </c>
       <c r="H130" t="n">
-        <v>1359.655069733296</v>
+        <v>930</v>
       </c>
       <c r="I130" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>6516</v>
+        <v>4272</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>679500</v>
+        <v>26855100</v>
       </c>
       <c r="G131" t="n">
-        <v>4792335000</v>
+        <v>29860350000</v>
       </c>
       <c r="H131" t="n">
-        <v>7052.737306843267</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I131" t="n">
-        <v>5.24</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2327</v>
+        <v>6145</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>9154320</v>
+        <v>100</v>
       </c>
       <c r="G132" t="n">
-        <v>23450671000</v>
+        <v>171000</v>
       </c>
       <c r="H132" t="n">
-        <v>2561.705402476645</v>
+        <v>1710</v>
       </c>
       <c r="I132" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3989</v>
+        <v>4205</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1206000</v>
+        <v>14426600</v>
       </c>
       <c r="G133" t="n">
-        <v>787604000</v>
+        <v>24829312000</v>
       </c>
       <c r="H133" t="n">
-        <v>653.0713101160862</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I133" t="n">
-        <v>5.2</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6908</v>
+        <v>3569</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>100</v>
+        <v>4271704</v>
       </c>
       <c r="G134" t="n">
-        <v>288000</v>
+        <v>5808044000</v>
       </c>
       <c r="H134" t="n">
-        <v>2880</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5988</v>
+        <v>6516</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>527300</v>
+        <v>679500</v>
       </c>
       <c r="G135" t="n">
-        <v>1212090000</v>
+        <v>4792335000</v>
       </c>
       <c r="H135" t="n">
-        <v>2298.672482457804</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I135" t="n">
-        <v>1.42</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>3529</v>
+        <v>2327</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>998000</v>
+        <v>9154320</v>
       </c>
       <c r="G136" t="n">
-        <v>667598000</v>
+        <v>23450671000</v>
       </c>
       <c r="H136" t="n">
-        <v>668.9358717434869</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I136" t="n">
-        <v>5.76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5473,35 +5473,35 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>7305</v>
+        <v>3989</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>309800</v>
+        <v>1206000</v>
       </c>
       <c r="G137" t="n">
-        <v>1321438000</v>
+        <v>787604000</v>
       </c>
       <c r="H137" t="n">
-        <v>4265.455132343447</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I137" t="n">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5541</v>
+        <v>6908</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F138" t="n">
         <v>100</v>
       </c>
       <c r="G138" t="n">
-        <v>127000</v>
+        <v>288000</v>
       </c>
       <c r="H138" t="n">
-        <v>1270</v>
+        <v>2880</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
@@ -5533,123 +5533,123 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2168</v>
+        <v>5988</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2094200</v>
+        <v>527300</v>
       </c>
       <c r="G139" t="n">
-        <v>4445105000</v>
+        <v>1212090000</v>
       </c>
       <c r="H139" t="n">
-        <v>2122.579027791042</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I139" t="n">
-        <v>5.02</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4967</v>
+        <v>3529</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4062075</v>
+        <v>998000</v>
       </c>
       <c r="G140" t="n">
-        <v>8729143000</v>
+        <v>667598000</v>
       </c>
       <c r="H140" t="n">
-        <v>2148.936934940886</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>4967</v>
+        <v>7305</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>4062075</v>
+        <v>309800</v>
       </c>
       <c r="G141" t="n">
-        <v>20578848000</v>
+        <v>1321438000</v>
       </c>
       <c r="H141" t="n">
-        <v>5066.092575838703</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>8803</v>
+        <v>5541</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F142" t="n">
         <v>100</v>
       </c>
       <c r="G142" t="n">
-        <v>361000</v>
+        <v>127000</v>
       </c>
       <c r="H142" t="n">
-        <v>3610</v>
+        <v>1270</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -5681,35 +5681,35 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>9882</v>
+        <v>2168</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2505000</v>
+        <v>2094200</v>
       </c>
       <c r="G143" t="n">
-        <v>5292086000</v>
+        <v>4445105000</v>
       </c>
       <c r="H143" t="n">
-        <v>2112.609181636727</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I143" t="n">
         <v>5.02</v>
@@ -5718,160 +5718,160 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8129</v>
+        <v>4967</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>7258230</v>
+        <v>4062075</v>
       </c>
       <c r="G144" t="n">
-        <v>24720910000</v>
+        <v>8729143000</v>
       </c>
       <c r="H144" t="n">
-        <v>3405.914389596362</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I144" t="n">
-        <v>9.460000000000001</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2206</v>
+        <v>4967</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>3462600</v>
+        <v>4062075</v>
       </c>
       <c r="G145" t="n">
-        <v>14385811000</v>
+        <v>20578848000</v>
       </c>
       <c r="H145" t="n">
-        <v>4154.626869982095</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I145" t="n">
-        <v>5.06</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3666</v>
+        <v>8803</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1053200</v>
+        <v>100</v>
       </c>
       <c r="G146" t="n">
-        <v>663809000</v>
+        <v>361000</v>
       </c>
       <c r="H146" t="n">
-        <v>630.278199772123</v>
+        <v>3610</v>
       </c>
       <c r="I146" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4347</v>
+        <v>9882</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>614893</v>
+        <v>2505000</v>
       </c>
       <c r="G147" t="n">
-        <v>940560000</v>
+        <v>5292086000</v>
       </c>
       <c r="H147" t="n">
-        <v>1529.631984751819</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I147" t="n">
-        <v>8.200000000000001</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5884,165 +5884,165 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3886330</v>
+        <v>7258230</v>
       </c>
       <c r="G148" t="n">
-        <v>10549885000</v>
+        <v>24720910000</v>
       </c>
       <c r="H148" t="n">
-        <v>2714.613787300615</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I148" t="n">
-        <v>5.06</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>8929</v>
+        <v>2206</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1260812</v>
+        <v>3462600</v>
       </c>
       <c r="G149" t="n">
-        <v>1699255000</v>
+        <v>14385811000</v>
       </c>
       <c r="H149" t="n">
-        <v>1347.74653160027</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I149" t="n">
-        <v>5.140000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>7278</v>
+        <v>3666</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>115400</v>
+        <v>1053200</v>
       </c>
       <c r="G150" t="n">
-        <v>302115000</v>
+        <v>663809000</v>
       </c>
       <c r="H150" t="n">
-        <v>2617.980935875217</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I150" t="n">
-        <v>0.24</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3591</v>
+        <v>4347</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2846091</v>
+        <v>614893</v>
       </c>
       <c r="G151" t="n">
-        <v>6888596000</v>
+        <v>940560000</v>
       </c>
       <c r="H151" t="n">
-        <v>2420.370957920882</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I151" t="n">
-        <v>5.13</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4042</v>
+        <v>8129</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>16459200</v>
+        <v>3886330</v>
       </c>
       <c r="G152" t="n">
-        <v>33451116000</v>
+        <v>10549885000</v>
       </c>
       <c r="H152" t="n">
-        <v>2032.365850102071</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I152" t="n">
         <v>5.06</v>
@@ -6051,160 +6051,160 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4521</v>
+        <v>8929</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>100</v>
+        <v>1260812</v>
       </c>
       <c r="G153" t="n">
-        <v>353000</v>
+        <v>1699255000</v>
       </c>
       <c r="H153" t="n">
-        <v>3530</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>8923</v>
+        <v>7278</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2445600</v>
+        <v>115400</v>
       </c>
       <c r="G154" t="n">
-        <v>3856031000</v>
+        <v>302115000</v>
       </c>
       <c r="H154" t="n">
-        <v>1576.721867844292</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I154" t="n">
-        <v>5.02</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4347</v>
+        <v>3591</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>400493</v>
+        <v>2846091</v>
       </c>
       <c r="G155" t="n">
-        <v>580713000</v>
+        <v>6888596000</v>
       </c>
       <c r="H155" t="n">
-        <v>1449.995380693296</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I155" t="n">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>9024</v>
+        <v>4042</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>16207437</v>
+        <v>16459200</v>
       </c>
       <c r="G156" t="n">
-        <v>27823532000</v>
+        <v>33451116000</v>
       </c>
       <c r="H156" t="n">
-        <v>1716.713876475349</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I156" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6213,21 +6213,21 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1518</v>
+        <v>4521</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F157" t="n">
         <v>100</v>
       </c>
       <c r="G157" t="n">
-        <v>292000</v>
+        <v>353000</v>
       </c>
       <c r="H157" t="n">
-        <v>2920</v>
+        <v>3530</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -6236,35 +6236,35 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7731</v>
+        <v>8923</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>17639800</v>
+        <v>2445600</v>
       </c>
       <c r="G158" t="n">
-        <v>26675255000</v>
+        <v>3856031000</v>
       </c>
       <c r="H158" t="n">
-        <v>1512.21980974841</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I158" t="n">
         <v>5.02</v>
@@ -6273,234 +6273,234 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4536</v>
+        <v>4347</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>18290500</v>
+        <v>400493</v>
       </c>
       <c r="G159" t="n">
-        <v>24591924000</v>
+        <v>580713000</v>
       </c>
       <c r="H159" t="n">
-        <v>1344.518957928979</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I159" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4185</v>
+        <v>9024</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>100</v>
+        <v>16207437</v>
       </c>
       <c r="G160" t="n">
-        <v>405000</v>
+        <v>27823532000</v>
       </c>
       <c r="H160" t="n">
-        <v>4050</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4549</v>
+        <v>1518</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2006900</v>
+        <v>100</v>
       </c>
       <c r="G161" t="n">
-        <v>3367745000</v>
+        <v>292000</v>
       </c>
       <c r="H161" t="n">
-        <v>1678.083113259255</v>
+        <v>2920</v>
       </c>
       <c r="I161" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>9627</v>
+        <v>7731</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>3401100</v>
+        <v>17639800</v>
       </c>
       <c r="G162" t="n">
-        <v>9648726000</v>
+        <v>26675255000</v>
       </c>
       <c r="H162" t="n">
-        <v>2836.942753814942</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I162" t="n">
-        <v>9.6</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>8304</v>
+        <v>4536</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>100</v>
+        <v>18290500</v>
       </c>
       <c r="G163" t="n">
-        <v>219000</v>
+        <v>24591924000</v>
       </c>
       <c r="H163" t="n">
-        <v>2190</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>3328</v>
+        <v>4185</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>845300</v>
+        <v>100</v>
       </c>
       <c r="G164" t="n">
-        <v>1219326000</v>
+        <v>405000</v>
       </c>
       <c r="H164" t="n">
-        <v>1442.477227019993</v>
+        <v>4050</v>
       </c>
       <c r="I164" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6509,72 +6509,72 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3328</v>
+        <v>4549</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>675500</v>
+        <v>2006900</v>
       </c>
       <c r="G165" t="n">
-        <v>976503000</v>
+        <v>3367745000</v>
       </c>
       <c r="H165" t="n">
-        <v>1445.60029607698</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I165" t="n">
-        <v>5.220000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>8818</v>
+        <v>9627</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2505000</v>
+        <v>3401100</v>
       </c>
       <c r="G166" t="n">
-        <v>3361654000</v>
+        <v>9648726000</v>
       </c>
       <c r="H166" t="n">
-        <v>1341.977644710579</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I166" t="n">
-        <v>5.09</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6583,21 +6583,21 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5541</v>
+        <v>8304</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F167" t="n">
         <v>100</v>
       </c>
       <c r="G167" t="n">
-        <v>117000</v>
+        <v>219000</v>
       </c>
       <c r="H167" t="n">
-        <v>1170</v>
+        <v>2190</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -6606,197 +6606,197 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>7315</v>
+        <v>3328</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>6994900</v>
+        <v>845300</v>
       </c>
       <c r="G168" t="n">
-        <v>5874641000</v>
+        <v>1219326000</v>
       </c>
       <c r="H168" t="n">
-        <v>839.8463166020958</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I168" t="n">
-        <v>14.23</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4837</v>
+        <v>3328</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>5428600</v>
+        <v>675500</v>
       </c>
       <c r="G169" t="n">
-        <v>4378021000</v>
+        <v>976503000</v>
       </c>
       <c r="H169" t="n">
-        <v>806.4733080352208</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I169" t="n">
-        <v>9.74</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4293</v>
+        <v>8818</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>20896886</v>
+        <v>2505000</v>
       </c>
       <c r="G170" t="n">
-        <v>9376038000</v>
+        <v>3361654000</v>
       </c>
       <c r="H170" t="n">
-        <v>448.6811097117532</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I170" t="n">
-        <v>9.9</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4631</v>
+        <v>5541</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>6563759</v>
+        <v>100</v>
       </c>
       <c r="G171" t="n">
-        <v>16844475000</v>
+        <v>117000</v>
       </c>
       <c r="H171" t="n">
-        <v>2566.284807227078</v>
+        <v>1170</v>
       </c>
       <c r="I171" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5449</v>
+        <v>7315</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2114100</v>
+        <v>6994900</v>
       </c>
       <c r="G172" t="n">
-        <v>3695597000</v>
+        <v>5874641000</v>
       </c>
       <c r="H172" t="n">
-        <v>1748.071046781136</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I172" t="n">
-        <v>5</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6805,331 +6805,331 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>6232</v>
+        <v>4837</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1499000</v>
+        <v>5428600</v>
       </c>
       <c r="G173" t="n">
-        <v>1369002000</v>
+        <v>4378021000</v>
       </c>
       <c r="H173" t="n">
-        <v>913.2768512341561</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I173" t="n">
-        <v>10.47</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>6237</v>
+        <v>4293</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1129500</v>
+        <v>20896886</v>
       </c>
       <c r="G174" t="n">
-        <v>1537738000</v>
+        <v>9376038000</v>
       </c>
       <c r="H174" t="n">
-        <v>1361.432492253209</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I174" t="n">
-        <v>5.02</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4987</v>
+        <v>4631</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1543800</v>
+        <v>6563759</v>
       </c>
       <c r="G175" t="n">
-        <v>874286000</v>
+        <v>16844475000</v>
       </c>
       <c r="H175" t="n">
-        <v>566.3207669387226</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I175" t="n">
-        <v>5.779999999999999</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4739</v>
+        <v>5449</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>15400600</v>
+        <v>2114100</v>
       </c>
       <c r="G176" t="n">
-        <v>66216726000</v>
+        <v>3695597000</v>
       </c>
       <c r="H176" t="n">
-        <v>4299.619884939548</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I176" t="n">
-        <v>6.419999999999999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2501</v>
+        <v>6232</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>4010500</v>
+        <v>1499000</v>
       </c>
       <c r="G177" t="n">
-        <v>10817766000</v>
+        <v>1369002000</v>
       </c>
       <c r="H177" t="n">
-        <v>2697.360927565142</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I177" t="n">
-        <v>5.09</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>4023</v>
+        <v>6237</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>100</v>
+        <v>1129500</v>
       </c>
       <c r="G178" t="n">
-        <v>796000</v>
+        <v>1537738000</v>
       </c>
       <c r="H178" t="n">
-        <v>7960</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5844</v>
+        <v>4987</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>4998800</v>
+        <v>1543800</v>
       </c>
       <c r="G179" t="n">
-        <v>24949147000</v>
+        <v>874286000</v>
       </c>
       <c r="H179" t="n">
-        <v>4991.027246539169</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I179" t="n">
-        <v>6.59</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5947</v>
+        <v>4739</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>7446200</v>
+        <v>15400600</v>
       </c>
       <c r="G180" t="n">
-        <v>21182239000</v>
+        <v>66216726000</v>
       </c>
       <c r="H180" t="n">
-        <v>2844.704547285864</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I180" t="n">
-        <v>4.96</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>5186</v>
+        <v>2501</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1536900</v>
+        <v>4010500</v>
       </c>
       <c r="G181" t="n">
-        <v>4758738000</v>
+        <v>10817766000</v>
       </c>
       <c r="H181" t="n">
-        <v>3096.322467304314</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I181" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7138,56 +7138,204 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>8303</v>
+        <v>4023</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>20000000</v>
+        <v>100</v>
       </c>
       <c r="G182" t="n">
-        <v>56014500000</v>
+        <v>796000</v>
       </c>
       <c r="H182" t="n">
-        <v>2800.725</v>
+        <v>7960</v>
       </c>
       <c r="I182" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
+          <t>S100RYJW.zip</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>5844</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>4998800</v>
+      </c>
+      <c r="G183" t="n">
+        <v>24949147000</v>
+      </c>
+      <c r="H183" t="n">
+        <v>4991.027246539169</v>
+      </c>
+      <c r="I183" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>S100RYRP.zip</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>5947</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>7446200</v>
+      </c>
+      <c r="G184" t="n">
+        <v>21182239000</v>
+      </c>
+      <c r="H184" t="n">
+        <v>2844.704547285864</v>
+      </c>
+      <c r="I184" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>S100RY2V.zip</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>5186</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>1536900</v>
+      </c>
+      <c r="G185" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H185" t="n">
+        <v>3096.322467304314</v>
+      </c>
+      <c r="I185" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G186" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I186" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
           <t>S100RVIC.zip</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
-      <c r="D183" t="n">
+      <c r="D187" t="n">
         <v>2812</v>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>2023-09-11</t>
         </is>
       </c>
-      <c r="F183" t="n">
+      <c r="F187" t="n">
         <v>1120000</v>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="n">
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="n">
         <v>9.779999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I187"/>
+  <dimension ref="A1:I190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2057,12 +2057,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100Z1ZH.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2071,405 +2071,405 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7745</v>
+        <v>3765</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1458700</v>
+        <v>6673200</v>
       </c>
       <c r="G45" t="n">
-        <v>3040190000</v>
+        <v>19362129000</v>
       </c>
       <c r="H45" t="n">
-        <v>2084.177692465894</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="I45" t="n">
-        <v>5.24</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G46" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H46" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I46" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G47" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H47" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I47" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G48" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H48" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I48" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100Z1ZF.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2972</v>
+        <v>3765</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>6600700</v>
       </c>
       <c r="G49" t="n">
-        <v>125000</v>
+        <v>19175476000</v>
       </c>
       <c r="H49" t="n">
-        <v>125000</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G50" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H50" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I50" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3106</v>
+        <v>2972</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>853156</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>4849339000</v>
+        <v>125000</v>
       </c>
       <c r="H51" t="n">
-        <v>5684.0003469471</v>
+        <v>125000</v>
       </c>
       <c r="I51" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8233</v>
+        <v>2175</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>261400</v>
+        <v>6792424</v>
       </c>
       <c r="G52" t="n">
-        <v>287906000</v>
+        <v>10040067000</v>
       </c>
       <c r="H52" t="n">
-        <v>1101.400153022188</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I52" t="n">
-        <v>0.08</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100Z1ZC.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2371</v>
+        <v>3765</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>10372003</v>
+        <v>6336400</v>
       </c>
       <c r="G53" t="n">
-        <v>24045569000</v>
+        <v>18726232000</v>
       </c>
       <c r="H53" t="n">
-        <v>2318.314890576102</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="I53" t="n">
-        <v>5.23</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2432</v>
+        <v>3106</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>853156</v>
       </c>
       <c r="G54" t="n">
-        <v>226000</v>
+        <v>4849339000</v>
       </c>
       <c r="H54" t="n">
-        <v>2260</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7378</v>
+        <v>8233</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>500400</v>
+        <v>261400</v>
       </c>
       <c r="G55" t="n">
-        <v>698873000</v>
+        <v>287906000</v>
       </c>
       <c r="H55" t="n">
-        <v>1396.628697042366</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I55" t="n">
-        <v>6.78</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2478,72 +2478,72 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>8570</v>
+        <v>2371</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>11014402</v>
+        <v>10372003</v>
       </c>
       <c r="G56" t="n">
-        <v>14194389000</v>
+        <v>24045569000</v>
       </c>
       <c r="H56" t="n">
-        <v>1288.711724885291</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6890</v>
+        <v>2432</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4038389</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>15954609000</v>
+        <v>226000</v>
       </c>
       <c r="H57" t="n">
-        <v>3950.736048458928</v>
+        <v>2260</v>
       </c>
       <c r="I57" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2552,109 +2552,109 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9742</v>
+        <v>7378</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1048500</v>
+        <v>500400</v>
       </c>
       <c r="G58" t="n">
-        <v>1970276000</v>
+        <v>698873000</v>
       </c>
       <c r="H58" t="n">
-        <v>1879.137815927515</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I58" t="n">
-        <v>5.02</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6201</v>
+        <v>8570</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>16322100</v>
+        <v>11014402</v>
       </c>
       <c r="G59" t="n">
-        <v>268179335000</v>
+        <v>14194389000</v>
       </c>
       <c r="H59" t="n">
-        <v>16430.4430802409</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I59" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G60" t="n">
-        <v>268179335457000</v>
+        <v>15954609000</v>
       </c>
       <c r="H60" t="n">
-        <v>16430443.10823975</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I60" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2663,109 +2663,109 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8011</v>
+        <v>9742</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>551300</v>
+        <v>1048500</v>
       </c>
       <c r="G61" t="n">
-        <v>1831405000</v>
+        <v>1970276000</v>
       </c>
       <c r="H61" t="n">
-        <v>3321.975331035734</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I61" t="n">
-        <v>5.36</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G62" t="n">
-        <v>49662804000</v>
+        <v>268179335000</v>
       </c>
       <c r="H62" t="n">
-        <v>11879.91675437757</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I62" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1882</v>
+        <v>6201</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1998200</v>
+        <v>16322100</v>
       </c>
       <c r="G63" t="n">
-        <v>2358382000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H63" t="n">
-        <v>1180.253227905114</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I63" t="n">
-        <v>3.97</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2774,72 +2774,72 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G64" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H64" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I64" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7940</v>
+        <v>6856</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>4180400</v>
       </c>
       <c r="G65" t="n">
-        <v>101000</v>
+        <v>49662804000</v>
       </c>
       <c r="H65" t="n">
-        <v>1010</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2852,68 +2852,68 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2528200</v>
+        <v>1998200</v>
       </c>
       <c r="G66" t="n">
-        <v>2984068000</v>
+        <v>2358382000</v>
       </c>
       <c r="H66" t="n">
-        <v>1180.31326635551</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I66" t="n">
-        <v>5.02</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6890</v>
+        <v>4549</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>100</v>
+        <v>2546351</v>
       </c>
       <c r="G67" t="n">
-        <v>203000</v>
+        <v>4958319000</v>
       </c>
       <c r="H67" t="n">
-        <v>2030</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2922,21 +2922,21 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2432</v>
+        <v>7940</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>226000</v>
+        <v>101000</v>
       </c>
       <c r="H68" t="n">
-        <v>2260</v>
+        <v>1010</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -2945,49 +2945,49 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6875</v>
+        <v>1882</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G69" t="n">
-        <v>487000</v>
+        <v>2984068000</v>
       </c>
       <c r="H69" t="n">
-        <v>4870</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2996,21 +2996,21 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4917</v>
+        <v>6890</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
       <c r="H70" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -3019,12 +3019,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3033,183 +3033,183 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8233</v>
+        <v>2432</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>287906000</v>
+        <v>226000</v>
       </c>
       <c r="H71" t="n">
-        <v>1101.400153022188</v>
+        <v>2260</v>
       </c>
       <c r="I71" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2229</v>
+        <v>6875</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>23390757000</v>
+        <v>487000</v>
       </c>
       <c r="H72" t="n">
-        <v>2919.137515755844</v>
+        <v>4870</v>
       </c>
       <c r="I72" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1882</v>
+        <v>4917</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4275700</v>
+        <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>5047062000</v>
+        <v>204000</v>
       </c>
       <c r="H73" t="n">
-        <v>1180.406015389293</v>
+        <v>2040</v>
       </c>
       <c r="I73" t="n">
-        <v>8.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5983</v>
+        <v>8233</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>44800</v>
+        <v>261400</v>
       </c>
       <c r="G74" t="n">
-        <v>315399000</v>
+        <v>287906000</v>
       </c>
       <c r="H74" t="n">
-        <v>7040.15625</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I74" t="n">
-        <v>4.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G75" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H75" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I75" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3222,105 +3222,105 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4783700</v>
+        <v>4275700</v>
       </c>
       <c r="G76" t="n">
-        <v>5646776000</v>
+        <v>5047062000</v>
       </c>
       <c r="H76" t="n">
-        <v>1180.420176850555</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I76" t="n">
-        <v>9.49</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G77" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H77" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I77" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6104</v>
+        <v>5983</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1297500</v>
+        <v>44800</v>
       </c>
       <c r="G78" t="n">
-        <v>4476090000</v>
+        <v>315399000</v>
       </c>
       <c r="H78" t="n">
-        <v>3449.780346820809</v>
+        <v>7040.15625</v>
       </c>
       <c r="I78" t="n">
-        <v>5.23</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3333,31 +3333,31 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>5865200</v>
+        <v>4783700</v>
       </c>
       <c r="G79" t="n">
-        <v>6923530000</v>
+        <v>5646776000</v>
       </c>
       <c r="H79" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I79" t="n">
-        <v>11.64</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3370,68 +3370,68 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>6431400</v>
+        <v>5295000</v>
       </c>
       <c r="G80" t="n">
-        <v>7591952000</v>
+        <v>6250386000</v>
       </c>
       <c r="H80" t="n">
-        <v>1180.450912709519</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I80" t="n">
-        <v>12.76</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100Z1UE.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3765</v>
+        <v>6104</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5883300</v>
+        <v>1297500</v>
       </c>
       <c r="G81" t="n">
-        <v>17576858000</v>
+        <v>4476090000</v>
       </c>
       <c r="H81" t="n">
-        <v>2987.584858837727</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I81" t="n">
-        <v>8.51</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3444,31 +3444,31 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>6942800</v>
+        <v>5865200</v>
       </c>
       <c r="G82" t="n">
-        <v>8195680000</v>
+        <v>6923530000</v>
       </c>
       <c r="H82" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I82" t="n">
-        <v>13.78</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3481,31 +3481,31 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>7455900</v>
+        <v>6431400</v>
       </c>
       <c r="G83" t="n">
-        <v>8801415000</v>
+        <v>7591952000</v>
       </c>
       <c r="H83" t="n">
-        <v>1180.463123164206</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I83" t="n">
-        <v>14.79</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z1UE.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3514,183 +3514,183 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5331</v>
+        <v>3765</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1481600</v>
+        <v>5883300</v>
       </c>
       <c r="G84" t="n">
-        <v>5294365000</v>
+        <v>17576858000</v>
       </c>
       <c r="H84" t="n">
-        <v>3573.410502159827</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>12332900</v>
+        <v>6942800</v>
       </c>
       <c r="G85" t="n">
-        <v>14653495000</v>
+        <v>8195680000</v>
       </c>
       <c r="H85" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I85" t="n">
-        <v>5.19</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6145</v>
+        <v>1882</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>100</v>
+        <v>7455900</v>
       </c>
       <c r="G86" t="n">
-        <v>171000</v>
+        <v>8801415000</v>
       </c>
       <c r="H86" t="n">
-        <v>1710</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8715</v>
+        <v>5331</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3810400</v>
+        <v>1481600</v>
       </c>
       <c r="G87" t="n">
-        <v>2500615000</v>
+        <v>5294365000</v>
       </c>
       <c r="H87" t="n">
-        <v>656.2604975855553</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I87" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8585</v>
+        <v>6952</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>8986800</v>
+        <v>12332900</v>
       </c>
       <c r="G88" t="n">
-        <v>7174886000</v>
+        <v>14653495000</v>
       </c>
       <c r="H88" t="n">
-        <v>798.3805136422309</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I88" t="n">
-        <v>5.23</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6908</v>
+        <v>6145</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G89" t="n">
-        <v>992000</v>
+        <v>171000</v>
       </c>
       <c r="H89" t="n">
-        <v>2480</v>
+        <v>1710</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -3722,12 +3722,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3736,144 +3736,146 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8923</v>
+        <v>8715</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2434800</v>
+        <v>3810400</v>
       </c>
       <c r="G90" t="n">
-        <v>4266809000</v>
+        <v>2500615000</v>
       </c>
       <c r="H90" t="n">
-        <v>1752.426893379333</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>9069</v>
+        <v>8585</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>8793900</v>
+        <v>8986800</v>
       </c>
       <c r="G91" t="n">
-        <v>13684104000</v>
+        <v>7174886000</v>
       </c>
       <c r="H91" t="n">
-        <v>1556.090471804319</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I91" t="n">
-        <v>5.01</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1878</v>
+        <v>6908</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3475000</v>
+        <v>400</v>
       </c>
       <c r="G92" t="n">
-        <v>47745269000</v>
+        <v>992000</v>
       </c>
       <c r="H92" t="n">
-        <v>13739.64575539568</v>
+        <v>2480</v>
       </c>
       <c r="I92" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3328</v>
+        <v>8923</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>2434800</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>4266809000</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1752.426893379333</v>
+      </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3882,72 +3884,72 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3076</v>
+        <v>9069</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2841700</v>
+        <v>8793900</v>
       </c>
       <c r="G94" t="n">
-        <v>5705436000</v>
+        <v>13684104000</v>
       </c>
       <c r="H94" t="n">
-        <v>2007.754513143541</v>
+        <v>1556.090471804319</v>
       </c>
       <c r="I94" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100Z1T1.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3765</v>
+        <v>1878</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>5187300</v>
+        <v>3475000</v>
       </c>
       <c r="G95" t="n">
-        <v>15645357000</v>
+        <v>47745269000</v>
       </c>
       <c r="H95" t="n">
-        <v>3016.088716673414</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I95" t="n">
-        <v>7.5</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3956,72 +3958,70 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3106</v>
+        <v>3328</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>900156</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>4095263000</v>
-      </c>
-      <c r="H96" t="n">
-        <v>4549.503641591014</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>9302</v>
+        <v>3076</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3799000</v>
+        <v>2841700</v>
       </c>
       <c r="G97" t="n">
-        <v>5671170000</v>
+        <v>5705436000</v>
       </c>
       <c r="H97" t="n">
-        <v>1492.806001579363</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I97" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100Z1P1.zip</t>
+          <t>S100Z1T1.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4034,17 +4034,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>5186300</v>
+        <v>5187300</v>
       </c>
       <c r="G98" t="n">
-        <v>15642334000</v>
+        <v>15645357000</v>
       </c>
       <c r="H98" t="n">
-        <v>3016.087384069568</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="I98" t="n">
         <v>7.5</v>
@@ -4053,220 +4053,220 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>9684</v>
+        <v>3106</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>6704059</v>
+        <v>900156</v>
       </c>
       <c r="G99" t="n">
-        <v>42054369000</v>
+        <v>4095263000</v>
       </c>
       <c r="H99" t="n">
-        <v>6272.971195510064</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I99" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4619</v>
+        <v>9302</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>3799000</v>
       </c>
       <c r="G100" t="n">
-        <v>119000</v>
+        <v>5671170000</v>
       </c>
       <c r="H100" t="n">
-        <v>1190</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100Z1P1.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6332</v>
+        <v>3765</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>100</v>
+        <v>5186300</v>
       </c>
       <c r="G101" t="n">
-        <v>141000</v>
+        <v>15642334000</v>
       </c>
       <c r="H101" t="n">
-        <v>1410</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4849</v>
+        <v>9684</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2946942</v>
+        <v>6704059</v>
       </c>
       <c r="G102" t="n">
-        <v>5148132000</v>
+        <v>42054369000</v>
       </c>
       <c r="H102" t="n">
-        <v>1746.940387696806</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I102" t="n">
-        <v>5.93</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>6927</v>
+        <v>4619</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G103" t="n">
-        <v>1023871000</v>
+        <v>119000</v>
       </c>
       <c r="H103" t="n">
-        <v>896.0103264198827</v>
+        <v>1190</v>
       </c>
       <c r="I103" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4676</v>
+        <v>6332</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>100</v>
       </c>
       <c r="G104" t="n">
-        <v>242000</v>
+        <v>141000</v>
       </c>
       <c r="H104" t="n">
-        <v>2420</v>
+        <v>1410</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -4275,49 +4275,49 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1776</v>
+        <v>4849</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>126500</v>
+        <v>2946942</v>
       </c>
       <c r="G105" t="n">
-        <v>153399000</v>
+        <v>5148132000</v>
       </c>
       <c r="H105" t="n">
-        <v>1212.640316205534</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I105" t="n">
-        <v>1.36</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4326,58 +4326,58 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3963</v>
+        <v>6927</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1507900</v>
+        <v>1142700</v>
       </c>
       <c r="G106" t="n">
-        <v>635874000</v>
+        <v>1023871000</v>
       </c>
       <c r="H106" t="n">
-        <v>421.6950726175476</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I106" t="n">
-        <v>5.18</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6923</v>
+        <v>4676</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>256000</v>
+        <v>242000</v>
       </c>
       <c r="H107" t="n">
-        <v>2560</v>
+        <v>2420</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -4386,12 +4386,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4400,109 +4400,109 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6890</v>
+        <v>1776</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>30000</v>
+        <v>126500</v>
       </c>
       <c r="G108" t="n">
-        <v>71610000</v>
+        <v>153399000</v>
       </c>
       <c r="H108" t="n">
-        <v>2387</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I108" t="n">
-        <v>0.06</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3132</v>
+        <v>3963</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>8970900</v>
+        <v>1507900</v>
       </c>
       <c r="G109" t="n">
-        <v>10240398000</v>
+        <v>635874000</v>
       </c>
       <c r="H109" t="n">
-        <v>1141.512891683109</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I109" t="n">
-        <v>5.01</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4512</v>
+        <v>6923</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2137400</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>620573000</v>
+        <v>256000</v>
       </c>
       <c r="H110" t="n">
-        <v>290.3401328717133</v>
+        <v>2560</v>
       </c>
       <c r="I110" t="n">
-        <v>6.140000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4511,701 +4511,701 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>9006</v>
+        <v>6890</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>30000</v>
       </c>
       <c r="G111" t="n">
-        <v>34824000</v>
+        <v>71610000</v>
       </c>
       <c r="H111" t="n">
-        <v>1160.8</v>
+        <v>2387</v>
       </c>
       <c r="I111" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>4626</v>
+        <v>3132</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>4670190</v>
+        <v>8970900</v>
       </c>
       <c r="G112" t="n">
-        <v>16652257000</v>
+        <v>10240398000</v>
       </c>
       <c r="H112" t="n">
-        <v>3565.648720929983</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I112" t="n">
-        <v>8</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>9987</v>
+        <v>4512</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3888200</v>
+        <v>2137400</v>
       </c>
       <c r="G113" t="n">
-        <v>16086019000</v>
+        <v>620573000</v>
       </c>
       <c r="H113" t="n">
-        <v>4137.137750115735</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>7732</v>
+        <v>9006</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>7995900</v>
+        <v>30000</v>
       </c>
       <c r="G114" t="n">
-        <v>16678425000</v>
+        <v>34824000</v>
       </c>
       <c r="H114" t="n">
-        <v>2085.872134468915</v>
+        <v>1160.8</v>
       </c>
       <c r="I114" t="n">
-        <v>7.380000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3861</v>
+        <v>4626</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>100</v>
+        <v>4670190</v>
       </c>
       <c r="G115" t="n">
-        <v>59000</v>
+        <v>16652257000</v>
       </c>
       <c r="H115" t="n">
-        <v>590</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5715</v>
+        <v>9987</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G116" t="n">
-        <v>160000</v>
+        <v>16086019000</v>
       </c>
       <c r="H116" t="n">
-        <v>1600</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1882</v>
+        <v>7732</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>8033500</v>
+        <v>7995900</v>
       </c>
       <c r="G117" t="n">
-        <v>9401444000</v>
+        <v>16678425000</v>
       </c>
       <c r="H117" t="n">
-        <v>1170.279952698077</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I117" t="n">
-        <v>15.94</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G118" t="n">
-        <v>9367939000</v>
+        <v>59000</v>
       </c>
       <c r="H118" t="n">
-        <v>1169.924818603025</v>
+        <v>590</v>
       </c>
       <c r="I118" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3978</v>
+        <v>5715</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2891700</v>
+        <v>100</v>
       </c>
       <c r="G119" t="n">
-        <v>3425686000</v>
+        <v>160000</v>
       </c>
       <c r="H119" t="n">
-        <v>1184.661617733513</v>
+        <v>1600</v>
       </c>
       <c r="I119" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>24347342</v>
+        <v>8033500</v>
       </c>
       <c r="G120" t="n">
-        <v>148917027000</v>
+        <v>9401444000</v>
       </c>
       <c r="H120" t="n">
-        <v>6116.356643776557</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I120" t="n">
-        <v>5.23</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9257</v>
+        <v>1882</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>100</v>
+        <v>8007300</v>
       </c>
       <c r="G121" t="n">
-        <v>57000</v>
+        <v>9367939000</v>
       </c>
       <c r="H121" t="n">
-        <v>570</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1882</v>
+        <v>3978</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>7914900</v>
+        <v>2891700</v>
       </c>
       <c r="G122" t="n">
-        <v>9250219000</v>
+        <v>3425686000</v>
       </c>
       <c r="H122" t="n">
-        <v>1168.709522546084</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I122" t="n">
-        <v>15.71</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>9531</v>
+        <v>4452</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>19554300</v>
+        <v>24347342</v>
       </c>
       <c r="G123" t="n">
-        <v>64960321000</v>
+        <v>148917027000</v>
       </c>
       <c r="H123" t="n">
-        <v>3322.047887165483</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I123" t="n">
-        <v>5.029999999999999</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4385</v>
+        <v>9257</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>8815360</v>
+        <v>100</v>
       </c>
       <c r="G124" t="n">
-        <v>17684138000</v>
+        <v>57000</v>
       </c>
       <c r="H124" t="n">
-        <v>2006.059650428343</v>
+        <v>570</v>
       </c>
       <c r="I124" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>7984</v>
+        <v>1882</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>6096500</v>
+        <v>7914900</v>
       </c>
       <c r="G125" t="n">
-        <v>13153972000</v>
+        <v>9250219000</v>
       </c>
       <c r="H125" t="n">
-        <v>2157.626835069302</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I125" t="n">
-        <v>5.02</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1973</v>
+        <v>9531</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>8973383</v>
+        <v>19554300</v>
       </c>
       <c r="G126" t="n">
-        <v>24947403000</v>
+        <v>64960321000</v>
       </c>
       <c r="H126" t="n">
-        <v>2780.155823060266</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I126" t="n">
-        <v>6.01</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6908</v>
+        <v>4385</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>502000</v>
+        <v>8815360</v>
       </c>
       <c r="G127" t="n">
-        <v>1257178000</v>
+        <v>17684138000</v>
       </c>
       <c r="H127" t="n">
-        <v>2504.338645418327</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I127" t="n">
-        <v>2.04</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3765</v>
+        <v>7984</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>4552900</v>
+        <v>6096500</v>
       </c>
       <c r="G128" t="n">
-        <v>13383536000</v>
+        <v>13153972000</v>
       </c>
       <c r="H128" t="n">
-        <v>2939.562915943684</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I128" t="n">
-        <v>5.47</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5482</v>
+        <v>1973</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>433300</v>
+        <v>8973383</v>
       </c>
       <c r="G129" t="n">
-        <v>1367192000</v>
+        <v>24947403000</v>
       </c>
       <c r="H129" t="n">
-        <v>3155.301177013616</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I129" t="n">
-        <v>2.18</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5214,72 +5214,72 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>8141</v>
+        <v>6908</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>100</v>
+        <v>502000</v>
       </c>
       <c r="G130" t="n">
-        <v>93000</v>
+        <v>1257178000</v>
       </c>
       <c r="H130" t="n">
-        <v>930</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4272</v>
+        <v>3765</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>26855100</v>
+        <v>4552900</v>
       </c>
       <c r="G131" t="n">
-        <v>29860350000</v>
+        <v>13383536000</v>
       </c>
       <c r="H131" t="n">
-        <v>1111.90611839092</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I131" t="n">
-        <v>15.75</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5288,294 +5288,294 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6145</v>
+        <v>5482</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>100</v>
+        <v>433300</v>
       </c>
       <c r="G132" t="n">
-        <v>171000</v>
+        <v>1367192000</v>
       </c>
       <c r="H132" t="n">
-        <v>1710</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4205</v>
+        <v>8141</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G133" t="n">
-        <v>24829312000</v>
+        <v>93000</v>
       </c>
       <c r="H133" t="n">
-        <v>1721.078563209627</v>
+        <v>930</v>
       </c>
       <c r="I133" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3569</v>
+        <v>4272</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>4271704</v>
+        <v>26855100</v>
       </c>
       <c r="G134" t="n">
-        <v>5808044000</v>
+        <v>29860350000</v>
       </c>
       <c r="H134" t="n">
-        <v>1359.655069733296</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I134" t="n">
-        <v>6.279999999999999</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6516</v>
+        <v>6145</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>679500</v>
+        <v>100</v>
       </c>
       <c r="G135" t="n">
-        <v>4792335000</v>
+        <v>171000</v>
       </c>
       <c r="H135" t="n">
-        <v>7052.737306843267</v>
+        <v>1710</v>
       </c>
       <c r="I135" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2327</v>
+        <v>4205</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>9154320</v>
+        <v>14426600</v>
       </c>
       <c r="G136" t="n">
-        <v>23450671000</v>
+        <v>24829312000</v>
       </c>
       <c r="H136" t="n">
-        <v>2561.705402476645</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I136" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3989</v>
+        <v>3569</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1206000</v>
+        <v>4271704</v>
       </c>
       <c r="G137" t="n">
-        <v>787604000</v>
+        <v>5808044000</v>
       </c>
       <c r="H137" t="n">
-        <v>653.0713101160862</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I137" t="n">
-        <v>5.2</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6908</v>
+        <v>6516</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>100</v>
+        <v>679500</v>
       </c>
       <c r="G138" t="n">
-        <v>288000</v>
+        <v>4792335000</v>
       </c>
       <c r="H138" t="n">
-        <v>2880</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>5988</v>
+        <v>2327</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>527300</v>
+        <v>9154320</v>
       </c>
       <c r="G139" t="n">
-        <v>1212090000</v>
+        <v>23450671000</v>
       </c>
       <c r="H139" t="n">
-        <v>2298.672482457804</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I139" t="n">
-        <v>1.42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5584,72 +5584,72 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3529</v>
+        <v>3989</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>998000</v>
+        <v>1206000</v>
       </c>
       <c r="G140" t="n">
-        <v>667598000</v>
+        <v>787604000</v>
       </c>
       <c r="H140" t="n">
-        <v>668.9358717434869</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I140" t="n">
-        <v>5.76</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7305</v>
+        <v>6908</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>309800</v>
+        <v>100</v>
       </c>
       <c r="G141" t="n">
-        <v>1321438000</v>
+        <v>288000</v>
       </c>
       <c r="H141" t="n">
-        <v>4265.455132343447</v>
+        <v>2880</v>
       </c>
       <c r="I141" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5658,391 +5658,391 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5541</v>
+        <v>5988</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>100</v>
+        <v>527300</v>
       </c>
       <c r="G142" t="n">
-        <v>127000</v>
+        <v>1212090000</v>
       </c>
       <c r="H142" t="n">
-        <v>1270</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2168</v>
+        <v>3529</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2094200</v>
+        <v>998000</v>
       </c>
       <c r="G143" t="n">
-        <v>4445105000</v>
+        <v>667598000</v>
       </c>
       <c r="H143" t="n">
-        <v>2122.579027791042</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I143" t="n">
-        <v>5.02</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4967</v>
+        <v>7305</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>4062075</v>
+        <v>309800</v>
       </c>
       <c r="G144" t="n">
-        <v>8729143000</v>
+        <v>1321438000</v>
       </c>
       <c r="H144" t="n">
-        <v>2148.936934940886</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G145" t="n">
-        <v>20578848000</v>
+        <v>127000</v>
       </c>
       <c r="H145" t="n">
-        <v>5066.092575838703</v>
+        <v>1270</v>
       </c>
       <c r="I145" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>8803</v>
+        <v>2168</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G146" t="n">
-        <v>361000</v>
+        <v>4445105000</v>
       </c>
       <c r="H146" t="n">
-        <v>3610</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G147" t="n">
-        <v>5292086000</v>
+        <v>8729143000</v>
       </c>
       <c r="H147" t="n">
-        <v>2112.609181636727</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I147" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>8129</v>
+        <v>4967</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>7258230</v>
+        <v>4062075</v>
       </c>
       <c r="G148" t="n">
-        <v>24720910000</v>
+        <v>20578848000</v>
       </c>
       <c r="H148" t="n">
-        <v>3405.914389596362</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I148" t="n">
-        <v>9.460000000000001</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2206</v>
+        <v>8803</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3462600</v>
+        <v>100</v>
       </c>
       <c r="G149" t="n">
-        <v>14385811000</v>
+        <v>361000</v>
       </c>
       <c r="H149" t="n">
-        <v>4154.626869982095</v>
+        <v>3610</v>
       </c>
       <c r="I149" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3666</v>
+        <v>9882</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1053200</v>
+        <v>2505000</v>
       </c>
       <c r="G150" t="n">
-        <v>663809000</v>
+        <v>5292086000</v>
       </c>
       <c r="H150" t="n">
-        <v>630.278199772123</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I150" t="n">
-        <v>5.16</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4347</v>
+        <v>8129</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>614893</v>
+        <v>7258230</v>
       </c>
       <c r="G151" t="n">
-        <v>940560000</v>
+        <v>24720910000</v>
       </c>
       <c r="H151" t="n">
-        <v>1529.631984751819</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I151" t="n">
-        <v>8.200000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>8129</v>
+        <v>2206</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3886330</v>
+        <v>3462600</v>
       </c>
       <c r="G152" t="n">
-        <v>10549885000</v>
+        <v>14385811000</v>
       </c>
       <c r="H152" t="n">
-        <v>2714.613787300615</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I152" t="n">
         <v>5.06</v>
@@ -6051,12 +6051,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6065,72 +6065,72 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>8929</v>
+        <v>3666</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1260812</v>
+        <v>1053200</v>
       </c>
       <c r="G153" t="n">
-        <v>1699255000</v>
+        <v>663809000</v>
       </c>
       <c r="H153" t="n">
-        <v>1347.74653160027</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I153" t="n">
-        <v>5.140000000000001</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7278</v>
+        <v>4347</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>115400</v>
+        <v>614893</v>
       </c>
       <c r="G154" t="n">
-        <v>302115000</v>
+        <v>940560000</v>
       </c>
       <c r="H154" t="n">
-        <v>2617.980935875217</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I154" t="n">
-        <v>0.24</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6139,72 +6139,72 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3591</v>
+        <v>8129</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2846091</v>
+        <v>3886330</v>
       </c>
       <c r="G155" t="n">
-        <v>6888596000</v>
+        <v>10549885000</v>
       </c>
       <c r="H155" t="n">
-        <v>2420.370957920882</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I155" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4042</v>
+        <v>8929</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>16459200</v>
+        <v>1260812</v>
       </c>
       <c r="G156" t="n">
-        <v>33451116000</v>
+        <v>1699255000</v>
       </c>
       <c r="H156" t="n">
-        <v>2032.365850102071</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I156" t="n">
-        <v>5.06</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6213,95 +6213,95 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>4521</v>
+        <v>7278</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>100</v>
+        <v>115400</v>
       </c>
       <c r="G157" t="n">
-        <v>353000</v>
+        <v>302115000</v>
       </c>
       <c r="H157" t="n">
-        <v>3530</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>8923</v>
+        <v>3591</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2445600</v>
+        <v>2846091</v>
       </c>
       <c r="G158" t="n">
-        <v>3856031000</v>
+        <v>6888596000</v>
       </c>
       <c r="H158" t="n">
-        <v>1576.721867844292</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I158" t="n">
-        <v>5.02</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4347</v>
+        <v>4042</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>400493</v>
+        <v>16459200</v>
       </c>
       <c r="G159" t="n">
-        <v>580713000</v>
+        <v>33451116000</v>
       </c>
       <c r="H159" t="n">
-        <v>1449.995380693296</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I159" t="n">
         <v>5.06</v>
@@ -6310,160 +6310,160 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>9024</v>
+        <v>4521</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>16207437</v>
+        <v>100</v>
       </c>
       <c r="G160" t="n">
-        <v>27823532000</v>
+        <v>353000</v>
       </c>
       <c r="H160" t="n">
-        <v>1716.713876475349</v>
+        <v>3530</v>
       </c>
       <c r="I160" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1518</v>
+        <v>8923</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>100</v>
+        <v>2445600</v>
       </c>
       <c r="G161" t="n">
-        <v>292000</v>
+        <v>3856031000</v>
       </c>
       <c r="H161" t="n">
-        <v>2920</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>7731</v>
+        <v>4347</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>17639800</v>
+        <v>400493</v>
       </c>
       <c r="G162" t="n">
-        <v>26675255000</v>
+        <v>580713000</v>
       </c>
       <c r="H162" t="n">
-        <v>1512.21980974841</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I162" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4536</v>
+        <v>9024</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>18290500</v>
+        <v>16207437</v>
       </c>
       <c r="G163" t="n">
-        <v>24591924000</v>
+        <v>27823532000</v>
       </c>
       <c r="H163" t="n">
-        <v>1344.518957928979</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I163" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4185</v>
+        <v>1518</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F164" t="n">
         <v>100</v>
       </c>
       <c r="G164" t="n">
-        <v>405000</v>
+        <v>292000</v>
       </c>
       <c r="H164" t="n">
-        <v>4050</v>
+        <v>2920</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -6495,86 +6495,86 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4549</v>
+        <v>7731</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2006900</v>
+        <v>17639800</v>
       </c>
       <c r="G165" t="n">
-        <v>3367745000</v>
+        <v>26675255000</v>
       </c>
       <c r="H165" t="n">
-        <v>1678.083113259255</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I165" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>9627</v>
+        <v>4536</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>3401100</v>
+        <v>18290500</v>
       </c>
       <c r="G166" t="n">
-        <v>9648726000</v>
+        <v>24591924000</v>
       </c>
       <c r="H166" t="n">
-        <v>2836.942753814942</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I166" t="n">
-        <v>9.6</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6583,21 +6583,21 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>8304</v>
+        <v>4185</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F167" t="n">
         <v>100</v>
       </c>
       <c r="G167" t="n">
-        <v>219000</v>
+        <v>405000</v>
       </c>
       <c r="H167" t="n">
-        <v>2190</v>
+        <v>4050</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -6606,12 +6606,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6620,257 +6620,257 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3328</v>
+        <v>4549</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>845300</v>
+        <v>2006900</v>
       </c>
       <c r="G168" t="n">
-        <v>1219326000</v>
+        <v>3367745000</v>
       </c>
       <c r="H168" t="n">
-        <v>1442.477227019993</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I168" t="n">
-        <v>6.54</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>675500</v>
+        <v>3401100</v>
       </c>
       <c r="G169" t="n">
-        <v>976503000</v>
+        <v>9648726000</v>
       </c>
       <c r="H169" t="n">
-        <v>1445.60029607698</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I169" t="n">
-        <v>5.220000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>8818</v>
+        <v>8304</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2505000</v>
+        <v>100</v>
       </c>
       <c r="G170" t="n">
-        <v>3361654000</v>
+        <v>219000</v>
       </c>
       <c r="H170" t="n">
-        <v>1341.977644710579</v>
+        <v>2190</v>
       </c>
       <c r="I170" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>100</v>
+        <v>845300</v>
       </c>
       <c r="G171" t="n">
-        <v>117000</v>
+        <v>1219326000</v>
       </c>
       <c r="H171" t="n">
-        <v>1170</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7315</v>
+        <v>3328</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>6994900</v>
+        <v>675500</v>
       </c>
       <c r="G172" t="n">
-        <v>5874641000</v>
+        <v>976503000</v>
       </c>
       <c r="H172" t="n">
-        <v>839.8463166020958</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I172" t="n">
-        <v>14.23</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4837</v>
+        <v>8818</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>5428600</v>
+        <v>2505000</v>
       </c>
       <c r="G173" t="n">
-        <v>4378021000</v>
+        <v>3361654000</v>
       </c>
       <c r="H173" t="n">
-        <v>806.4733080352208</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I173" t="n">
-        <v>9.74</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>4293</v>
+        <v>5541</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>20896886</v>
+        <v>100</v>
       </c>
       <c r="G174" t="n">
-        <v>9376038000</v>
+        <v>117000</v>
       </c>
       <c r="H174" t="n">
-        <v>448.6811097117532</v>
+        <v>1170</v>
       </c>
       <c r="I174" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6879,72 +6879,72 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4631</v>
+        <v>7315</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>6563759</v>
+        <v>6994900</v>
       </c>
       <c r="G175" t="n">
-        <v>16844475000</v>
+        <v>5874641000</v>
       </c>
       <c r="H175" t="n">
-        <v>2566.284807227078</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I175" t="n">
-        <v>6.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5449</v>
+        <v>4837</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2114100</v>
+        <v>5428600</v>
       </c>
       <c r="G176" t="n">
-        <v>3695597000</v>
+        <v>4378021000</v>
       </c>
       <c r="H176" t="n">
-        <v>1748.071046781136</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I176" t="n">
-        <v>5</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6953,109 +6953,109 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>6232</v>
+        <v>4293</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1499000</v>
+        <v>20896886</v>
       </c>
       <c r="G177" t="n">
-        <v>1369002000</v>
+        <v>9376038000</v>
       </c>
       <c r="H177" t="n">
-        <v>913.2768512341561</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I177" t="n">
-        <v>10.47</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6237</v>
+        <v>4631</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1129500</v>
+        <v>6563759</v>
       </c>
       <c r="G178" t="n">
-        <v>1537738000</v>
+        <v>16844475000</v>
       </c>
       <c r="H178" t="n">
-        <v>1361.432492253209</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I178" t="n">
-        <v>5.02</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4987</v>
+        <v>5449</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1543800</v>
+        <v>2114100</v>
       </c>
       <c r="G179" t="n">
-        <v>874286000</v>
+        <v>3695597000</v>
       </c>
       <c r="H179" t="n">
-        <v>566.3207669387226</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I179" t="n">
-        <v>5.779999999999999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7064,278 +7064,389 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4739</v>
+        <v>6232</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>15400600</v>
+        <v>1499000</v>
       </c>
       <c r="G180" t="n">
-        <v>66216726000</v>
+        <v>1369002000</v>
       </c>
       <c r="H180" t="n">
-        <v>4299.619884939548</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I180" t="n">
-        <v>6.419999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2501</v>
+        <v>6237</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>4010500</v>
+        <v>1129500</v>
       </c>
       <c r="G181" t="n">
-        <v>10817766000</v>
+        <v>1537738000</v>
       </c>
       <c r="H181" t="n">
-        <v>2697.360927565142</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I181" t="n">
-        <v>5.09</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4023</v>
+        <v>4987</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>100</v>
+        <v>1543800</v>
       </c>
       <c r="G182" t="n">
-        <v>796000</v>
+        <v>874286000</v>
       </c>
       <c r="H182" t="n">
-        <v>7960</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>5844</v>
+        <v>4739</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>4998800</v>
+        <v>15400600</v>
       </c>
       <c r="G183" t="n">
-        <v>24949147000</v>
+        <v>66216726000</v>
       </c>
       <c r="H183" t="n">
-        <v>4991.027246539169</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I183" t="n">
-        <v>6.59</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5947</v>
+        <v>2501</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>7446200</v>
+        <v>4010500</v>
       </c>
       <c r="G184" t="n">
-        <v>21182239000</v>
+        <v>10817766000</v>
       </c>
       <c r="H184" t="n">
-        <v>2844.704547285864</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I184" t="n">
-        <v>4.96</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>5186</v>
+        <v>4023</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1536900</v>
+        <v>100</v>
       </c>
       <c r="G185" t="n">
-        <v>4758738000</v>
+        <v>796000</v>
       </c>
       <c r="H185" t="n">
-        <v>3096.322467304314</v>
+        <v>7960</v>
       </c>
       <c r="I185" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>8303</v>
+        <v>5844</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>20000000</v>
+        <v>4998800</v>
       </c>
       <c r="G186" t="n">
-        <v>56014500000</v>
+        <v>24949147000</v>
       </c>
       <c r="H186" t="n">
-        <v>2800.725</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I186" t="n">
-        <v>9.75</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
+          <t>S100RYRP.zip</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>5947</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>7446200</v>
+      </c>
+      <c r="G187" t="n">
+        <v>21182239000</v>
+      </c>
+      <c r="H187" t="n">
+        <v>2844.704547285864</v>
+      </c>
+      <c r="I187" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>S100RY2V.zip</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>5186</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>1536900</v>
+      </c>
+      <c r="G188" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H188" t="n">
+        <v>3096.322467304314</v>
+      </c>
+      <c r="I188" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G189" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I189" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
           <t>S100RVIC.zip</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
-      <c r="D187" t="n">
+      <c r="D190" t="n">
         <v>2812</v>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>2023-09-11</t>
         </is>
       </c>
-      <c r="F187" t="n">
+      <c r="F190" t="n">
         <v>1120000</v>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="n">
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="n">
         <v>9.779999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2131,86 +2131,86 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100Z2CJ.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9072</v>
+        <v>4189</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>8985002</v>
+        <v>2917700</v>
       </c>
       <c r="G47" t="n">
-        <v>24970571000</v>
+        <v>7487288000</v>
       </c>
       <c r="H47" t="n">
-        <v>2779.139169918938</v>
+        <v>2566.161017239607</v>
       </c>
       <c r="I47" t="n">
-        <v>7.1</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G48" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H48" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I48" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100Z1ZF.zip</t>
+          <t>S100Z2BC.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3765</v>
+        <v>4189</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2227,286 +2227,286 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6600700</v>
+        <v>2040400</v>
       </c>
       <c r="G49" t="n">
-        <v>19175476000</v>
+        <v>5203426000</v>
       </c>
       <c r="H49" t="n">
-        <v>2905.067038344418</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I49" t="n">
-        <v>9.539999999999999</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G50" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H50" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I50" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100Z1ZF.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2972</v>
+        <v>3765</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>6600700</v>
       </c>
       <c r="G51" t="n">
-        <v>125000</v>
+        <v>19175476000</v>
       </c>
       <c r="H51" t="n">
-        <v>125000</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G52" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H52" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I52" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100Z1ZC.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3765</v>
+        <v>2972</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6336400</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>18726232000</v>
+        <v>125000</v>
       </c>
       <c r="H53" t="n">
-        <v>2955.342465753425</v>
+        <v>125000</v>
       </c>
       <c r="I53" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G54" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H54" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I54" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100Z1ZC.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>8233</v>
+        <v>3765</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>261400</v>
+        <v>6336400</v>
       </c>
       <c r="G55" t="n">
-        <v>287906000</v>
+        <v>18726232000</v>
       </c>
       <c r="H55" t="n">
-        <v>1101.400153022188</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="I55" t="n">
-        <v>0.08</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2371</v>
+        <v>3106</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10372003</v>
+        <v>853156</v>
       </c>
       <c r="G56" t="n">
-        <v>24045569000</v>
+        <v>4849339000</v>
       </c>
       <c r="H56" t="n">
-        <v>2318.314890576102</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I56" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2515,479 +2515,479 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2432</v>
+        <v>8233</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>100</v>
+        <v>261400</v>
       </c>
       <c r="G57" t="n">
-        <v>226000</v>
+        <v>287906000</v>
       </c>
       <c r="H57" t="n">
-        <v>2260</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G58" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H58" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I58" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>8570</v>
+        <v>2432</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>11014402</v>
+        <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>14194389000</v>
+        <v>226000</v>
       </c>
       <c r="H59" t="n">
-        <v>1288.711724885291</v>
+        <v>2260</v>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6890</v>
+        <v>7378</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4038389</v>
+        <v>500400</v>
       </c>
       <c r="G60" t="n">
-        <v>15954609000</v>
+        <v>698873000</v>
       </c>
       <c r="H60" t="n">
-        <v>3950.736048458928</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I60" t="n">
-        <v>8.5</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9742</v>
+        <v>8570</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1048500</v>
+        <v>11014402</v>
       </c>
       <c r="G61" t="n">
-        <v>1970276000</v>
+        <v>14194389000</v>
       </c>
       <c r="H61" t="n">
-        <v>1879.137815927515</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I61" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G62" t="n">
-        <v>268179335000</v>
+        <v>15954609000</v>
       </c>
       <c r="H62" t="n">
-        <v>16430.4430802409</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I62" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G63" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H63" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I63" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G64" t="n">
-        <v>1831405000</v>
+        <v>268179335000</v>
       </c>
       <c r="H64" t="n">
-        <v>3321.975331035734</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I64" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G65" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H65" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I65" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1882</v>
+        <v>8011</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1998200</v>
+        <v>551300</v>
       </c>
       <c r="G66" t="n">
-        <v>2358382000</v>
+        <v>1831405000</v>
       </c>
       <c r="H66" t="n">
-        <v>1180.253227905114</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I66" t="n">
-        <v>3.97</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4549</v>
+        <v>6856</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2546351</v>
+        <v>4180400</v>
       </c>
       <c r="G67" t="n">
-        <v>4958319000</v>
+        <v>49662804000</v>
       </c>
       <c r="H67" t="n">
-        <v>1947.225264702313</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I67" t="n">
-        <v>7.37</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7940</v>
+        <v>1882</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>100</v>
+        <v>1998200</v>
       </c>
       <c r="G68" t="n">
-        <v>101000</v>
+        <v>2358382000</v>
       </c>
       <c r="H68" t="n">
-        <v>1010</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1882</v>
+        <v>4549</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2528200</v>
+        <v>2546351</v>
       </c>
       <c r="G69" t="n">
-        <v>2984068000</v>
+        <v>4958319000</v>
       </c>
       <c r="H69" t="n">
-        <v>1180.31326635551</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I69" t="n">
-        <v>5.02</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2996,21 +2996,21 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H70" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -3019,49 +3019,49 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2432</v>
+        <v>1882</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G71" t="n">
-        <v>226000</v>
+        <v>2984068000</v>
       </c>
       <c r="H71" t="n">
-        <v>2260</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3070,21 +3070,21 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H72" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -3093,12 +3093,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H73" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -3130,12 +3130,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3144,294 +3144,294 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H74" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I74" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2229</v>
+        <v>4917</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>23390757000</v>
+        <v>204000</v>
       </c>
       <c r="H75" t="n">
-        <v>2919.137515755844</v>
+        <v>2040</v>
       </c>
       <c r="I75" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1882</v>
+        <v>8233</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4275700</v>
+        <v>261400</v>
       </c>
       <c r="G76" t="n">
-        <v>5047062000</v>
+        <v>287906000</v>
       </c>
       <c r="H76" t="n">
-        <v>1180.406015389293</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I76" t="n">
-        <v>8.48</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G77" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H77" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I77" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G78" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H78" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I78" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G79" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H79" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I79" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G80" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H80" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I80" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1297500</v>
+        <v>4783700</v>
       </c>
       <c r="G81" t="n">
-        <v>4476090000</v>
+        <v>5646776000</v>
       </c>
       <c r="H81" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I81" t="n">
-        <v>5.23</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3444,68 +3444,68 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5865200</v>
+        <v>5295000</v>
       </c>
       <c r="G82" t="n">
-        <v>6923530000</v>
+        <v>6250386000</v>
       </c>
       <c r="H82" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I82" t="n">
-        <v>11.64</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G83" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H83" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I83" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100Z1UE.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3514,35 +3514,35 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3765</v>
+        <v>1882</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5883300</v>
+        <v>5865200</v>
       </c>
       <c r="G84" t="n">
-        <v>17576858000</v>
+        <v>6923530000</v>
       </c>
       <c r="H84" t="n">
-        <v>2987.584858837727</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I84" t="n">
-        <v>8.51</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3555,31 +3555,31 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6942800</v>
+        <v>6431400</v>
       </c>
       <c r="G85" t="n">
-        <v>8195680000</v>
+        <v>7591952000</v>
       </c>
       <c r="H85" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I85" t="n">
-        <v>13.78</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z1UE.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3588,35 +3588,35 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1882</v>
+        <v>3765</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>7455900</v>
+        <v>5883300</v>
       </c>
       <c r="G86" t="n">
-        <v>8801415000</v>
+        <v>17576858000</v>
       </c>
       <c r="H86" t="n">
-        <v>1180.463123164206</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="I86" t="n">
-        <v>14.79</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3625,523 +3625,523 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G87" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H87" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G88" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H88" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I88" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G89" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H89" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G90" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H90" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I90" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G91" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H91" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I91" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G92" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H92" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G93" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H93" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G94" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H94" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I94" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G95" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H95" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I95" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G97" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H97" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I97" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100Z1T1.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3765</v>
+        <v>3328</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>5187300</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>15645357000</v>
-      </c>
-      <c r="H98" t="n">
-        <v>3016.088716673414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G99" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H99" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100Z1T1.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9302</v>
+        <v>3765</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3799000</v>
+        <v>5187300</v>
       </c>
       <c r="G100" t="n">
-        <v>5671170000</v>
+        <v>15645357000</v>
       </c>
       <c r="H100" t="n">
-        <v>1492.806001579363</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="I100" t="n">
-        <v>5.07</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100Z1P1.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3765</v>
+        <v>3106</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4149,27 +4149,27 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>5186300</v>
+        <v>900156</v>
       </c>
       <c r="G101" t="n">
-        <v>15642334000</v>
+        <v>4095263000</v>
       </c>
       <c r="H101" t="n">
-        <v>3016.087384069568</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I101" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4178,294 +4178,294 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G102" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H102" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I102" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100Z1P1.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>4619</v>
+        <v>3765</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>100</v>
+        <v>5186300</v>
       </c>
       <c r="G103" t="n">
-        <v>119000</v>
+        <v>15642334000</v>
       </c>
       <c r="H103" t="n">
-        <v>1190</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G104" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H104" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G105" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H105" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I105" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G106" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H106" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I106" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G107" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H107" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G108" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H108" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I108" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G109" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H109" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I109" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4474,257 +4474,257 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G110" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H110" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G111" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H111" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I111" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H112" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I112" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G113" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H113" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I113" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G114" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H114" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I114" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G115" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H115" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I115" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G116" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H116" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4733,442 +4733,442 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G117" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H117" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I117" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G118" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H118" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G119" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H119" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G120" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H120" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I120" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G121" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H121" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I121" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G122" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H122" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I122" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G123" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H123" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I123" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G124" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H124" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G125" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H125" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I125" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H126" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I126" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G127" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H127" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I127" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G128" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H128" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I128" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5177,109 +5177,109 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G129" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H129" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I129" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G130" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H130" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I130" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G131" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H131" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I131" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5288,109 +5288,109 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G132" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H132" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I132" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G133" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H133" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G134" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H134" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I134" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5399,21 +5399,21 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F135" t="n">
         <v>100</v>
       </c>
       <c r="G135" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H135" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
@@ -5422,456 +5422,456 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G136" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H136" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I136" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G137" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H137" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I137" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G138" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H138" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I138" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2327</v>
+        <v>3569</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>9154320</v>
+        <v>4271704</v>
       </c>
       <c r="G139" t="n">
-        <v>23450671000</v>
+        <v>5808044000</v>
       </c>
       <c r="H139" t="n">
-        <v>2561.705402476645</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I139" t="n">
-        <v>5</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G140" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H140" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I140" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G141" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H141" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G142" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H142" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I142" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G143" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H143" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I143" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G144" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H144" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I144" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G145" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H145" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G146" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H146" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I146" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G147" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H147" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5880,44 +5880,44 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G148" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H148" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I148" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5925,249 +5925,249 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G149" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H149" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G150" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H150" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I150" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G151" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H151" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I151" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G152" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H152" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I152" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G153" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H153" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I153" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G154" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H154" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I154" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G155" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H155" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I155" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6176,775 +6176,775 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G156" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H156" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I156" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G157" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H157" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I157" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G158" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H158" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I158" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G159" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H159" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I159" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G160" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H160" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G161" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H161" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I161" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G162" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H162" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I162" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G163" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H163" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I163" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G164" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H164" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G165" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H165" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I165" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G166" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H166" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I166" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G167" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H167" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G168" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H168" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I168" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G169" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H169" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I169" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G170" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H170" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G171" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H171" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I171" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G172" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H172" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I172" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G173" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H173" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I173" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G174" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H174" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G175" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H175" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I175" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G176" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H176" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I176" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6953,35 +6953,35 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G177" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H177" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I177" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6990,72 +6990,72 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G178" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H178" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I178" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G179" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H179" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I179" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7064,389 +7064,463 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G180" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H180" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I180" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G181" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H181" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I181" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G182" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H182" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I182" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G183" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H183" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I183" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G184" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H184" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I184" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G185" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H185" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G186" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H186" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I186" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G187" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H187" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I187" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G188" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H188" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I188" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G189" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H189" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I189" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
+          <t>S100RY2V.zip</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>5186</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>1536900</v>
+      </c>
+      <c r="G190" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3096.322467304314</v>
+      </c>
+      <c r="I190" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G191" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H191" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I191" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>S100RVIC.zip</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
-      <c r="D190" t="n">
+      <c r="D192" t="n">
         <v>2812</v>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>2023-09-11</t>
         </is>
       </c>
-      <c r="F190" t="n">
+      <c r="F192" t="n">
         <v>1120000</v>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="n">
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="n">
         <v>9.779999999999999</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I192"/>
+  <dimension ref="A1:I193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1983,58 +1983,58 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100Z2JM.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-17_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6675</v>
+        <v>4189</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>314400</v>
+        <v>4476500</v>
       </c>
       <c r="G43" t="n">
-        <v>1717778000</v>
+        <v>11865379000</v>
       </c>
       <c r="H43" t="n">
-        <v>5463.67048346056</v>
+        <v>2650.592873897018</v>
       </c>
       <c r="I43" t="n">
-        <v>5.029999999999999</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3549</v>
+        <v>6675</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2042,64 +2042,64 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>13408159</v>
+        <v>314400</v>
       </c>
       <c r="G44" t="n">
-        <v>40855887000</v>
+        <v>1717778000</v>
       </c>
       <c r="H44" t="n">
-        <v>3047.091476167608</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I44" t="n">
-        <v>14.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100Z1ZH.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3765</v>
+        <v>3549</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6673200</v>
+        <v>13408159</v>
       </c>
       <c r="G45" t="n">
-        <v>19362129000</v>
+        <v>40855887000</v>
       </c>
       <c r="H45" t="n">
-        <v>2901.475903614458</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I45" t="n">
-        <v>9.65</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100Z2IH.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-09_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2108,35 +2108,35 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7745</v>
+        <v>4189</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1458700</v>
+        <v>4054500</v>
       </c>
       <c r="G46" t="n">
-        <v>3040190000</v>
+        <v>10605706000</v>
       </c>
       <c r="H46" t="n">
-        <v>2084.177692465894</v>
+        <v>2615.786410161549</v>
       </c>
       <c r="I46" t="n">
-        <v>5.24</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100Z2CJ.zip</t>
+          <t>S100Z1ZH.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2145,72 +2145,72 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4189</v>
+        <v>3765</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2917700</v>
+        <v>6673200</v>
       </c>
       <c r="G47" t="n">
-        <v>7487288000</v>
+        <v>19362129000</v>
       </c>
       <c r="H47" t="n">
-        <v>2566.161017239607</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="I47" t="n">
-        <v>7.85</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G48" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H48" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I48" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100Z2BC.zip</t>
+          <t>S100Z2CJ.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2223,68 +2223,68 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2040400</v>
+        <v>2917700</v>
       </c>
       <c r="G49" t="n">
-        <v>5203426000</v>
+        <v>7487288000</v>
       </c>
       <c r="H49" t="n">
-        <v>2550.198980592041</v>
+        <v>2566.161017239607</v>
       </c>
       <c r="I49" t="n">
-        <v>5.489999999999999</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G50" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H50" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I50" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100Z1ZF.zip</t>
+          <t>S100Z2BC.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3765</v>
+        <v>4189</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2301,286 +2301,286 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6600700</v>
+        <v>2040400</v>
       </c>
       <c r="G51" t="n">
-        <v>19175476000</v>
+        <v>5203426000</v>
       </c>
       <c r="H51" t="n">
-        <v>2905.067038344418</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I51" t="n">
-        <v>9.539999999999999</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G52" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H52" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I52" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100Z1ZF.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2972</v>
+        <v>3765</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>6600700</v>
       </c>
       <c r="G53" t="n">
-        <v>125000</v>
+        <v>19175476000</v>
       </c>
       <c r="H53" t="n">
-        <v>125000</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G54" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H54" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I54" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100Z1ZC.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3765</v>
+        <v>2972</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6336400</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>18726232000</v>
+        <v>125000</v>
       </c>
       <c r="H55" t="n">
-        <v>2955.342465753425</v>
+        <v>125000</v>
       </c>
       <c r="I55" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G56" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H56" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I56" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100Z1ZC.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>8233</v>
+        <v>3765</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>261400</v>
+        <v>6336400</v>
       </c>
       <c r="G57" t="n">
-        <v>287906000</v>
+        <v>18726232000</v>
       </c>
       <c r="H57" t="n">
-        <v>1101.400153022188</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="I57" t="n">
-        <v>0.08</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2371</v>
+        <v>3106</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10372003</v>
+        <v>853156</v>
       </c>
       <c r="G58" t="n">
-        <v>24045569000</v>
+        <v>4849339000</v>
       </c>
       <c r="H58" t="n">
-        <v>2318.314890576102</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I58" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2589,479 +2589,479 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2432</v>
+        <v>8233</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>261400</v>
       </c>
       <c r="G59" t="n">
-        <v>226000</v>
+        <v>287906000</v>
       </c>
       <c r="H59" t="n">
-        <v>2260</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G60" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H60" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I60" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8570</v>
+        <v>2432</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>11014402</v>
+        <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>14194389000</v>
+        <v>226000</v>
       </c>
       <c r="H61" t="n">
-        <v>1288.711724885291</v>
+        <v>2260</v>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6890</v>
+        <v>7378</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4038389</v>
+        <v>500400</v>
       </c>
       <c r="G62" t="n">
-        <v>15954609000</v>
+        <v>698873000</v>
       </c>
       <c r="H62" t="n">
-        <v>3950.736048458928</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I62" t="n">
-        <v>8.5</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9742</v>
+        <v>8570</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1048500</v>
+        <v>11014402</v>
       </c>
       <c r="G63" t="n">
-        <v>1970276000</v>
+        <v>14194389000</v>
       </c>
       <c r="H63" t="n">
-        <v>1879.137815927515</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I63" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G64" t="n">
-        <v>268179335000</v>
+        <v>15954609000</v>
       </c>
       <c r="H64" t="n">
-        <v>16430.4430802409</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I64" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G65" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H65" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I65" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G66" t="n">
-        <v>1831405000</v>
+        <v>268179335000</v>
       </c>
       <c r="H66" t="n">
-        <v>3321.975331035734</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I66" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G67" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H67" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I67" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1882</v>
+        <v>8011</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1998200</v>
+        <v>551300</v>
       </c>
       <c r="G68" t="n">
-        <v>2358382000</v>
+        <v>1831405000</v>
       </c>
       <c r="H68" t="n">
-        <v>1180.253227905114</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I68" t="n">
-        <v>3.97</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4549</v>
+        <v>6856</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2546351</v>
+        <v>4180400</v>
       </c>
       <c r="G69" t="n">
-        <v>4958319000</v>
+        <v>49662804000</v>
       </c>
       <c r="H69" t="n">
-        <v>1947.225264702313</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I69" t="n">
-        <v>7.37</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7940</v>
+        <v>1882</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>100</v>
+        <v>1998200</v>
       </c>
       <c r="G70" t="n">
-        <v>101000</v>
+        <v>2358382000</v>
       </c>
       <c r="H70" t="n">
-        <v>1010</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1882</v>
+        <v>4549</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2528200</v>
+        <v>2546351</v>
       </c>
       <c r="G71" t="n">
-        <v>2984068000</v>
+        <v>4958319000</v>
       </c>
       <c r="H71" t="n">
-        <v>1180.31326635551</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I71" t="n">
-        <v>5.02</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3070,21 +3070,21 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H72" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -3093,49 +3093,49 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2432</v>
+        <v>1882</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G73" t="n">
-        <v>226000</v>
+        <v>2984068000</v>
       </c>
       <c r="H73" t="n">
-        <v>2260</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H74" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -3167,12 +3167,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H75" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3204,12 +3204,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3218,294 +3218,294 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G76" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H76" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I76" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2229</v>
+        <v>4917</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G77" t="n">
-        <v>23390757000</v>
+        <v>204000</v>
       </c>
       <c r="H77" t="n">
-        <v>2919.137515755844</v>
+        <v>2040</v>
       </c>
       <c r="I77" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1882</v>
+        <v>8233</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>4275700</v>
+        <v>261400</v>
       </c>
       <c r="G78" t="n">
-        <v>5047062000</v>
+        <v>287906000</v>
       </c>
       <c r="H78" t="n">
-        <v>1180.406015389293</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I78" t="n">
-        <v>8.48</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G79" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H79" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I79" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G80" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H80" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I80" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G81" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H81" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I81" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G82" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H82" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I82" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1297500</v>
+        <v>4783700</v>
       </c>
       <c r="G83" t="n">
-        <v>4476090000</v>
+        <v>5646776000</v>
       </c>
       <c r="H83" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I83" t="n">
-        <v>5.23</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3518,68 +3518,68 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5865200</v>
+        <v>5295000</v>
       </c>
       <c r="G84" t="n">
-        <v>6923530000</v>
+        <v>6250386000</v>
       </c>
       <c r="H84" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I84" t="n">
-        <v>11.64</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G85" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H85" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I85" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100Z1UE.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3588,35 +3588,35 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3765</v>
+        <v>1882</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5883300</v>
+        <v>5865200</v>
       </c>
       <c r="G86" t="n">
-        <v>17576858000</v>
+        <v>6923530000</v>
       </c>
       <c r="H86" t="n">
-        <v>2987.584858837727</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I86" t="n">
-        <v>8.51</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3629,31 +3629,31 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>6942800</v>
+        <v>6431400</v>
       </c>
       <c r="G87" t="n">
-        <v>8195680000</v>
+        <v>7591952000</v>
       </c>
       <c r="H87" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I87" t="n">
-        <v>13.78</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z1UE.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3662,35 +3662,35 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1882</v>
+        <v>3765</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>7455900</v>
+        <v>5883300</v>
       </c>
       <c r="G88" t="n">
-        <v>8801415000</v>
+        <v>17576858000</v>
       </c>
       <c r="H88" t="n">
-        <v>1180.463123164206</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="I88" t="n">
-        <v>14.79</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3699,523 +3699,523 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G89" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H89" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G90" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H90" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I90" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G91" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H91" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G92" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H92" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I92" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G93" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H93" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I93" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G94" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H94" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G95" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H95" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I95" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G96" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H96" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I96" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G97" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H97" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I97" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G99" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H99" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I99" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100Z1T1.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3765</v>
+        <v>3328</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>5187300</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>15645357000</v>
-      </c>
-      <c r="H100" t="n">
-        <v>3016.088716673414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G101" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H101" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100Z1T1.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>9302</v>
+        <v>3765</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3799000</v>
+        <v>5187300</v>
       </c>
       <c r="G102" t="n">
-        <v>5671170000</v>
+        <v>15645357000</v>
       </c>
       <c r="H102" t="n">
-        <v>1492.806001579363</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="I102" t="n">
-        <v>5.07</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100Z1P1.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3765</v>
+        <v>3106</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4223,27 +4223,27 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>5186300</v>
+        <v>900156</v>
       </c>
       <c r="G103" t="n">
-        <v>15642334000</v>
+        <v>4095263000</v>
       </c>
       <c r="H103" t="n">
-        <v>3016.087384069568</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I103" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4252,294 +4252,294 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G104" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H104" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I104" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100Z1P1.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4619</v>
+        <v>3765</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>100</v>
+        <v>5186300</v>
       </c>
       <c r="G105" t="n">
-        <v>119000</v>
+        <v>15642334000</v>
       </c>
       <c r="H105" t="n">
-        <v>1190</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G106" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H106" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G107" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H107" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I107" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G108" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H108" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I108" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G109" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H109" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G110" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H110" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I110" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H111" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I111" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4548,257 +4548,257 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G112" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H112" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G113" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H113" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I113" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G114" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H114" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I114" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G115" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H115" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I115" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G116" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H116" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I116" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G117" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H117" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G118" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H118" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4807,442 +4807,442 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>7732</v>
+        <v>4626</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>7995900</v>
+        <v>4670190</v>
       </c>
       <c r="G119" t="n">
-        <v>16678425000</v>
+        <v>16652257000</v>
       </c>
       <c r="H119" t="n">
-        <v>2085.872134468915</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I119" t="n">
-        <v>7.380000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>3861</v>
+        <v>9987</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>100</v>
+        <v>3888200</v>
       </c>
       <c r="G120" t="n">
-        <v>59000</v>
+        <v>16086019000</v>
       </c>
       <c r="H120" t="n">
-        <v>590</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G121" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H121" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G122" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H122" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I122" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G123" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H123" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I123" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G124" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H124" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I124" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G125" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H125" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I125" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G126" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H126" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G127" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H127" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I127" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G128" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H128" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I128" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G129" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H129" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I129" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G130" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H130" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I130" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5251,109 +5251,109 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G131" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H131" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I131" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G132" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H132" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I132" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G133" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H133" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I133" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5362,109 +5362,109 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G134" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H134" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I134" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G135" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H135" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G136" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H136" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I136" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5473,21 +5473,21 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F137" t="n">
         <v>100</v>
       </c>
       <c r="G137" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H137" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
@@ -5496,456 +5496,456 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G138" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H138" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I138" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G139" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H139" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I139" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>6516</v>
+        <v>4205</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>679500</v>
+        <v>14426600</v>
       </c>
       <c r="G140" t="n">
-        <v>4792335000</v>
+        <v>24829312000</v>
       </c>
       <c r="H140" t="n">
-        <v>7052.737306843267</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I140" t="n">
-        <v>5.24</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2327</v>
+        <v>3569</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>9154320</v>
+        <v>4271704</v>
       </c>
       <c r="G141" t="n">
-        <v>23450671000</v>
+        <v>5808044000</v>
       </c>
       <c r="H141" t="n">
-        <v>2561.705402476645</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I141" t="n">
-        <v>5</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G142" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H142" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G143" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H143" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G144" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H144" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I144" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G145" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H145" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I145" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G146" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H146" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I146" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G147" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H147" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G148" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H148" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I148" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G149" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H149" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5954,44 +5954,44 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G150" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H150" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I150" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5999,249 +5999,249 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G151" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H151" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>9882</v>
+        <v>4967</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2505000</v>
+        <v>4062075</v>
       </c>
       <c r="G152" t="n">
-        <v>5292086000</v>
+        <v>20578848000</v>
       </c>
       <c r="H152" t="n">
-        <v>2112.609181636727</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I152" t="n">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>8129</v>
+        <v>8803</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>7258230</v>
+        <v>100</v>
       </c>
       <c r="G153" t="n">
-        <v>24720910000</v>
+        <v>361000</v>
       </c>
       <c r="H153" t="n">
-        <v>3405.914389596362</v>
+        <v>3610</v>
       </c>
       <c r="I153" t="n">
-        <v>9.460000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G154" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H154" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I154" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G155" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H155" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I155" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G156" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H156" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I156" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G157" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H157" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I157" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6250,775 +6250,775 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G158" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H158" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I158" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G159" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H159" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I159" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G160" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H160" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I160" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G161" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H161" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I161" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4521</v>
+        <v>3591</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>100</v>
+        <v>2846091</v>
       </c>
       <c r="G162" t="n">
-        <v>353000</v>
+        <v>6888596000</v>
       </c>
       <c r="H162" t="n">
-        <v>3530</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>8923</v>
+        <v>4042</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2445600</v>
+        <v>16459200</v>
       </c>
       <c r="G163" t="n">
-        <v>3856031000</v>
+        <v>33451116000</v>
       </c>
       <c r="H163" t="n">
-        <v>1576.721867844292</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I163" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G164" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H164" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I164" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G165" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H165" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I165" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G166" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H166" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G167" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H167" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I167" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G168" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H168" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I168" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G169" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H169" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G170" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H170" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I170" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G171" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H171" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I171" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G172" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H172" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G173" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H173" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I173" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G174" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H174" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I174" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G175" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H175" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I175" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G176" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H176" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G177" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H177" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I177" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G178" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H178" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I178" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7027,35 +7027,35 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G179" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H179" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I179" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7064,72 +7064,72 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G180" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H180" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I180" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>5449</v>
+        <v>4293</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>2114100</v>
+        <v>20896886</v>
       </c>
       <c r="G181" t="n">
-        <v>3695597000</v>
+        <v>9376038000</v>
       </c>
       <c r="H181" t="n">
-        <v>1748.071046781136</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I181" t="n">
-        <v>5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7138,390 +7138,431 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>6232</v>
+        <v>4631</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1499000</v>
+        <v>6563759</v>
       </c>
       <c r="G182" t="n">
-        <v>1369002000</v>
+        <v>16844475000</v>
       </c>
       <c r="H182" t="n">
-        <v>913.2768512341561</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I182" t="n">
-        <v>10.47</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G183" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H183" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I183" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G184" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H184" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I184" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G185" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H185" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I185" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G186" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H186" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I186" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G187" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H187" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G188" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H188" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I188" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G189" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H189" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I189" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G190" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H190" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I190" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>S100RX5R.zip</t>
+          <t>S100RYRP.zip</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>8303</v>
+        <v>5947</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>20000000</v>
+        <v>7446200</v>
       </c>
       <c r="G191" t="n">
-        <v>56014500000</v>
+        <v>21182239000</v>
       </c>
       <c r="H191" t="n">
-        <v>2800.725</v>
+        <v>2844.704547285864</v>
       </c>
       <c r="I191" t="n">
-        <v>9.75</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S100RVIC.zip</t>
+          <t>S100RY2V.zip</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>jplvh030000-lvh-001_E33309-000_2023-09-11_01_2023-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2812</v>
+        <v>5186</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
+        <v>1536900</v>
+      </c>
+      <c r="G192" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H192" t="n">
+        <v>3096.322467304314</v>
+      </c>
       <c r="I192" t="n">
-        <v>9.779999999999999</v>
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>S100RX5R.zip</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>8303</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G193" t="n">
+        <v>56014500000</v>
+      </c>
+      <c r="H193" t="n">
+        <v>2800.725</v>
+      </c>
+      <c r="I193" t="n">
+        <v>9.75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I193"/>
+  <dimension ref="A1:I195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,12 +762,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S100YR7M.zip</t>
+          <t>S100YR7O.zip</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3864</v>
+        <v>9831</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>81000</v>
+        <v>53000</v>
       </c>
       <c r="H10" t="n">
-        <v>810</v>
+        <v>530</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -799,12 +799,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S100YR7O.zip</t>
+          <t>S100YR7M.zip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2026-07-13_01_2026-07-21.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-07-13_01_2026-07-21.csv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9831</v>
+        <v>3864</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>53000</v>
+        <v>81000</v>
       </c>
       <c r="H11" t="n">
-        <v>530</v>
+        <v>810</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1391,21 +1391,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100Y2BG.zip</t>
+          <t>S100Y2OE.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7244</v>
+        <v>3863</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1413,36 +1413,36 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5197900</v>
+        <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>2856142000</v>
+        <v>125000</v>
       </c>
       <c r="H27" t="n">
-        <v>549.4799823005444</v>
+        <v>1250</v>
       </c>
       <c r="I27" t="n">
-        <v>5.390000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100Y2OE.zip</t>
+          <t>S100Y2B5.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3863</v>
+        <v>7004</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>100</v>
+        <v>9267600</v>
       </c>
       <c r="G28" t="n">
-        <v>125000</v>
+        <v>9449965000</v>
       </c>
       <c r="H28" t="n">
-        <v>1250</v>
+        <v>1019.677694332945</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100Y2B5.zip</t>
+          <t>S100Y2BG.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7004</v>
+        <v>7244</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1487,16 +1487,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9267600</v>
+        <v>5197900</v>
       </c>
       <c r="G29" t="n">
-        <v>9449965000</v>
+        <v>2856142000</v>
       </c>
       <c r="H29" t="n">
-        <v>1019.677694332945</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="I29" t="n">
-        <v>5.44</v>
+        <v>5.390000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1724,21 +1724,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5423</v>
+        <v>6952</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1746,36 +1746,36 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6884398</v>
+        <v>11964800</v>
       </c>
       <c r="G36" t="n">
-        <v>11052572000</v>
+        <v>14335634000</v>
       </c>
       <c r="H36" t="n">
-        <v>1605.452212379354</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I36" t="n">
-        <v>6.25</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6952</v>
+        <v>5423</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1783,36 +1783,36 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>11964800</v>
+        <v>6884398</v>
       </c>
       <c r="G37" t="n">
-        <v>14335634000</v>
+        <v>11052572000</v>
       </c>
       <c r="H37" t="n">
-        <v>1198.150742177053</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I37" t="n">
-        <v>5.029999999999999</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9468</v>
+        <v>4676</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1820,36 +1820,36 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>13197300</v>
+        <v>2662900</v>
       </c>
       <c r="G38" t="n">
-        <v>39531520000</v>
+        <v>8365298000</v>
       </c>
       <c r="H38" t="n">
-        <v>2995.424821743842</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I38" t="n">
-        <v>8.859999999999999</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4676</v>
+        <v>9468</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1857,16 +1857,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2662900</v>
+        <v>13197300</v>
       </c>
       <c r="G39" t="n">
-        <v>8365298000</v>
+        <v>39531520000</v>
       </c>
       <c r="H39" t="n">
-        <v>3141.424011416125</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I39" t="n">
-        <v>1.57</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1909,49 +1909,49 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100Z2V7.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-03-09_02_2026-09-24.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6594</v>
+        <v>4189</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>80322406</v>
+        <v>4878200</v>
       </c>
       <c r="G41" t="n">
-        <v>178330543000</v>
+        <v>13041315000</v>
       </c>
       <c r="H41" t="n">
-        <v>2220.184278344451</v>
+        <v>2673.3867000123</v>
       </c>
       <c r="I41" t="n">
-        <v>6.74</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1960,220 +1960,220 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1721</v>
+        <v>6594</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7462000</v>
+        <v>80322406</v>
       </c>
       <c r="G42" t="n">
-        <v>27875864000</v>
+        <v>178330543000</v>
       </c>
       <c r="H42" t="n">
-        <v>3735.709461270437</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I42" t="n">
-        <v>5.609999999999999</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100Z2JM.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-17_02_2026-09-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4189</v>
+        <v>1721</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4476500</v>
+        <v>7462000</v>
       </c>
       <c r="G43" t="n">
-        <v>11865379000</v>
+        <v>27875864000</v>
       </c>
       <c r="H43" t="n">
-        <v>2650.592873897018</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I43" t="n">
-        <v>12.05</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100Z2US.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-19_02_2026-09-24.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6675</v>
+        <v>4189</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>314400</v>
+        <v>4482100</v>
       </c>
       <c r="G44" t="n">
-        <v>1717778000</v>
+        <v>11882173000</v>
       </c>
       <c r="H44" t="n">
-        <v>5463.67048346056</v>
+        <v>2651.028089511613</v>
       </c>
       <c r="I44" t="n">
-        <v>5.029999999999999</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100Z2JM.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-17_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3549</v>
+        <v>4189</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>13408159</v>
+        <v>4476500</v>
       </c>
       <c r="G45" t="n">
-        <v>40855887000</v>
+        <v>11865379000</v>
       </c>
       <c r="H45" t="n">
-        <v>3047.091476167608</v>
+        <v>2650.592873897018</v>
       </c>
       <c r="I45" t="n">
-        <v>14.02</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100Z2IH.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-09_02_2026-09-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4189</v>
+        <v>6675</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4054500</v>
+        <v>314400</v>
       </c>
       <c r="G46" t="n">
-        <v>10605706000</v>
+        <v>1717778000</v>
       </c>
       <c r="H46" t="n">
-        <v>2615.786410161549</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I46" t="n">
-        <v>10.91</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100Z1ZH.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3765</v>
+        <v>3549</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6673200</v>
+        <v>13408159</v>
       </c>
       <c r="G47" t="n">
-        <v>19362129000</v>
+        <v>40855887000</v>
       </c>
       <c r="H47" t="n">
-        <v>2901.475903614458</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I47" t="n">
-        <v>9.65</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100Z2IH.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-09_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2182,35 +2182,35 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7745</v>
+        <v>4189</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1458700</v>
+        <v>4054500</v>
       </c>
       <c r="G48" t="n">
-        <v>3040190000</v>
+        <v>10605706000</v>
       </c>
       <c r="H48" t="n">
-        <v>2084.177692465894</v>
+        <v>2615.786410161549</v>
       </c>
       <c r="I48" t="n">
-        <v>5.24</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100Z2CJ.zip</t>
+          <t>S100Z1ZH.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2219,72 +2219,72 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4189</v>
+        <v>3765</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2917700</v>
+        <v>6673200</v>
       </c>
       <c r="G49" t="n">
-        <v>7487288000</v>
+        <v>19362129000</v>
       </c>
       <c r="H49" t="n">
-        <v>2566.161017239607</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="I49" t="n">
-        <v>7.85</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G50" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H50" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I50" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100Z2BC.zip</t>
+          <t>S100Z2CJ.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2297,57 +2297,57 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2040400</v>
+        <v>2917700</v>
       </c>
       <c r="G51" t="n">
-        <v>5203426000</v>
+        <v>7487288000</v>
       </c>
       <c r="H51" t="n">
-        <v>2550.198980592041</v>
+        <v>2566.161017239607</v>
       </c>
       <c r="I51" t="n">
-        <v>5.489999999999999</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G52" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H52" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I52" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="53">
@@ -2390,271 +2390,271 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100Z2BC.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G54" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H54" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I54" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2972</v>
+        <v>4189</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2040400</v>
       </c>
       <c r="G55" t="n">
-        <v>125000</v>
+        <v>5203426000</v>
       </c>
       <c r="H55" t="n">
-        <v>125000</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G56" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H56" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I56" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100Z1ZC.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3765</v>
+        <v>2972</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>6336400</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>18726232000</v>
+        <v>125000</v>
       </c>
       <c r="H57" t="n">
-        <v>2955.342465753425</v>
+        <v>125000</v>
       </c>
       <c r="I57" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G58" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H58" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I58" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100Z1ZC.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>8233</v>
+        <v>3765</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>261400</v>
+        <v>6336400</v>
       </c>
       <c r="G59" t="n">
-        <v>287906000</v>
+        <v>18726232000</v>
       </c>
       <c r="H59" t="n">
-        <v>1101.400153022188</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2371</v>
+        <v>3106</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>10372003</v>
+        <v>853156</v>
       </c>
       <c r="G60" t="n">
-        <v>24045569000</v>
+        <v>4849339000</v>
       </c>
       <c r="H60" t="n">
-        <v>2318.314890576102</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I60" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2663,368 +2663,368 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2432</v>
+        <v>8233</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>261400</v>
       </c>
       <c r="G61" t="n">
-        <v>226000</v>
+        <v>287906000</v>
       </c>
       <c r="H61" t="n">
-        <v>2260</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7378</v>
+        <v>2371</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>500400</v>
+        <v>10372003</v>
       </c>
       <c r="G62" t="n">
-        <v>698873000</v>
+        <v>24045569000</v>
       </c>
       <c r="H62" t="n">
-        <v>1396.628697042366</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I62" t="n">
-        <v>6.78</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G63" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H63" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6890</v>
+        <v>2432</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4038389</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>15954609000</v>
+        <v>226000</v>
       </c>
       <c r="H64" t="n">
-        <v>3950.736048458928</v>
+        <v>2260</v>
       </c>
       <c r="I64" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9742</v>
+        <v>8570</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1048500</v>
+        <v>11014402</v>
       </c>
       <c r="G65" t="n">
-        <v>1970276000</v>
+        <v>14194389000</v>
       </c>
       <c r="H65" t="n">
-        <v>1879.137815927515</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I65" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G66" t="n">
-        <v>268179335000</v>
+        <v>15954609000</v>
       </c>
       <c r="H66" t="n">
-        <v>16430.4430802409</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I66" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G67" t="n">
-        <v>268179335457000</v>
+        <v>1970276000</v>
       </c>
       <c r="H67" t="n">
-        <v>16430443.10823975</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I67" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G68" t="n">
-        <v>1831405000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H68" t="n">
-        <v>3321.975331035734</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I68" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G69" t="n">
-        <v>49662804000</v>
+        <v>268179335000</v>
       </c>
       <c r="H69" t="n">
-        <v>11879.91675437757</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I69" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1882</v>
+        <v>6856</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1998200</v>
+        <v>4180400</v>
       </c>
       <c r="G70" t="n">
-        <v>2358382000</v>
+        <v>49662804000</v>
       </c>
       <c r="H70" t="n">
-        <v>1180.253227905114</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I70" t="n">
-        <v>3.97</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3033,109 +3033,109 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G71" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H71" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I71" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7940</v>
+        <v>1882</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>100</v>
+        <v>1998200</v>
       </c>
       <c r="G72" t="n">
-        <v>101000</v>
+        <v>2358382000</v>
       </c>
       <c r="H72" t="n">
-        <v>1010</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1882</v>
+        <v>4549</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2528200</v>
+        <v>2546351</v>
       </c>
       <c r="G73" t="n">
-        <v>2984068000</v>
+        <v>4958319000</v>
       </c>
       <c r="H73" t="n">
-        <v>1180.31326635551</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I73" t="n">
-        <v>5.02</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H74" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -3167,49 +3167,49 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2432</v>
+        <v>1882</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G75" t="n">
-        <v>226000</v>
+        <v>2984068000</v>
       </c>
       <c r="H75" t="n">
-        <v>2260</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>100</v>
       </c>
       <c r="G76" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H76" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -3241,12 +3241,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3255,21 +3255,21 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>100</v>
       </c>
       <c r="G77" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H77" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -3278,12 +3278,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3292,294 +3292,294 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G78" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H78" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I78" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2229</v>
+        <v>4917</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>8012900</v>
+        <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>23390757000</v>
+        <v>204000</v>
       </c>
       <c r="H79" t="n">
-        <v>2919.137515755844</v>
+        <v>2040</v>
       </c>
       <c r="I79" t="n">
-        <v>5.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1882</v>
+        <v>8233</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4275700</v>
+        <v>261400</v>
       </c>
       <c r="G80" t="n">
-        <v>5047062000</v>
+        <v>287906000</v>
       </c>
       <c r="H80" t="n">
-        <v>1180.406015389293</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I80" t="n">
-        <v>8.48</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G81" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H81" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I81" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G82" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H82" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I82" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G83" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H83" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I83" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G84" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H84" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I84" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1297500</v>
+        <v>4783700</v>
       </c>
       <c r="G85" t="n">
-        <v>4476090000</v>
+        <v>5646776000</v>
       </c>
       <c r="H85" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I85" t="n">
-        <v>5.23</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3592,68 +3592,68 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5865200</v>
+        <v>5295000</v>
       </c>
       <c r="G86" t="n">
-        <v>6923530000</v>
+        <v>6250386000</v>
       </c>
       <c r="H86" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I86" t="n">
-        <v>11.64</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G87" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H87" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I87" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100Z1UE.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3662,35 +3662,35 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3765</v>
+        <v>1882</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5883300</v>
+        <v>5865200</v>
       </c>
       <c r="G88" t="n">
-        <v>17576858000</v>
+        <v>6923530000</v>
       </c>
       <c r="H88" t="n">
-        <v>2987.584858837727</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I88" t="n">
-        <v>8.51</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3703,31 +3703,31 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>6942800</v>
+        <v>6431400</v>
       </c>
       <c r="G89" t="n">
-        <v>8195680000</v>
+        <v>7591952000</v>
       </c>
       <c r="H89" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I89" t="n">
-        <v>13.78</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z1UE.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3736,35 +3736,35 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1882</v>
+        <v>3765</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>7455900</v>
+        <v>5883300</v>
       </c>
       <c r="G90" t="n">
-        <v>8801415000</v>
+        <v>17576858000</v>
       </c>
       <c r="H90" t="n">
-        <v>1180.463123164206</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="I90" t="n">
-        <v>14.79</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3773,523 +3773,523 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G91" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H91" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I91" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G92" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H92" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I92" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G93" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H93" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G94" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H94" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I94" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G95" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H95" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I95" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G96" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H96" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G97" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H97" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G98" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H98" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I98" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G99" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H99" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I99" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G101" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H101" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I101" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100Z1T1.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3765</v>
+        <v>3328</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>5187300</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>15645357000</v>
-      </c>
-      <c r="H102" t="n">
-        <v>3016.088716673414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G103" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H103" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100Z1T1.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9302</v>
+        <v>3765</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3799000</v>
+        <v>5187300</v>
       </c>
       <c r="G104" t="n">
-        <v>5671170000</v>
+        <v>15645357000</v>
       </c>
       <c r="H104" t="n">
-        <v>1492.806001579363</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="I104" t="n">
-        <v>5.07</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100Z1P1.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3765</v>
+        <v>3106</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4297,27 +4297,27 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5186300</v>
+        <v>900156</v>
       </c>
       <c r="G105" t="n">
-        <v>15642334000</v>
+        <v>4095263000</v>
       </c>
       <c r="H105" t="n">
-        <v>3016.087384069568</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I105" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4326,294 +4326,294 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G106" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H106" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I106" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100Z1P1.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4619</v>
+        <v>3765</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>100</v>
+        <v>5186300</v>
       </c>
       <c r="G107" t="n">
-        <v>119000</v>
+        <v>15642334000</v>
       </c>
       <c r="H107" t="n">
-        <v>1190</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G108" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H108" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G109" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H109" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I109" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G110" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H110" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I110" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G111" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H111" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G112" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H112" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I112" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G113" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H113" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I113" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4622,701 +4622,701 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G114" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H114" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G115" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H115" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I115" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G116" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H116" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I116" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G117" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H117" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I117" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G118" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H118" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I118" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4626</v>
+        <v>4512</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>4670190</v>
+        <v>2137400</v>
       </c>
       <c r="G119" t="n">
-        <v>16652257000</v>
+        <v>620573000</v>
       </c>
       <c r="H119" t="n">
-        <v>3565.648720929983</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I119" t="n">
-        <v>8</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>9987</v>
+        <v>9006</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>3888200</v>
+        <v>30000</v>
       </c>
       <c r="G120" t="n">
-        <v>16086019000</v>
+        <v>34824000</v>
       </c>
       <c r="H120" t="n">
-        <v>4137.137750115735</v>
+        <v>1160.8</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G121" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H121" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I121" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3861</v>
+        <v>4626</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>100</v>
+        <v>4670190</v>
       </c>
       <c r="G122" t="n">
-        <v>59000</v>
+        <v>16652257000</v>
       </c>
       <c r="H122" t="n">
-        <v>590</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G123" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H123" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G124" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H124" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I124" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G125" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H125" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I125" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G126" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H126" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I126" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G127" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H127" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I127" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G128" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H128" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G129" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H129" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I129" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G130" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H130" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I130" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G131" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H131" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I131" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G132" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H132" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I132" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5325,109 +5325,109 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G133" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H133" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I133" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G134" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H134" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I134" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G135" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H135" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I135" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5436,109 +5436,109 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G136" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H136" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I136" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G137" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H137" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G138" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H138" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I138" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>100</v>
       </c>
       <c r="G139" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H139" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -5570,456 +5570,456 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4205</v>
+        <v>4272</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>14426600</v>
+        <v>26855100</v>
       </c>
       <c r="G140" t="n">
-        <v>24829312000</v>
+        <v>29860350000</v>
       </c>
       <c r="H140" t="n">
-        <v>1721.078563209627</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I140" t="n">
-        <v>6.29</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3569</v>
+        <v>6145</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>4271704</v>
+        <v>100</v>
       </c>
       <c r="G141" t="n">
-        <v>5808044000</v>
+        <v>171000</v>
       </c>
       <c r="H141" t="n">
-        <v>1359.655069733296</v>
+        <v>1710</v>
       </c>
       <c r="I141" t="n">
-        <v>6.279999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G142" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H142" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I142" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2327</v>
+        <v>4205</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>9154320</v>
+        <v>14426600</v>
       </c>
       <c r="G143" t="n">
-        <v>23450671000</v>
+        <v>24829312000</v>
       </c>
       <c r="H143" t="n">
-        <v>2561.705402476645</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I143" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G144" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H144" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I144" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G145" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H145" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G146" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H146" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I146" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G147" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H147" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I147" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G148" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H148" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I148" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G149" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H149" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G150" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H150" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I150" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G151" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H151" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6028,44 +6028,44 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4967</v>
+        <v>2168</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>4062075</v>
+        <v>2094200</v>
       </c>
       <c r="G152" t="n">
-        <v>20578848000</v>
+        <v>4445105000</v>
       </c>
       <c r="H152" t="n">
-        <v>5066.092575838703</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>8803</v>
+        <v>4967</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -6073,249 +6073,249 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>100</v>
+        <v>4062075</v>
       </c>
       <c r="G153" t="n">
-        <v>361000</v>
+        <v>8729143000</v>
       </c>
       <c r="H153" t="n">
-        <v>3610</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>9882</v>
+        <v>8803</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2505000</v>
+        <v>100</v>
       </c>
       <c r="G154" t="n">
-        <v>5292086000</v>
+        <v>361000</v>
       </c>
       <c r="H154" t="n">
-        <v>2112.609181636727</v>
+        <v>3610</v>
       </c>
       <c r="I154" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8129</v>
+        <v>4967</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>7258230</v>
+        <v>4062075</v>
       </c>
       <c r="G155" t="n">
-        <v>24720910000</v>
+        <v>20578848000</v>
       </c>
       <c r="H155" t="n">
-        <v>3405.914389596362</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I155" t="n">
-        <v>9.460000000000001</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G156" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H156" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I156" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G157" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H157" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I157" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G158" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H158" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I158" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G159" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H159" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I159" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6324,775 +6324,775 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G160" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H160" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I160" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G161" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H161" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I161" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3591</v>
+        <v>8929</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2846091</v>
+        <v>1260812</v>
       </c>
       <c r="G162" t="n">
-        <v>6888596000</v>
+        <v>1699255000</v>
       </c>
       <c r="H162" t="n">
-        <v>2420.370957920882</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I162" t="n">
-        <v>5.13</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4042</v>
+        <v>7278</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>16459200</v>
+        <v>115400</v>
       </c>
       <c r="G163" t="n">
-        <v>33451116000</v>
+        <v>302115000</v>
       </c>
       <c r="H163" t="n">
-        <v>2032.365850102071</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I163" t="n">
-        <v>5.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4521</v>
+        <v>4042</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>100</v>
+        <v>16459200</v>
       </c>
       <c r="G164" t="n">
-        <v>353000</v>
+        <v>33451116000</v>
       </c>
       <c r="H164" t="n">
-        <v>3530</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>8923</v>
+        <v>3591</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2445600</v>
+        <v>2846091</v>
       </c>
       <c r="G165" t="n">
-        <v>3856031000</v>
+        <v>6888596000</v>
       </c>
       <c r="H165" t="n">
-        <v>1576.721867844292</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I165" t="n">
-        <v>5.02</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G166" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H166" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I166" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G167" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H167" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I167" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G168" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H168" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G169" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H169" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I169" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G170" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H170" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I170" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G171" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H171" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G172" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H172" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I172" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G173" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H173" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I173" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G174" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H174" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G175" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H175" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I175" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G176" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H176" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I176" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G177" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H177" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I177" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G178" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H178" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G179" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H179" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I179" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G180" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H180" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I180" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7101,35 +7101,35 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>4293</v>
+        <v>7315</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>20896886</v>
+        <v>6994900</v>
       </c>
       <c r="G181" t="n">
-        <v>9376038000</v>
+        <v>5874641000</v>
       </c>
       <c r="H181" t="n">
-        <v>448.6811097117532</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I181" t="n">
-        <v>9.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7138,72 +7138,72 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4631</v>
+        <v>4837</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>6563759</v>
+        <v>5428600</v>
       </c>
       <c r="G182" t="n">
-        <v>16844475000</v>
+        <v>4378021000</v>
       </c>
       <c r="H182" t="n">
-        <v>2566.284807227078</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I182" t="n">
-        <v>6.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>5449</v>
+        <v>4631</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2114100</v>
+        <v>6563759</v>
       </c>
       <c r="G183" t="n">
-        <v>3695597000</v>
+        <v>16844475000</v>
       </c>
       <c r="H183" t="n">
-        <v>1748.071046781136</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I183" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7212,356 +7212,430 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>6232</v>
+        <v>4293</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1499000</v>
+        <v>20896886</v>
       </c>
       <c r="G184" t="n">
-        <v>1369002000</v>
+        <v>9376038000</v>
       </c>
       <c r="H184" t="n">
-        <v>913.2768512341561</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I184" t="n">
-        <v>10.47</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G185" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H185" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I185" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G186" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H186" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I186" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G187" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H187" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I187" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G188" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H188" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I188" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G189" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H189" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G190" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H190" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I190" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>5947</v>
+        <v>4023</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>7446200</v>
+        <v>100</v>
       </c>
       <c r="G191" t="n">
-        <v>21182239000</v>
+        <v>796000</v>
       </c>
       <c r="H191" t="n">
-        <v>2844.704547285864</v>
+        <v>7960</v>
       </c>
       <c r="I191" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5186</v>
+        <v>5844</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1536900</v>
+        <v>4998800</v>
       </c>
       <c r="G192" t="n">
-        <v>4758738000</v>
+        <v>24949147000</v>
       </c>
       <c r="H192" t="n">
-        <v>3096.322467304314</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I192" t="n">
-        <v>5.08</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>S100RY2V.zip</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>5186</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1536900</v>
+      </c>
+      <c r="G193" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H193" t="n">
+        <v>3096.322467304314</v>
+      </c>
+      <c r="I193" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>S100RYRP.zip</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>5947</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>7446200</v>
+      </c>
+      <c r="G194" t="n">
+        <v>21182239000</v>
+      </c>
+      <c r="H194" t="n">
+        <v>2844.704547285864</v>
+      </c>
+      <c r="I194" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
           <t>S100RX5R.zip</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
-      <c r="D193" t="n">
+      <c r="D195" t="n">
         <v>8303</v>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>2023-09-21</t>
         </is>
       </c>
-      <c r="F193" t="n">
+      <c r="F195" t="n">
         <v>20000000</v>
       </c>
-      <c r="G193" t="n">
+      <c r="G195" t="n">
         <v>56014500000</v>
       </c>
-      <c r="H193" t="n">
+      <c r="H195" t="n">
         <v>2800.725</v>
       </c>
-      <c r="I193" t="n">
+      <c r="I195" t="n">
         <v>9.75</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I195"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,95 +1687,95 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100XW5T.zip</t>
+          <t>S100Z3CL.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-03-31_02_2026-09-25.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4613</v>
+        <v>4189</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8982300</v>
+        <v>5704800</v>
       </c>
       <c r="G35" t="n">
-        <v>21391558000</v>
+        <v>15430630000</v>
       </c>
       <c r="H35" t="n">
-        <v>2381.523440544182</v>
+        <v>2704.850301500491</v>
       </c>
       <c r="I35" t="n">
-        <v>5.050000000000001</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6952</v>
+        <v>4613</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11964800</v>
+        <v>8982300</v>
       </c>
       <c r="G36" t="n">
-        <v>14335634000</v>
+        <v>21391558000</v>
       </c>
       <c r="H36" t="n">
-        <v>1198.150742177053</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I36" t="n">
-        <v>5.029999999999999</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5423</v>
+        <v>6952</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1783,73 +1783,73 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6884398</v>
+        <v>11964800</v>
       </c>
       <c r="G37" t="n">
-        <v>11052572000</v>
+        <v>14335634000</v>
       </c>
       <c r="H37" t="n">
-        <v>1605.452212379354</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I37" t="n">
-        <v>6.25</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4676</v>
+        <v>5423</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2662900</v>
+        <v>6884398</v>
       </c>
       <c r="G38" t="n">
-        <v>8365298000</v>
+        <v>11052572000</v>
       </c>
       <c r="H38" t="n">
-        <v>3141.424011416125</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I38" t="n">
-        <v>1.57</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9468</v>
+        <v>4676</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1857,397 +1857,397 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>13197300</v>
+        <v>2662900</v>
       </c>
       <c r="G39" t="n">
-        <v>39531520000</v>
+        <v>8365298000</v>
       </c>
       <c r="H39" t="n">
-        <v>2995.424821743842</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I39" t="n">
-        <v>8.859999999999999</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3132</v>
+        <v>9468</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14653542</v>
+        <v>13197300</v>
       </c>
       <c r="G40" t="n">
-        <v>23038030000</v>
+        <v>39531520000</v>
       </c>
       <c r="H40" t="n">
-        <v>1572.181660925393</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I40" t="n">
-        <v>8.18</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100Z2V7.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-03-09_02_2026-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4189</v>
+        <v>3132</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4878200</v>
+        <v>14653542</v>
       </c>
       <c r="G41" t="n">
-        <v>13041315000</v>
+        <v>23038030000</v>
       </c>
       <c r="H41" t="n">
-        <v>2673.3867000123</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I41" t="n">
-        <v>13.13</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100Z3AR.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-03-10_02_2026-09-25.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6594</v>
+        <v>4189</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>80322406</v>
+        <v>5332700</v>
       </c>
       <c r="G42" t="n">
-        <v>178330543000</v>
+        <v>14369804000</v>
       </c>
       <c r="H42" t="n">
-        <v>2220.184278344451</v>
+        <v>2694.658240666079</v>
       </c>
       <c r="I42" t="n">
-        <v>6.74</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100Z2V7.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-03-09_02_2026-09-24.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1721</v>
+        <v>4189</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>7462000</v>
+        <v>4878200</v>
       </c>
       <c r="G43" t="n">
-        <v>27875864000</v>
+        <v>13041315000</v>
       </c>
       <c r="H43" t="n">
-        <v>3735.709461270437</v>
+        <v>2673.3867000123</v>
       </c>
       <c r="I43" t="n">
-        <v>5.609999999999999</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100Z2US.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-19_02_2026-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4189</v>
+        <v>6594</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4482100</v>
+        <v>80322406</v>
       </c>
       <c r="G44" t="n">
-        <v>11882173000</v>
+        <v>178330543000</v>
       </c>
       <c r="H44" t="n">
-        <v>2651.028089511613</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I44" t="n">
-        <v>12.07</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100Z2JM.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-17_02_2026-09-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4189</v>
+        <v>1721</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4476500</v>
+        <v>7462000</v>
       </c>
       <c r="G45" t="n">
-        <v>11865379000</v>
+        <v>27875864000</v>
       </c>
       <c r="H45" t="n">
-        <v>2650.592873897018</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I45" t="n">
-        <v>12.05</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100Z2US.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-19_02_2026-09-24.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6675</v>
+        <v>4189</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>314400</v>
+        <v>4482100</v>
       </c>
       <c r="G46" t="n">
-        <v>1717778000</v>
+        <v>11882173000</v>
       </c>
       <c r="H46" t="n">
-        <v>5463.67048346056</v>
+        <v>2651.028089511613</v>
       </c>
       <c r="I46" t="n">
-        <v>5.029999999999999</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100Z2JM.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-17_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3549</v>
+        <v>4189</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>13408159</v>
+        <v>4476500</v>
       </c>
       <c r="G47" t="n">
-        <v>40855887000</v>
+        <v>11865379000</v>
       </c>
       <c r="H47" t="n">
-        <v>3047.091476167608</v>
+        <v>2650.592873897018</v>
       </c>
       <c r="I47" t="n">
-        <v>14.02</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100Z2IH.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-09_02_2026-09-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4189</v>
+        <v>6675</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4054500</v>
+        <v>314400</v>
       </c>
       <c r="G48" t="n">
-        <v>10605706000</v>
+        <v>1717778000</v>
       </c>
       <c r="H48" t="n">
-        <v>2615.786410161549</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I48" t="n">
-        <v>10.91</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100Z1ZH.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3765</v>
+        <v>3549</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6673200</v>
+        <v>13408159</v>
       </c>
       <c r="G49" t="n">
-        <v>19362129000</v>
+        <v>40855887000</v>
       </c>
       <c r="H49" t="n">
-        <v>2901.475903614458</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I49" t="n">
-        <v>9.65</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100Z2IH.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-09_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2256,35 +2256,35 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7745</v>
+        <v>4189</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1458700</v>
+        <v>4054500</v>
       </c>
       <c r="G50" t="n">
-        <v>3040190000</v>
+        <v>10605706000</v>
       </c>
       <c r="H50" t="n">
-        <v>2084.177692465894</v>
+        <v>2615.786410161549</v>
       </c>
       <c r="I50" t="n">
-        <v>5.24</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100Z2CJ.zip</t>
+          <t>S100Z1ZH.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2293,72 +2293,72 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4189</v>
+        <v>3765</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2917700</v>
+        <v>6673200</v>
       </c>
       <c r="G51" t="n">
-        <v>7487288000</v>
+        <v>19362129000</v>
       </c>
       <c r="H51" t="n">
-        <v>2566.161017239607</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="I51" t="n">
-        <v>7.85</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G52" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H52" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I52" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100Z1ZF.zip</t>
+          <t>S100Z2CJ.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2367,72 +2367,72 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3765</v>
+        <v>4189</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6600700</v>
+        <v>2917700</v>
       </c>
       <c r="G53" t="n">
-        <v>19175476000</v>
+        <v>7487288000</v>
       </c>
       <c r="H53" t="n">
-        <v>2905.067038344418</v>
+        <v>2566.161017239607</v>
       </c>
       <c r="I53" t="n">
-        <v>9.539999999999999</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100Z2BC.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G54" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H54" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I54" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100Z1ZF.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4189</v>
+        <v>3765</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2449,656 +2449,656 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2040400</v>
+        <v>6600700</v>
       </c>
       <c r="G55" t="n">
-        <v>5203426000</v>
+        <v>19175476000</v>
       </c>
       <c r="H55" t="n">
-        <v>2550.198980592041</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="I55" t="n">
-        <v>5.489999999999999</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100Z2BC.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G56" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H56" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I56" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2972</v>
+        <v>4189</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>2040400</v>
       </c>
       <c r="G57" t="n">
-        <v>125000</v>
+        <v>5203426000</v>
       </c>
       <c r="H57" t="n">
-        <v>125000</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G58" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H58" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I58" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100Z1ZC.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3765</v>
+        <v>2972</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>6336400</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>18726232000</v>
+        <v>125000</v>
       </c>
       <c r="H59" t="n">
-        <v>2955.342465753425</v>
+        <v>125000</v>
       </c>
       <c r="I59" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G60" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H60" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I60" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100Z1ZC.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8233</v>
+        <v>3765</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>261400</v>
+        <v>6336400</v>
       </c>
       <c r="G61" t="n">
-        <v>287906000</v>
+        <v>18726232000</v>
       </c>
       <c r="H61" t="n">
-        <v>1101.400153022188</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="I61" t="n">
-        <v>0.08</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2371</v>
+        <v>3106</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>10372003</v>
+        <v>853156</v>
       </c>
       <c r="G62" t="n">
-        <v>24045569000</v>
+        <v>4849339000</v>
       </c>
       <c r="H62" t="n">
-        <v>2318.314890576102</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I62" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7378</v>
+        <v>8233</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>500400</v>
+        <v>261400</v>
       </c>
       <c r="G63" t="n">
-        <v>698873000</v>
+        <v>287906000</v>
       </c>
       <c r="H63" t="n">
-        <v>1396.628697042366</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I63" t="n">
-        <v>6.78</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G64" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H64" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G65" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H65" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6890</v>
+        <v>2432</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4038389</v>
+        <v>100</v>
       </c>
       <c r="G66" t="n">
-        <v>15954609000</v>
+        <v>226000</v>
       </c>
       <c r="H66" t="n">
-        <v>3950.736048458928</v>
+        <v>2260</v>
       </c>
       <c r="I66" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>9742</v>
+        <v>8570</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1048500</v>
+        <v>11014402</v>
       </c>
       <c r="G67" t="n">
-        <v>1970276000</v>
+        <v>14194389000</v>
       </c>
       <c r="H67" t="n">
-        <v>1879.137815927515</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I67" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G68" t="n">
-        <v>268179335457000</v>
+        <v>15954609000</v>
       </c>
       <c r="H68" t="n">
-        <v>16430443.10823975</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I68" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G69" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H69" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I69" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G70" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H70" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I70" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G71" t="n">
-        <v>1831405000</v>
+        <v>268179335000</v>
       </c>
       <c r="H71" t="n">
-        <v>3321.975331035734</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I71" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1882</v>
+        <v>6856</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1998200</v>
+        <v>4180400</v>
       </c>
       <c r="G72" t="n">
-        <v>2358382000</v>
+        <v>49662804000</v>
       </c>
       <c r="H72" t="n">
-        <v>1180.253227905114</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I72" t="n">
-        <v>3.97</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3107,109 +3107,109 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G73" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H73" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I73" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7940</v>
+        <v>1882</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>100</v>
+        <v>1998200</v>
       </c>
       <c r="G74" t="n">
-        <v>101000</v>
+        <v>2358382000</v>
       </c>
       <c r="H74" t="n">
-        <v>1010</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1882</v>
+        <v>4549</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2528200</v>
+        <v>2546351</v>
       </c>
       <c r="G75" t="n">
-        <v>2984068000</v>
+        <v>4958319000</v>
       </c>
       <c r="H75" t="n">
-        <v>1180.31326635551</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I75" t="n">
-        <v>5.02</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>100</v>
       </c>
       <c r="G76" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H76" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -3241,49 +3241,49 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2432</v>
+        <v>1882</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G77" t="n">
-        <v>226000</v>
+        <v>2984068000</v>
       </c>
       <c r="H77" t="n">
-        <v>2260</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3292,21 +3292,21 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>100</v>
       </c>
       <c r="G78" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H78" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -3315,12 +3315,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H79" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3366,294 +3366,294 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G80" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H80" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1882</v>
+        <v>4917</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4275700</v>
+        <v>100</v>
       </c>
       <c r="G81" t="n">
-        <v>5047062000</v>
+        <v>204000</v>
       </c>
       <c r="H81" t="n">
-        <v>1180.406015389293</v>
+        <v>2040</v>
       </c>
       <c r="I81" t="n">
-        <v>8.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2229</v>
+        <v>8233</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>8012900</v>
+        <v>261400</v>
       </c>
       <c r="G82" t="n">
-        <v>23390757000</v>
+        <v>287906000</v>
       </c>
       <c r="H82" t="n">
-        <v>2919.137515755844</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I82" t="n">
-        <v>5.98</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100WOYY.zip</t>
+          <t>S100Z0TS.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5983</v>
+        <v>1882</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>44800</v>
+        <v>4275700</v>
       </c>
       <c r="G83" t="n">
-        <v>315399000</v>
+        <v>5047062000</v>
       </c>
       <c r="H83" t="n">
-        <v>7040.15625</v>
+        <v>1180.406015389293</v>
       </c>
       <c r="I83" t="n">
-        <v>4.07</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100WO50.zip</t>
+          <t>S100WO9C.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5983</v>
+        <v>2229</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>44800</v>
+        <v>8012900</v>
       </c>
       <c r="G84" t="n">
-        <v>315399000</v>
+        <v>23390757000</v>
       </c>
       <c r="H84" t="n">
-        <v>7040.15625</v>
+        <v>2919.137515755844</v>
       </c>
       <c r="I84" t="n">
-        <v>4.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S100Z0RN.zip</t>
+          <t>S100WOYY.zip</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-17.csv</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4783700</v>
+        <v>44800</v>
       </c>
       <c r="G85" t="n">
-        <v>5646776000</v>
+        <v>315399000</v>
       </c>
       <c r="H85" t="n">
-        <v>1180.420176850555</v>
+        <v>7040.15625</v>
       </c>
       <c r="I85" t="n">
-        <v>9.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S100Z09M.zip</t>
+          <t>S100WO50.zip</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E40869-000_2025-09-05_01_2025-09-12.csv</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ＳＥＮＪＩＮ　ＣＡＰＩＴＡＬ　ＰＴＹ　ＬＴＤ</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1882</v>
+        <v>5983</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5295000</v>
+        <v>44800</v>
       </c>
       <c r="G86" t="n">
-        <v>6250386000</v>
+        <v>315399000</v>
       </c>
       <c r="H86" t="n">
-        <v>1180.431728045326</v>
+        <v>7040.15625</v>
       </c>
       <c r="I86" t="n">
-        <v>10.51</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S100WKF3.zip</t>
+          <t>S100Z0RN.zip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-09-04_02_2026-09-09.csv</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6104</v>
+        <v>1882</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1297500</v>
+        <v>4783700</v>
       </c>
       <c r="G87" t="n">
-        <v>4476090000</v>
+        <v>5646776000</v>
       </c>
       <c r="H87" t="n">
-        <v>3449.780346820809</v>
+        <v>1180.420176850555</v>
       </c>
       <c r="I87" t="n">
-        <v>5.23</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S100Z080.zip</t>
+          <t>S100Z09M.zip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-26_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3666,68 +3666,68 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5865200</v>
+        <v>5295000</v>
       </c>
       <c r="G88" t="n">
-        <v>6923530000</v>
+        <v>6250386000</v>
       </c>
       <c r="H88" t="n">
-        <v>1180.442269658324</v>
+        <v>1180.431728045326</v>
       </c>
       <c r="I88" t="n">
-        <v>11.64</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S100Z092.zip</t>
+          <t>S100WKF3.zip</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-08-19_01_2025-08-22.csv</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1882</v>
+        <v>6104</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>6431400</v>
+        <v>1297500</v>
       </c>
       <c r="G89" t="n">
-        <v>7591952000</v>
+        <v>4476090000</v>
       </c>
       <c r="H89" t="n">
-        <v>1180.450912709519</v>
+        <v>3449.780346820809</v>
       </c>
       <c r="I89" t="n">
-        <v>12.76</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S100Z1UE.zip</t>
+          <t>S100Z080.zip</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-13_02_2026-09-08.csv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3736,35 +3736,35 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3765</v>
+        <v>1882</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5883300</v>
+        <v>5865200</v>
       </c>
       <c r="G90" t="n">
-        <v>17576858000</v>
+        <v>6923530000</v>
       </c>
       <c r="H90" t="n">
-        <v>2987.584858837727</v>
+        <v>1180.442269658324</v>
       </c>
       <c r="I90" t="n">
-        <v>8.51</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S100Z07P.zip</t>
+          <t>S100Z092.zip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-08-04_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3777,31 +3777,31 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6942800</v>
+        <v>6431400</v>
       </c>
       <c r="G91" t="n">
-        <v>8195680000</v>
+        <v>7591952000</v>
       </c>
       <c r="H91" t="n">
-        <v>1180.45745232471</v>
+        <v>1180.450912709519</v>
       </c>
       <c r="I91" t="n">
-        <v>13.78</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S100Z034.zip</t>
+          <t>S100Z1UE.zip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-31_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3810,35 +3810,35 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1882</v>
+        <v>3765</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>7455900</v>
+        <v>5883300</v>
       </c>
       <c r="G92" t="n">
-        <v>8801415000</v>
+        <v>17576858000</v>
       </c>
       <c r="H92" t="n">
-        <v>1180.463123164206</v>
+        <v>2987.584858837727</v>
       </c>
       <c r="I92" t="n">
-        <v>14.79</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S100WCIP.zip</t>
+          <t>S100Z07P.zip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-28_02_2026-09-07.csv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3847,523 +3847,523 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5331</v>
+        <v>1882</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1481600</v>
+        <v>6942800</v>
       </c>
       <c r="G93" t="n">
-        <v>5294365000</v>
+        <v>8195680000</v>
       </c>
       <c r="H93" t="n">
-        <v>3573.410502159827</v>
+        <v>1180.45745232471</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S100WB2Y.zip</t>
+          <t>S100Z034.zip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-11_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6952</v>
+        <v>1882</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>12332900</v>
+        <v>7455900</v>
       </c>
       <c r="G94" t="n">
-        <v>14653495000</v>
+        <v>8801415000</v>
       </c>
       <c r="H94" t="n">
-        <v>1188.162962482466</v>
+        <v>1180.463123164206</v>
       </c>
       <c r="I94" t="n">
-        <v>5.19</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S100WAVT.zip</t>
+          <t>S100WCIP.zip</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-07-10_01_2025-07-17.csv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6145</v>
+        <v>5331</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>100</v>
+        <v>1481600</v>
       </c>
       <c r="G95" t="n">
-        <v>171000</v>
+        <v>5294365000</v>
       </c>
       <c r="H95" t="n">
-        <v>1710</v>
+        <v>3573.410502159827</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S100WACZ.zip</t>
+          <t>S100WB2Y.zip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-07-02_01_2025-07-09.csv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>8715</v>
+        <v>6952</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3810400</v>
+        <v>12332900</v>
       </c>
       <c r="G96" t="n">
-        <v>2500615000</v>
+        <v>14653495000</v>
       </c>
       <c r="H96" t="n">
-        <v>656.2604975855553</v>
+        <v>1188.162962482466</v>
       </c>
       <c r="I96" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S100W5LT.zip</t>
+          <t>S100WAVT.zip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-30_01_2025-07-07.csv</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>8585</v>
+        <v>6145</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>8986800</v>
+        <v>100</v>
       </c>
       <c r="G97" t="n">
-        <v>7174886000</v>
+        <v>171000</v>
       </c>
       <c r="H97" t="n">
-        <v>798.3805136422309</v>
+        <v>1710</v>
       </c>
       <c r="I97" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S100W435.zip</t>
+          <t>S100WACZ.zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-06-26_01_2025-07-03.csv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6908</v>
+        <v>8715</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>400</v>
+        <v>3810400</v>
       </c>
       <c r="G98" t="n">
-        <v>992000</v>
+        <v>2500615000</v>
       </c>
       <c r="H98" t="n">
-        <v>2480</v>
+        <v>656.2604975855553</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S100VV1I.zip</t>
+          <t>S100W5LT.zip</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-06-24_01_2025-07-01.csv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8923</v>
+        <v>8585</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2434800</v>
+        <v>8986800</v>
       </c>
       <c r="G99" t="n">
-        <v>4266809000</v>
+        <v>7174886000</v>
       </c>
       <c r="H99" t="n">
-        <v>1752.426893379333</v>
+        <v>798.3805136422309</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S100VUUK.zip</t>
+          <t>S100W435.zip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-06-19_01_2025-06-26.csv</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>9069</v>
+        <v>6908</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>8793900</v>
+        <v>400</v>
       </c>
       <c r="G100" t="n">
-        <v>13684104000</v>
+        <v>992000</v>
       </c>
       <c r="H100" t="n">
-        <v>1556.090471804319</v>
+        <v>2480</v>
       </c>
       <c r="I100" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S100VT64.zip</t>
+          <t>S100VV1I.zip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-29_01_2025-06-05.csv</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1878</v>
+        <v>8923</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3475000</v>
+        <v>2434800</v>
       </c>
       <c r="G101" t="n">
-        <v>47745269000</v>
+        <v>4266809000</v>
       </c>
       <c r="H101" t="n">
-        <v>13739.64575539568</v>
+        <v>1752.426893379333</v>
       </c>
       <c r="I101" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S100VRQO.zip</t>
+          <t>S100VUUK.zip</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-28_01_2025-06-04.csv</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3328</v>
+        <v>9069</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>8793900</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>13684104000</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1556.090471804319</v>
+      </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S100VQJZ.zip</t>
+          <t>S100VT64.zip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-05-22_01_2025-05-23.csv</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3076</v>
+        <v>1878</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2841700</v>
+        <v>3475000</v>
       </c>
       <c r="G103" t="n">
-        <v>5705436000</v>
+        <v>47745269000</v>
       </c>
       <c r="H103" t="n">
-        <v>2007.754513143541</v>
+        <v>13739.64575539568</v>
       </c>
       <c r="I103" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S100Z1T1.zip</t>
+          <t>S100VRQO.zip</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
+          <t>jplvh020000-lvh-001_E34595-000_2025-05-07_02_2025-05-16.csv</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3765</v>
+        <v>3328</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>5187300</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>15645357000</v>
-      </c>
-      <c r="H104" t="n">
-        <v>3016.088716673414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S100VP86.zip</t>
+          <t>S100VQJZ.zip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-05-02_01_2025-05-13.csv</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3106</v>
+        <v>3076</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>900156</v>
+        <v>2841700</v>
       </c>
       <c r="G105" t="n">
-        <v>4095263000</v>
+        <v>5705436000</v>
       </c>
       <c r="H105" t="n">
-        <v>4549.503641591014</v>
+        <v>2007.754513143541</v>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S100VPVZ.zip</t>
+          <t>S100Z1T1.zip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-05-01_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9302</v>
+        <v>3765</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3799000</v>
+        <v>5187300</v>
       </c>
       <c r="G106" t="n">
-        <v>5671170000</v>
+        <v>15645357000</v>
       </c>
       <c r="H106" t="n">
-        <v>1492.806001579363</v>
+        <v>3016.088716673414</v>
       </c>
       <c r="I106" t="n">
-        <v>5.07</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S100Z1P1.zip</t>
+          <t>S100VP86.zip</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3765</v>
+        <v>3106</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4371,27 +4371,27 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>5186300</v>
+        <v>900156</v>
       </c>
       <c r="G107" t="n">
-        <v>15642334000</v>
+        <v>4095263000</v>
       </c>
       <c r="H107" t="n">
-        <v>3016.087384069568</v>
+        <v>4549.503641591014</v>
       </c>
       <c r="I107" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S100VONW.zip</t>
+          <t>S100VPVZ.zip</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-28_01_2025-05-08.csv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4400,294 +4400,294 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>9684</v>
+        <v>9302</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>6704059</v>
+        <v>3799000</v>
       </c>
       <c r="G108" t="n">
-        <v>42054369000</v>
+        <v>5671170000</v>
       </c>
       <c r="H108" t="n">
-        <v>6272.971195510064</v>
+        <v>1492.806001579363</v>
       </c>
       <c r="I108" t="n">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S100VLU2.zip</t>
+          <t>S100Z1P1.zip</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-04-28_02_2026-09-15.csv</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4619</v>
+        <v>3765</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>100</v>
+        <v>5186300</v>
       </c>
       <c r="G109" t="n">
-        <v>119000</v>
+        <v>15642334000</v>
       </c>
       <c r="H109" t="n">
-        <v>1190</v>
+        <v>3016.087384069568</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S100VLGK.zip</t>
+          <t>S100VONW.zip</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2025-04-21_01_2025-04-28.csv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6332</v>
+        <v>9684</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>100</v>
+        <v>6704059</v>
       </c>
       <c r="G110" t="n">
-        <v>141000</v>
+        <v>42054369000</v>
       </c>
       <c r="H110" t="n">
-        <v>1410</v>
+        <v>6272.971195510064</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S100VJXU.zip</t>
+          <t>S100VLU2.zip</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-07_01_2025-04-14.csv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4849</v>
+        <v>4619</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2946942</v>
+        <v>100</v>
       </c>
       <c r="G111" t="n">
-        <v>5148132000</v>
+        <v>119000</v>
       </c>
       <c r="H111" t="n">
-        <v>1746.940387696806</v>
+        <v>1190</v>
       </c>
       <c r="I111" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S100VJZS.zip</t>
+          <t>S100VLGK.zip</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-04-04_01_2025-04-11.csv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6927</v>
+        <v>6332</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1142700</v>
+        <v>100</v>
       </c>
       <c r="G112" t="n">
-        <v>1023871000</v>
+        <v>141000</v>
       </c>
       <c r="H112" t="n">
-        <v>896.0103264198827</v>
+        <v>1410</v>
       </c>
       <c r="I112" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S100VJYW.zip</t>
+          <t>S100VJXU.zip</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>株式会社レノ代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>4676</v>
+        <v>4849</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>100</v>
+        <v>2946942</v>
       </c>
       <c r="G113" t="n">
-        <v>242000</v>
+        <v>5148132000</v>
       </c>
       <c r="H113" t="n">
-        <v>2420</v>
+        <v>1746.940387696806</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S100VIX7.zip</t>
+          <t>S100VJZS.zip</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-31_01_2025-04-07.csv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1776</v>
+        <v>6927</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>126500</v>
+        <v>1142700</v>
       </c>
       <c r="G114" t="n">
-        <v>153399000</v>
+        <v>1023871000</v>
       </c>
       <c r="H114" t="n">
-        <v>1212.640316205534</v>
+        <v>896.0103264198827</v>
       </c>
       <c r="I114" t="n">
-        <v>1.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S100VFPV.zip</t>
+          <t>S100VJYW.zip</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
+          <t>jplvh010000-lvh-001_E24231-000_2025-03-27_01_2025-04-03.csv</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社レノ代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3963</v>
+        <v>4676</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1507900</v>
+        <v>100</v>
       </c>
       <c r="G115" t="n">
-        <v>635874000</v>
+        <v>242000</v>
       </c>
       <c r="H115" t="n">
-        <v>421.6950726175476</v>
+        <v>2420</v>
       </c>
       <c r="I115" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S100VF2W.zip</t>
+          <t>S100VIX7.zip</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-25_01_2025-04-01.csv</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4696,701 +4696,701 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6923</v>
+        <v>1776</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>100</v>
+        <v>126500</v>
       </c>
       <c r="G116" t="n">
-        <v>256000</v>
+        <v>153399000</v>
       </c>
       <c r="H116" t="n">
-        <v>2560</v>
+        <v>1212.640316205534</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S100VE1G.zip</t>
+          <t>S100VFPV.zip</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-03-19_01_2025-03-27.csv</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6890</v>
+        <v>3963</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>30000</v>
+        <v>1507900</v>
       </c>
       <c r="G117" t="n">
-        <v>71610000</v>
+        <v>635874000</v>
       </c>
       <c r="H117" t="n">
-        <v>2387</v>
+        <v>421.6950726175476</v>
       </c>
       <c r="I117" t="n">
-        <v>0.06</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S100VCMT.zip</t>
+          <t>S100VF2W.zip</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-12_01_2025-03-19.csv</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>3132</v>
+        <v>6923</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>8970900</v>
+        <v>100</v>
       </c>
       <c r="G118" t="n">
-        <v>10240398000</v>
+        <v>256000</v>
       </c>
       <c r="H118" t="n">
-        <v>1141.512891683109</v>
+        <v>2560</v>
       </c>
       <c r="I118" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S100VAJU.zip</t>
+          <t>S100VE1G.zip</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-03-07_01_2025-03-14.csv</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4512</v>
+        <v>6890</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2137400</v>
+        <v>30000</v>
       </c>
       <c r="G119" t="n">
-        <v>620573000</v>
+        <v>71610000</v>
       </c>
       <c r="H119" t="n">
-        <v>290.3401328717133</v>
+        <v>2387</v>
       </c>
       <c r="I119" t="n">
-        <v>6.140000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S100V9Z0.zip</t>
+          <t>S100VCMT.zip</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2025-03-03_01_2025-03-10.csv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>9006</v>
+        <v>3132</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>30000</v>
+        <v>8970900</v>
       </c>
       <c r="G120" t="n">
-        <v>34824000</v>
+        <v>10240398000</v>
       </c>
       <c r="H120" t="n">
-        <v>1160.8</v>
+        <v>1141.512891683109</v>
       </c>
       <c r="I120" t="n">
-        <v>0.01</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S100V827.zip</t>
+          <t>S100VAJU.zip</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-02-19_01_2025-02-27.csv</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9987</v>
+        <v>4512</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3888200</v>
+        <v>2137400</v>
       </c>
       <c r="G121" t="n">
-        <v>16086019000</v>
+        <v>620573000</v>
       </c>
       <c r="H121" t="n">
-        <v>4137.137750115735</v>
+        <v>290.3401328717133</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>6.140000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S100V7YO.zip</t>
+          <t>S100V9Z0.zip</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-02-13_01_2025-02-20.csv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>4626</v>
+        <v>9006</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>4670190</v>
+        <v>30000</v>
       </c>
       <c r="G122" t="n">
-        <v>16652257000</v>
+        <v>34824000</v>
       </c>
       <c r="H122" t="n">
-        <v>3565.648720929983</v>
+        <v>1160.8</v>
       </c>
       <c r="I122" t="n">
-        <v>8</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S100V45I.zip</t>
+          <t>S100V827.zip</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2025-02-10_01_2025-02-12.csv</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>7732</v>
+        <v>9987</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7995900</v>
+        <v>3888200</v>
       </c>
       <c r="G123" t="n">
-        <v>16678425000</v>
+        <v>16086019000</v>
       </c>
       <c r="H123" t="n">
-        <v>2085.872134468915</v>
+        <v>4137.137750115735</v>
       </c>
       <c r="I123" t="n">
-        <v>7.380000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S100V4AM.zip</t>
+          <t>S100V7YO.zip</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-02-10_01_2025-02-18.csv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3861</v>
+        <v>4626</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>100</v>
+        <v>4670190</v>
       </c>
       <c r="G124" t="n">
-        <v>59000</v>
+        <v>16652257000</v>
       </c>
       <c r="H124" t="n">
-        <v>590</v>
+        <v>3565.648720929983</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S100V3YF.zip</t>
+          <t>S100V45I.zip</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-01-17_01_2025-01-24.csv</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5715</v>
+        <v>7732</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>100</v>
+        <v>7995900</v>
       </c>
       <c r="G125" t="n">
-        <v>160000</v>
+        <v>16678425000</v>
       </c>
       <c r="H125" t="n">
-        <v>1600</v>
+        <v>2085.872134468915</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>7.380000000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S100Z00S.zip</t>
+          <t>S100V4AM.zip</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-01-15_01_2025-01-22.csv</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1882</v>
+        <v>3861</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>8033500</v>
+        <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>9401444000</v>
+        <v>59000</v>
       </c>
       <c r="H126" t="n">
-        <v>1170.279952698077</v>
+        <v>590</v>
       </c>
       <c r="I126" t="n">
-        <v>15.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S100YZVM.zip</t>
+          <t>S100V3YF.zip</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-01-10_01_2025-01-20.csv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1882</v>
+        <v>5715</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>8007300</v>
+        <v>100</v>
       </c>
       <c r="G127" t="n">
-        <v>9367939000</v>
+        <v>160000</v>
       </c>
       <c r="H127" t="n">
-        <v>1169.924818603025</v>
+        <v>1600</v>
       </c>
       <c r="I127" t="n">
-        <v>15.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S100UYE4.zip</t>
+          <t>S100Z00S.zip</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-27_02_2026-09-04.csv</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3978</v>
+        <v>1882</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2891700</v>
+        <v>8033500</v>
       </c>
       <c r="G128" t="n">
-        <v>3425686000</v>
+        <v>9401444000</v>
       </c>
       <c r="H128" t="n">
-        <v>1184.661617733513</v>
+        <v>1170.279952698077</v>
       </c>
       <c r="I128" t="n">
-        <v>7.12</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S100UWW1.zip</t>
+          <t>S100YZVM.zip</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-12-17_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4452</v>
+        <v>1882</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>24347342</v>
+        <v>8007300</v>
       </c>
       <c r="G129" t="n">
-        <v>148917027000</v>
+        <v>9367939000</v>
       </c>
       <c r="H129" t="n">
-        <v>6116.356643776557</v>
+        <v>1169.924818603025</v>
       </c>
       <c r="I129" t="n">
-        <v>5.23</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S100UWQK.zip</t>
+          <t>S100UYE4.zip</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-13_01_2024-12-17.csv</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>9257</v>
+        <v>3978</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>100</v>
+        <v>2891700</v>
       </c>
       <c r="G130" t="n">
-        <v>57000</v>
+        <v>3425686000</v>
       </c>
       <c r="H130" t="n">
-        <v>570</v>
+        <v>1184.661617733513</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S100YZUZ.zip</t>
+          <t>S100UWW1.zip</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-12-05_01_2024-12-10.csv</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1882</v>
+        <v>4452</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>7914900</v>
+        <v>24347342</v>
       </c>
       <c r="G131" t="n">
-        <v>9250219000</v>
+        <v>148917027000</v>
       </c>
       <c r="H131" t="n">
-        <v>1168.709522546084</v>
+        <v>6116.356643776557</v>
       </c>
       <c r="I131" t="n">
-        <v>15.71</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S100UMDQ.zip</t>
+          <t>S100UWQK.zip</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-12-02_01_2024-12-09.csv</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9531</v>
+        <v>9257</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>19554300</v>
+        <v>100</v>
       </c>
       <c r="G132" t="n">
-        <v>64960321000</v>
+        <v>57000</v>
       </c>
       <c r="H132" t="n">
-        <v>3322.047887165483</v>
+        <v>570</v>
       </c>
       <c r="I132" t="n">
-        <v>5.029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S100UORL.zip</t>
+          <t>S100YZUZ.zip</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-11-26_02_2026-09-03.csv</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4385</v>
+        <v>1882</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>8815360</v>
+        <v>7914900</v>
       </c>
       <c r="G133" t="n">
-        <v>17684138000</v>
+        <v>9250219000</v>
       </c>
       <c r="H133" t="n">
-        <v>2006.059650428343</v>
+        <v>1168.709522546084</v>
       </c>
       <c r="I133" t="n">
-        <v>5.37</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S100UMI2.zip</t>
+          <t>S100UMDQ.zip</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2024-11-12_01_2024-11-19.csv</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>7984</v>
+        <v>9531</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>6096500</v>
+        <v>19554300</v>
       </c>
       <c r="G134" t="n">
-        <v>13153972000</v>
+        <v>64960321000</v>
       </c>
       <c r="H134" t="n">
-        <v>2157.626835069302</v>
+        <v>3322.047887165483</v>
       </c>
       <c r="I134" t="n">
-        <v>5.02</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S100UMJC.zip</t>
+          <t>S100UORL.zip</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-06_01_2024-11-13.csv</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5399,109 +5399,109 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1973</v>
+        <v>4385</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>8973383</v>
+        <v>8815360</v>
       </c>
       <c r="G135" t="n">
-        <v>24947403000</v>
+        <v>17684138000</v>
       </c>
       <c r="H135" t="n">
-        <v>2780.155823060266</v>
+        <v>2006.059650428343</v>
       </c>
       <c r="I135" t="n">
-        <v>6.01</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S100UKY9.zip</t>
+          <t>S100UMI2.zip</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-11-01_01_2024-11-06.csv</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6908</v>
+        <v>7984</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>502000</v>
+        <v>6096500</v>
       </c>
       <c r="G136" t="n">
-        <v>1257178000</v>
+        <v>13153972000</v>
       </c>
       <c r="H136" t="n">
-        <v>2504.338645418327</v>
+        <v>2157.626835069302</v>
       </c>
       <c r="I136" t="n">
-        <v>2.04</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S100UIC4.zip</t>
+          <t>S100UMJC.zip</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-10-30_01_2024-11-07.csv</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3765</v>
+        <v>1973</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>4552900</v>
+        <v>8973383</v>
       </c>
       <c r="G137" t="n">
-        <v>13383536000</v>
+        <v>24947403000</v>
       </c>
       <c r="H137" t="n">
-        <v>2939.562915943684</v>
+        <v>2780.155823060266</v>
       </c>
       <c r="I137" t="n">
-        <v>5.47</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S100UEDF.zip</t>
+          <t>S100UKY9.zip</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-10-22_01_2024-10-29.csv</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5510,109 +5510,109 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>5482</v>
+        <v>6908</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>433300</v>
+        <v>502000</v>
       </c>
       <c r="G138" t="n">
-        <v>1367192000</v>
+        <v>1257178000</v>
       </c>
       <c r="H138" t="n">
-        <v>3155.301177013616</v>
+        <v>2504.338645418327</v>
       </c>
       <c r="I138" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S100UCI9.zip</t>
+          <t>S100UIC4.zip</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2024-10-08_01_2024-10-16.csv</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>8141</v>
+        <v>3765</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>100</v>
+        <v>4552900</v>
       </c>
       <c r="G139" t="n">
-        <v>93000</v>
+        <v>13383536000</v>
       </c>
       <c r="H139" t="n">
-        <v>930</v>
+        <v>2939.562915943684</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S100UE9B.zip</t>
+          <t>S100UEDF.zip</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-13_01_2024-09-24.csv</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4272</v>
+        <v>5482</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>26855100</v>
+        <v>433300</v>
       </c>
       <c r="G140" t="n">
-        <v>29860350000</v>
+        <v>1367192000</v>
       </c>
       <c r="H140" t="n">
-        <v>1111.90611839092</v>
+        <v>3155.301177013616</v>
       </c>
       <c r="I140" t="n">
-        <v>15.75</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S100UBQ6.zip</t>
+          <t>S100UCI9.zip</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-06_01_2024-09-13.csv</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5621,21 +5621,21 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6145</v>
+        <v>8141</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F141" t="n">
         <v>100</v>
       </c>
       <c r="G141" t="n">
-        <v>171000</v>
+        <v>93000</v>
       </c>
       <c r="H141" t="n">
-        <v>1710</v>
+        <v>930</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -5644,493 +5644,493 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S100UBH9.zip</t>
+          <t>S100UE9B.zip</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-09-06_02_2024-09-19.csv</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3569</v>
+        <v>4272</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>4271704</v>
+        <v>26855100</v>
       </c>
       <c r="G142" t="n">
-        <v>5808044000</v>
+        <v>29860350000</v>
       </c>
       <c r="H142" t="n">
-        <v>1359.655069733296</v>
+        <v>1111.90611839092</v>
       </c>
       <c r="I142" t="n">
-        <v>6.279999999999999</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S100UB89.zip</t>
+          <t>S100UBQ6.zip</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-09-03_01_2024-09-10.csv</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4205</v>
+        <v>6145</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2024-08-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>14426600</v>
+        <v>100</v>
       </c>
       <c r="G143" t="n">
-        <v>24829312000</v>
+        <v>171000</v>
       </c>
       <c r="H143" t="n">
-        <v>1721.078563209627</v>
+        <v>1710</v>
       </c>
       <c r="I143" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S100U9FC.zip</t>
+          <t>S100UBH9.zip</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>6516</v>
+        <v>3569</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>679500</v>
+        <v>4271704</v>
       </c>
       <c r="G144" t="n">
-        <v>4792335000</v>
+        <v>5808044000</v>
       </c>
       <c r="H144" t="n">
-        <v>7052.737306843267</v>
+        <v>1359.655069733296</v>
       </c>
       <c r="I144" t="n">
-        <v>5.24</v>
+        <v>6.279999999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S100UA4H.zip</t>
+          <t>S100UB89.zip</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-08-30_01_2024-09-06.csv</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2327</v>
+        <v>4205</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>9154320</v>
+        <v>14426600</v>
       </c>
       <c r="G145" t="n">
-        <v>23450671000</v>
+        <v>24829312000</v>
       </c>
       <c r="H145" t="n">
-        <v>2561.705402476645</v>
+        <v>1721.078563209627</v>
       </c>
       <c r="I145" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S100U8JX.zip</t>
+          <t>S100U9FC.zip</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-08-20_01_2024-08-27.csv</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3989</v>
+        <v>6516</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1206000</v>
+        <v>679500</v>
       </c>
       <c r="G146" t="n">
-        <v>787604000</v>
+        <v>4792335000</v>
       </c>
       <c r="H146" t="n">
-        <v>653.0713101160862</v>
+        <v>7052.737306843267</v>
       </c>
       <c r="I146" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S100U8Q2.zip</t>
+          <t>S100UA4H.zip</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-08-19_01_2024-08-26.csv</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>6908</v>
+        <v>2327</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>100</v>
+        <v>9154320</v>
       </c>
       <c r="G147" t="n">
-        <v>288000</v>
+        <v>23450671000</v>
       </c>
       <c r="H147" t="n">
-        <v>2880</v>
+        <v>2561.705402476645</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S100U705.zip</t>
+          <t>S100U8JX.zip</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-14_01_2024-08-21.csv</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>5988</v>
+        <v>3989</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>527300</v>
+        <v>1206000</v>
       </c>
       <c r="G148" t="n">
-        <v>1212090000</v>
+        <v>787604000</v>
       </c>
       <c r="H148" t="n">
-        <v>2298.672482457804</v>
+        <v>653.0713101160862</v>
       </c>
       <c r="I148" t="n">
-        <v>1.42</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S100U5II.zip</t>
+          <t>S100U8Q2.zip</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2024-08-13_01_2024-08-20.csv</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3529</v>
+        <v>6908</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>998000</v>
+        <v>100</v>
       </c>
       <c r="G149" t="n">
-        <v>667598000</v>
+        <v>288000</v>
       </c>
       <c r="H149" t="n">
-        <v>668.9358717434869</v>
+        <v>2880</v>
       </c>
       <c r="I149" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S100U528.zip</t>
+          <t>S100U705.zip</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-08-06_01_2024-08-14.csv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>7305</v>
+        <v>5988</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>309800</v>
+        <v>527300</v>
       </c>
       <c r="G150" t="n">
-        <v>1321438000</v>
+        <v>1212090000</v>
       </c>
       <c r="H150" t="n">
-        <v>4265.455132343447</v>
+        <v>2298.672482457804</v>
       </c>
       <c r="I150" t="n">
-        <v>5.12</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S100U4Z7.zip</t>
+          <t>S100U5II.zip</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-08-01_01_2024-08-08.csv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>5541</v>
+        <v>3529</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>100</v>
+        <v>998000</v>
       </c>
       <c r="G151" t="n">
-        <v>127000</v>
+        <v>667598000</v>
       </c>
       <c r="H151" t="n">
-        <v>1270</v>
+        <v>668.9358717434869</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S100U47L.zip</t>
+          <t>S100U528.zip</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-30_01_2024-08-06.csv</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2168</v>
+        <v>7305</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2094200</v>
+        <v>309800</v>
       </c>
       <c r="G152" t="n">
-        <v>4445105000</v>
+        <v>1321438000</v>
       </c>
       <c r="H152" t="n">
-        <v>2122.579027791042</v>
+        <v>4265.455132343447</v>
       </c>
       <c r="I152" t="n">
-        <v>5.02</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S100U3HM.zip</t>
+          <t>S100U4Z7.zip</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-25_01_2024-08-01.csv</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>4967</v>
+        <v>5541</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>4062075</v>
+        <v>100</v>
       </c>
       <c r="G153" t="n">
-        <v>8729143000</v>
+        <v>127000</v>
       </c>
       <c r="H153" t="n">
-        <v>2148.936934940886</v>
+        <v>1270</v>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S100U45I.zip</t>
+          <t>S100U47L.zip</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-25_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>8803</v>
+        <v>2168</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>100</v>
+        <v>2094200</v>
       </c>
       <c r="G154" t="n">
-        <v>361000</v>
+        <v>4445105000</v>
       </c>
       <c r="H154" t="n">
-        <v>3610</v>
+        <v>2122.579027791042</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S100UK9S.zip</t>
+          <t>S100U3HM.zip</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-07-24.csv</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6150,10 +6150,10 @@
         <v>4062075</v>
       </c>
       <c r="G155" t="n">
-        <v>20578848000</v>
+        <v>8729143000</v>
       </c>
       <c r="H155" t="n">
-        <v>5066.092575838703</v>
+        <v>2148.936934940886</v>
       </c>
       <c r="I155" t="n">
         <v>5.2</v>
@@ -6162,234 +6162,234 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S100U325.zip</t>
+          <t>S100U45I.zip</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-07-22_01_2024-07-29.csv</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>9882</v>
+        <v>8803</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>2505000</v>
+        <v>100</v>
       </c>
       <c r="G156" t="n">
-        <v>5292086000</v>
+        <v>361000</v>
       </c>
       <c r="H156" t="n">
-        <v>2112.609181636727</v>
+        <v>3610</v>
       </c>
       <c r="I156" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S100U4Z0.zip</t>
+          <t>S100UK9S.zip</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-07-22_01_2024-10-23.csv</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>8129</v>
+        <v>4967</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>7258230</v>
+        <v>4062075</v>
       </c>
       <c r="G157" t="n">
-        <v>24720910000</v>
+        <v>20578848000</v>
       </c>
       <c r="H157" t="n">
-        <v>3405.914389596362</v>
+        <v>5066.092575838703</v>
       </c>
       <c r="I157" t="n">
-        <v>9.460000000000001</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S100U2CM.zip</t>
+          <t>S100U325.zip</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-07-19_01_2024-07-26.csv</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2206</v>
+        <v>9882</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3462600</v>
+        <v>2505000</v>
       </c>
       <c r="G158" t="n">
-        <v>14385811000</v>
+        <v>5292086000</v>
       </c>
       <c r="H158" t="n">
-        <v>4154.626869982095</v>
+        <v>2112.609181636727</v>
       </c>
       <c r="I158" t="n">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S100U07U.zip</t>
+          <t>S100U4Z0.zip</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-07-16_02_2024-07-31.csv</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3666</v>
+        <v>8129</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1053200</v>
+        <v>7258230</v>
       </c>
       <c r="G159" t="n">
-        <v>663809000</v>
+        <v>24720910000</v>
       </c>
       <c r="H159" t="n">
-        <v>630.278199772123</v>
+        <v>3405.914389596362</v>
       </c>
       <c r="I159" t="n">
-        <v>5.16</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S100U1HO.zip</t>
+          <t>S100U2CM.zip</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-07-10_01_2024-07-18.csv</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>4347</v>
+        <v>2206</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>614893</v>
+        <v>3462600</v>
       </c>
       <c r="G160" t="n">
-        <v>940560000</v>
+        <v>14385811000</v>
       </c>
       <c r="H160" t="n">
-        <v>1529.631984751819</v>
+        <v>4154.626869982095</v>
       </c>
       <c r="I160" t="n">
-        <v>8.200000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S100TRA6.zip</t>
+          <t>S100U07U.zip</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-04_01_2024-07-11.csv</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>8129</v>
+        <v>3666</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>3886330</v>
+        <v>1053200</v>
       </c>
       <c r="G161" t="n">
-        <v>10549885000</v>
+        <v>663809000</v>
       </c>
       <c r="H161" t="n">
-        <v>2714.613787300615</v>
+        <v>630.278199772123</v>
       </c>
       <c r="I161" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S100TMDP.zip</t>
+          <t>S100U1HO.zip</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-07-03_01_2024-07-12.csv</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6398,775 +6398,775 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>8929</v>
+        <v>4347</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1260812</v>
+        <v>614893</v>
       </c>
       <c r="G162" t="n">
-        <v>1699255000</v>
+        <v>940560000</v>
       </c>
       <c r="H162" t="n">
-        <v>1347.74653160027</v>
+        <v>1529.631984751819</v>
       </c>
       <c r="I162" t="n">
-        <v>5.140000000000001</v>
+        <v>8.200000000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S100TMID.zip</t>
+          <t>S100TRA6.zip</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-17_01_2024-06-24.csv</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>7278</v>
+        <v>8129</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>115400</v>
+        <v>3886330</v>
       </c>
       <c r="G163" t="n">
-        <v>302115000</v>
+        <v>10549885000</v>
       </c>
       <c r="H163" t="n">
-        <v>2617.980935875217</v>
+        <v>2714.613787300615</v>
       </c>
       <c r="I163" t="n">
-        <v>0.24</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S100TK8M.zip</t>
+          <t>S100TMDP.zip</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-06-11_01_2024-06-18.csv</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>4042</v>
+        <v>8929</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>16459200</v>
+        <v>1260812</v>
       </c>
       <c r="G164" t="n">
-        <v>33451116000</v>
+        <v>1699255000</v>
       </c>
       <c r="H164" t="n">
-        <v>2032.365850102071</v>
+        <v>1347.74653160027</v>
       </c>
       <c r="I164" t="n">
-        <v>5.06</v>
+        <v>5.140000000000001</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S100TLGT.zip</t>
+          <t>S100TMID.zip</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-06-10_01_2024-06-17.csv</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3591</v>
+        <v>7278</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2846091</v>
+        <v>115400</v>
       </c>
       <c r="G165" t="n">
-        <v>6888596000</v>
+        <v>302115000</v>
       </c>
       <c r="H165" t="n">
-        <v>2420.370957920882</v>
+        <v>2617.980935875217</v>
       </c>
       <c r="I165" t="n">
-        <v>5.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S100TJMY.zip</t>
+          <t>S100TK8M.zip</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-06-04_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4521</v>
+        <v>4042</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>100</v>
+        <v>16459200</v>
       </c>
       <c r="G166" t="n">
-        <v>353000</v>
+        <v>33451116000</v>
       </c>
       <c r="H166" t="n">
-        <v>3530</v>
+        <v>2032.365850102071</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S100TJBE.zip</t>
+          <t>S100TLGT.zip</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-06-04_01_2024-06-11.csv</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ダルトン　インベストメンツ　インク</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>8923</v>
+        <v>3591</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2445600</v>
+        <v>2846091</v>
       </c>
       <c r="G167" t="n">
-        <v>3856031000</v>
+        <v>6888596000</v>
       </c>
       <c r="H167" t="n">
-        <v>1576.721867844292</v>
+        <v>2420.370957920882</v>
       </c>
       <c r="I167" t="n">
-        <v>5.02</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S100THZ6.zip</t>
+          <t>S100TJMY.zip</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-29_01_2024-06-05.csv</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4347</v>
+        <v>4521</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>400493</v>
+        <v>100</v>
       </c>
       <c r="G168" t="n">
-        <v>580713000</v>
+        <v>353000</v>
       </c>
       <c r="H168" t="n">
-        <v>1449.995380693296</v>
+        <v>3530</v>
       </c>
       <c r="I168" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S100TFJS.zip</t>
+          <t>S100TJBE.zip</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
+          <t>jplvh010000-lvh-001_E39237-000_2024-05-27_01_2024-06-03.csv</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>ダルトン　インベストメンツ　インク</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>9024</v>
+        <v>8923</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>16207437</v>
+        <v>2445600</v>
       </c>
       <c r="G169" t="n">
-        <v>27823532000</v>
+        <v>3856031000</v>
       </c>
       <c r="H169" t="n">
-        <v>1716.713876475349</v>
+        <v>1576.721867844292</v>
       </c>
       <c r="I169" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S100TDVX.zip</t>
+          <t>S100THZ6.zip</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-05-22_01_2024-05-29.csv</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1518</v>
+        <v>4347</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>100</v>
+        <v>400493</v>
       </c>
       <c r="G170" t="n">
-        <v>292000</v>
+        <v>580713000</v>
       </c>
       <c r="H170" t="n">
-        <v>2920</v>
+        <v>1449.995380693296</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S100TBA3.zip</t>
+          <t>S100TFJS.zip</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2024-05-07_01_2024-05-14.csv</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7731</v>
+        <v>9024</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>17639800</v>
+        <v>16207437</v>
       </c>
       <c r="G171" t="n">
-        <v>26675255000</v>
+        <v>27823532000</v>
       </c>
       <c r="H171" t="n">
-        <v>1512.21980974841</v>
+        <v>1716.713876475349</v>
       </c>
       <c r="I171" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S100TB1B.zip</t>
+          <t>S100TDVX.zip</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-05-02_01_2024-05-13.csv</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4536</v>
+        <v>1518</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>18290500</v>
+        <v>100</v>
       </c>
       <c r="G172" t="n">
-        <v>24591924000</v>
+        <v>292000</v>
       </c>
       <c r="H172" t="n">
-        <v>1344.518957928979</v>
+        <v>2920</v>
       </c>
       <c r="I172" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S100T7B6.zip</t>
+          <t>S100TBA3.zip</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
+          <t>jplvh010000-lvh-002_E24872-000_2024-04-22_01_2024-04-23.csv</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4185</v>
+        <v>7731</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>100</v>
+        <v>17639800</v>
       </c>
       <c r="G173" t="n">
-        <v>405000</v>
+        <v>26675255000</v>
       </c>
       <c r="H173" t="n">
-        <v>4050</v>
+        <v>1512.21980974841</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S100T0IC.zip</t>
+          <t>S100TB1B.zip</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2024-04-19_01_2024-04-22.csv</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>4549</v>
+        <v>4536</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2006900</v>
+        <v>18290500</v>
       </c>
       <c r="G174" t="n">
-        <v>3367745000</v>
+        <v>24591924000</v>
       </c>
       <c r="H174" t="n">
-        <v>1678.083113259255</v>
+        <v>1344.518957928979</v>
       </c>
       <c r="I174" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S100SZYE.zip</t>
+          <t>S100T7B6.zip</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-03-26_01_2024-04-02.csv</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>9627</v>
+        <v>4185</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3401100</v>
+        <v>100</v>
       </c>
       <c r="G175" t="n">
-        <v>9648726000</v>
+        <v>405000</v>
       </c>
       <c r="H175" t="n">
-        <v>2836.942753814942</v>
+        <v>4050</v>
       </c>
       <c r="I175" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S100SXVR.zip</t>
+          <t>S100T0IC.zip</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-03-05_01_2024-03-11.csv</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>8304</v>
+        <v>4549</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>100</v>
+        <v>2006900</v>
       </c>
       <c r="G176" t="n">
-        <v>219000</v>
+        <v>3367745000</v>
       </c>
       <c r="H176" t="n">
-        <v>2190</v>
+        <v>1678.083113259255</v>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S100SY8N.zip</t>
+          <t>S100SZYE.zip</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-03-04_01_2024-03-06.csv</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>3328</v>
+        <v>9627</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>845300</v>
+        <v>3401100</v>
       </c>
       <c r="G177" t="n">
-        <v>1219326000</v>
+        <v>9648726000</v>
       </c>
       <c r="H177" t="n">
-        <v>1442.477227019993</v>
+        <v>2836.942753814942</v>
       </c>
       <c r="I177" t="n">
-        <v>6.54</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S100SW6R.zip</t>
+          <t>S100SXVR.zip</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-02-20_01_2024-02-28.csv</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>3328</v>
+        <v>8304</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>675500</v>
+        <v>100</v>
       </c>
       <c r="G178" t="n">
-        <v>976503000</v>
+        <v>219000</v>
       </c>
       <c r="H178" t="n">
-        <v>1445.60029607698</v>
+        <v>2190</v>
       </c>
       <c r="I178" t="n">
-        <v>5.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S100ST3I.zip</t>
+          <t>S100SY8N.zip</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-15_01_2024-02-27.csv</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>8818</v>
+        <v>3328</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>2505000</v>
+        <v>845300</v>
       </c>
       <c r="G179" t="n">
-        <v>3361654000</v>
+        <v>1219326000</v>
       </c>
       <c r="H179" t="n">
-        <v>1341.977644710579</v>
+        <v>1442.477227019993</v>
       </c>
       <c r="I179" t="n">
-        <v>5.09</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S100SO4R.zip</t>
+          <t>S100SW6R.zip</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2024-02-13_01_2024-02-20.csv</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5541</v>
+        <v>3328</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>100</v>
+        <v>675500</v>
       </c>
       <c r="G180" t="n">
-        <v>117000</v>
+        <v>976503000</v>
       </c>
       <c r="H180" t="n">
-        <v>1170</v>
+        <v>1445.60029607698</v>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>5.220000000000001</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S100SN7U.zip</t>
+          <t>S100ST3I.zip</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2024-02-07_01_2024-02-15.csv</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>7315</v>
+        <v>8818</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>6994900</v>
+        <v>2505000</v>
       </c>
       <c r="G181" t="n">
-        <v>5874641000</v>
+        <v>3361654000</v>
       </c>
       <c r="H181" t="n">
-        <v>839.8463166020958</v>
+        <v>1341.977644710579</v>
       </c>
       <c r="I181" t="n">
-        <v>14.23</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S100SLMH.zip</t>
+          <t>S100SO4R.zip</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2024-01-18_01_2024-01-25.csv</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4837</v>
+        <v>5541</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>5428600</v>
+        <v>100</v>
       </c>
       <c r="G182" t="n">
-        <v>4378021000</v>
+        <v>117000</v>
       </c>
       <c r="H182" t="n">
-        <v>806.4733080352208</v>
+        <v>1170</v>
       </c>
       <c r="I182" t="n">
-        <v>9.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S100SJ27.zip</t>
+          <t>S100SN7U.zip</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-16_01_2024-01-23.csv</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7175,35 +7175,35 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>4631</v>
+        <v>7315</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>6563759</v>
+        <v>6994900</v>
       </c>
       <c r="G183" t="n">
-        <v>16844475000</v>
+        <v>5874641000</v>
       </c>
       <c r="H183" t="n">
-        <v>2566.284807227078</v>
+        <v>839.8463166020958</v>
       </c>
       <c r="I183" t="n">
-        <v>6.9</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S100SJ0K.zip</t>
+          <t>S100SLMH.zip</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2024-01-09_01_2024-01-16.csv</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7212,72 +7212,72 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4293</v>
+        <v>4837</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>20896886</v>
+        <v>5428600</v>
       </c>
       <c r="G184" t="n">
-        <v>9376038000</v>
+        <v>4378021000</v>
       </c>
       <c r="H184" t="n">
-        <v>448.6811097117532</v>
+        <v>806.4733080352208</v>
       </c>
       <c r="I184" t="n">
-        <v>9.9</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S100SHYB.zip</t>
+          <t>S100SJ27.zip</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>5449</v>
+        <v>4631</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2114100</v>
+        <v>6563759</v>
       </c>
       <c r="G185" t="n">
-        <v>3695597000</v>
+        <v>16844475000</v>
       </c>
       <c r="H185" t="n">
-        <v>1748.071046781136</v>
+        <v>2566.284807227078</v>
       </c>
       <c r="I185" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S100SDCB.zip</t>
+          <t>S100SJ0K.zip</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-12-21_01_2023-12-28.csv</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7286,356 +7286,430 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>6232</v>
+        <v>4293</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1499000</v>
+        <v>20896886</v>
       </c>
       <c r="G186" t="n">
-        <v>1369002000</v>
+        <v>9376038000</v>
       </c>
       <c r="H186" t="n">
-        <v>913.2768512341561</v>
+        <v>448.6811097117532</v>
       </c>
       <c r="I186" t="n">
-        <v>10.47</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S100SB0S.zip</t>
+          <t>S100SHYB.zip</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2023-12-19_01_2023-12-26.csv</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>6237</v>
+        <v>5449</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1129500</v>
+        <v>2114100</v>
       </c>
       <c r="G187" t="n">
-        <v>1537738000</v>
+        <v>3695597000</v>
       </c>
       <c r="H187" t="n">
-        <v>1361.432492253209</v>
+        <v>1748.071046781136</v>
       </c>
       <c r="I187" t="n">
-        <v>5.02</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S100S8AS.zip</t>
+          <t>S100SDCB.zip</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-29_01_2023-12-04.csv</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4987</v>
+        <v>6232</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1543800</v>
+        <v>1499000</v>
       </c>
       <c r="G188" t="n">
-        <v>874286000</v>
+        <v>1369002000</v>
       </c>
       <c r="H188" t="n">
-        <v>566.3207669387226</v>
+        <v>913.2768512341561</v>
       </c>
       <c r="I188" t="n">
-        <v>5.779999999999999</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S100S4PN.zip</t>
+          <t>S100SB0S.zip</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2023-11-09_01_2023-11-16.csv</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>4739</v>
+        <v>6237</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>15400600</v>
+        <v>1129500</v>
       </c>
       <c r="G189" t="n">
-        <v>66216726000</v>
+        <v>1537738000</v>
       </c>
       <c r="H189" t="n">
-        <v>4299.619884939548</v>
+        <v>1361.432492253209</v>
       </c>
       <c r="I189" t="n">
-        <v>6.419999999999999</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>S100S1V3.zip</t>
+          <t>S100S8AS.zip</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2023-11-08_01_2023-11-15.csv</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2501</v>
+        <v>4987</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>4010500</v>
+        <v>1543800</v>
       </c>
       <c r="G190" t="n">
-        <v>10817766000</v>
+        <v>874286000</v>
       </c>
       <c r="H190" t="n">
-        <v>2697.360927565142</v>
+        <v>566.3207669387226</v>
       </c>
       <c r="I190" t="n">
-        <v>5.09</v>
+        <v>5.779999999999999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>S100RZUR.zip</t>
+          <t>S100S4PN.zip</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2023-11-02_01_2023-11-07.csv</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>4023</v>
+        <v>4739</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>100</v>
+        <v>15400600</v>
       </c>
       <c r="G191" t="n">
-        <v>796000</v>
+        <v>66216726000</v>
       </c>
       <c r="H191" t="n">
-        <v>7960</v>
+        <v>4299.619884939548</v>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>6.419999999999999</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S100RYJW.zip</t>
+          <t>S100S1V3.zip</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2023-10-12_01_2023-10-19.csv</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5844</v>
+        <v>2501</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>4998800</v>
+        <v>4010500</v>
       </c>
       <c r="G192" t="n">
-        <v>24949147000</v>
+        <v>10817766000</v>
       </c>
       <c r="H192" t="n">
-        <v>4991.027246539169</v>
+        <v>2697.360927565142</v>
       </c>
       <c r="I192" t="n">
-        <v>6.59</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S100RY2V.zip</t>
+          <t>S100RZUR.zip</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2023-10-04_01_2023-10-12.csv</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>5186</v>
+        <v>4023</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1536900</v>
+        <v>100</v>
       </c>
       <c r="G193" t="n">
-        <v>4758738000</v>
+        <v>796000</v>
       </c>
       <c r="H193" t="n">
-        <v>3096.322467304314</v>
+        <v>7960</v>
       </c>
       <c r="I193" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>S100RYRP.zip</t>
+          <t>S100RYJW.zip</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2023-10-02_01_2023-10-04.csv</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>5947</v>
+        <v>5844</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>7446200</v>
+        <v>4998800</v>
       </c>
       <c r="G194" t="n">
-        <v>21182239000</v>
+        <v>24949147000</v>
       </c>
       <c r="H194" t="n">
-        <v>2844.704547285864</v>
+        <v>4991.027246539169</v>
       </c>
       <c r="I194" t="n">
-        <v>4.96</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
+          <t>S100RY2V.zip</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>5186</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>1536900</v>
+      </c>
+      <c r="G195" t="n">
+        <v>4758738000</v>
+      </c>
+      <c r="H195" t="n">
+        <v>3096.322467304314</v>
+      </c>
+      <c r="I195" t="n">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>S100RYRP.zip</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>jplvh010000-lvh-001_E08827-000_2023-09-27_01_2023-10-04.csv</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>5947</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>7446200</v>
+      </c>
+      <c r="G196" t="n">
+        <v>21182239000</v>
+      </c>
+      <c r="H196" t="n">
+        <v>2844.704547285864</v>
+      </c>
+      <c r="I196" t="n">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
           <t>S100RX5R.zip</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>jplvh010000-lvh-001_E04037-000_2023-09-21_01_2023-09-28.csv</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
-      <c r="D195" t="n">
+      <c r="D197" t="n">
         <v>8303</v>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>2023-09-21</t>
         </is>
       </c>
-      <c r="F195" t="n">
+      <c r="F197" t="n">
         <v>20000000</v>
       </c>
-      <c r="G195" t="n">
+      <c r="G197" t="n">
         <v>56014500000</v>
       </c>
-      <c r="H195" t="n">
+      <c r="H197" t="n">
         <v>2800.725</v>
       </c>
-      <c r="I195" t="n">
+      <c r="I197" t="n">
         <v>9.75</v>
       </c>
     </row>

--- a/docs/アクティビスト銘柄一覧.xlsx
+++ b/docs/アクティビスト銘柄一覧.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:I198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1280,86 +1280,86 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S100Y79Q.zip</t>
+          <t>S100Z3OY.zip</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-06-01_02_2026-09-28.csv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2871</v>
+        <v>4189</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12872200</v>
+        <v>6344600</v>
       </c>
       <c r="G24" t="n">
-        <v>23365599000</v>
+        <v>17188304000</v>
       </c>
       <c r="H24" t="n">
-        <v>1815.198567455447</v>
+        <v>2709.123348989692</v>
       </c>
       <c r="I24" t="n">
-        <v>5.01</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S100Y5E5.zip</t>
+          <t>S100Y79Q.zip</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-05-26_01_2026-05-29.csv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9274</v>
+        <v>2871</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>12872200</v>
       </c>
       <c r="G25" t="n">
-        <v>73000</v>
+        <v>23365599000</v>
       </c>
       <c r="H25" t="n">
-        <v>730</v>
+        <v>1815.198567455447</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S100Y3QD.zip</t>
+          <t>S100Y5E5.zip</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-14_01_2026-05-21.csv</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4088</v>
+        <v>9274</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>197000</v>
+        <v>73000</v>
       </c>
       <c r="H26" t="n">
-        <v>1970</v>
+        <v>730</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1391,95 +1391,95 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S100Y2OE.zip</t>
+          <t>S100Z3LP.zip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-05-12_02_2026-09-28.csv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3863</v>
+        <v>4189</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>5972000</v>
       </c>
       <c r="G27" t="n">
-        <v>125000</v>
+        <v>16177790000</v>
       </c>
       <c r="H27" t="n">
-        <v>1250</v>
+        <v>2708.940053583389</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S100Y2B5.zip</t>
+          <t>S100Y3QD.zip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-05-11_01_2026-05-18.csv</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7004</v>
+        <v>4088</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9267600</v>
+        <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>9449965000</v>
+        <v>197000</v>
       </c>
       <c r="H28" t="n">
-        <v>1019.677694332945</v>
+        <v>1970</v>
       </c>
       <c r="I28" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S100Y2BG.zip</t>
+          <t>S100Y2OE.zip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7244</v>
+        <v>3863</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1487,27 +1487,27 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5197900</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>2856142000</v>
+        <v>125000</v>
       </c>
       <c r="H29" t="n">
-        <v>549.4799823005444</v>
+        <v>1250</v>
       </c>
       <c r="I29" t="n">
-        <v>5.390000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S100Y25J.zip</t>
+          <t>S100Y2B5.zip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1516,35 +1516,35 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7242</v>
+        <v>7004</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2841100</v>
+        <v>9267600</v>
       </c>
       <c r="G30" t="n">
-        <v>8024171000</v>
+        <v>9449965000</v>
       </c>
       <c r="H30" t="n">
-        <v>2824.318397803668</v>
+        <v>1019.677694332945</v>
       </c>
       <c r="I30" t="n">
-        <v>5.63</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S100Y1ML.zip</t>
+          <t>S100Y2BG.zip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-30_01_2026-05-12.csv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1553,35 +1553,35 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3774</v>
+        <v>7244</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>13723994</v>
+        <v>5197900</v>
       </c>
       <c r="G31" t="n">
-        <v>36441482000</v>
+        <v>2856142000</v>
       </c>
       <c r="H31" t="n">
-        <v>2655.311711736394</v>
+        <v>549.4799823005444</v>
       </c>
       <c r="I31" t="n">
-        <v>7.48</v>
+        <v>5.390000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S100Y12P.zip</t>
+          <t>S100Y25J.zip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-28_01_2026-05-11.csv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1590,72 +1590,72 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4071</v>
+        <v>7242</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3400107</v>
+        <v>2841100</v>
       </c>
       <c r="G32" t="n">
-        <v>7823559000</v>
+        <v>8024171000</v>
       </c>
       <c r="H32" t="n">
-        <v>2300.974351689521</v>
+        <v>2824.318397803668</v>
       </c>
       <c r="I32" t="n">
-        <v>8.02</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S100Y15W.zip</t>
+          <t>S100Y1ML.zip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-24_01_2026-05-07.csv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9147</v>
+        <v>3774</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>12252200</v>
+        <v>13723994</v>
       </c>
       <c r="G33" t="n">
-        <v>40939867000</v>
+        <v>36441482000</v>
       </c>
       <c r="H33" t="n">
-        <v>3341.42986565678</v>
+        <v>2655.311711736394</v>
       </c>
       <c r="I33" t="n">
-        <v>5.04</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S100XXO7.zip</t>
+          <t>S100Y12P.zip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-04-23_01_2026-05-01.csv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1664,220 +1664,220 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4626</v>
+        <v>4071</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>17384460</v>
+        <v>3400107</v>
       </c>
       <c r="G34" t="n">
-        <v>38239610000</v>
+        <v>7823559000</v>
       </c>
       <c r="H34" t="n">
-        <v>2199.643244598912</v>
+        <v>2300.974351689521</v>
       </c>
       <c r="I34" t="n">
-        <v>14.88</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S100Z3CL.zip</t>
+          <t>S100Y15W.zip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-03-31_02_2026-09-25.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2026-04-21_01_2026-04-28.csv</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4189</v>
+        <v>9147</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5704800</v>
+        <v>12252200</v>
       </c>
       <c r="G35" t="n">
-        <v>15430630000</v>
+        <v>40939867000</v>
       </c>
       <c r="H35" t="n">
-        <v>2704.850301500491</v>
+        <v>3341.42986565678</v>
       </c>
       <c r="I35" t="n">
-        <v>15.36</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S100XW5T.zip</t>
+          <t>S100XXO7.zip</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-31_01_2026-04-08.csv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4613</v>
+        <v>4626</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>8982300</v>
+        <v>17384460</v>
       </c>
       <c r="G36" t="n">
-        <v>21391558000</v>
+        <v>38239610000</v>
       </c>
       <c r="H36" t="n">
-        <v>2381.523440544182</v>
+        <v>2199.643244598912</v>
       </c>
       <c r="I36" t="n">
-        <v>5.050000000000001</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S100XWKV.zip</t>
+          <t>S100Z3CL.zip</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-03-31_02_2026-09-25.csv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6952</v>
+        <v>4189</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>11964800</v>
+        <v>5704800</v>
       </c>
       <c r="G37" t="n">
-        <v>14335634000</v>
+        <v>15430630000</v>
       </c>
       <c r="H37" t="n">
-        <v>1198.150742177053</v>
+        <v>2704.850301500491</v>
       </c>
       <c r="I37" t="n">
-        <v>5.029999999999999</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S100XVQY.zip</t>
+          <t>S100XW5T.zip</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
+          <t>jplvh010000-lvh-001_E24872-000_2026-03-30_01_2026-04-01.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>シルチェスター・インターナショナル・インベスターズ・エルエルピー</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5423</v>
+        <v>4613</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>6884398</v>
+        <v>8982300</v>
       </c>
       <c r="G38" t="n">
-        <v>11052572000</v>
+        <v>21391558000</v>
       </c>
       <c r="H38" t="n">
-        <v>1605.452212379354</v>
+        <v>2381.523440544182</v>
       </c>
       <c r="I38" t="n">
-        <v>6.25</v>
+        <v>5.050000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S100XR6B.zip</t>
+          <t>S100XWKV.zip</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E33309-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
+          <t>3Dインベストメント・パートナーズ・プライベート・リミティッド</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4676</v>
+        <v>6952</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2662900</v>
+        <v>11964800</v>
       </c>
       <c r="G39" t="n">
-        <v>8365298000</v>
+        <v>14335634000</v>
       </c>
       <c r="H39" t="n">
-        <v>3141.424011416125</v>
+        <v>1198.150742177053</v>
       </c>
       <c r="I39" t="n">
-        <v>1.57</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S100XR4F.zip</t>
+          <t>S100XVQY.zip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-26_01_2026-04-02.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1886,442 +1886,442 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9468</v>
+        <v>5423</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>13197300</v>
+        <v>6884398</v>
       </c>
       <c r="G40" t="n">
-        <v>39531520000</v>
+        <v>11052572000</v>
       </c>
       <c r="H40" t="n">
-        <v>2995.424821743842</v>
+        <v>1605.452212379354</v>
       </c>
       <c r="I40" t="n">
-        <v>8.859999999999999</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S100XRXF.zip</t>
+          <t>S100XR6B.zip</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
+          <t>jplvh010000-lvh-001_E04037-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ダルトン・インベストメンツ・エルエルシー</t>
+          <t>株式会社エスグラントコーポレーション代表取締役　池田龍哉</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3132</v>
+        <v>4676</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14653542</v>
+        <v>2662900</v>
       </c>
       <c r="G41" t="n">
-        <v>23038030000</v>
+        <v>8365298000</v>
       </c>
       <c r="H41" t="n">
-        <v>1572.181660925393</v>
+        <v>3141.424011416125</v>
       </c>
       <c r="I41" t="n">
-        <v>8.18</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S100Z3AR.zip</t>
+          <t>S100XR4F.zip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-03-10_02_2026-09-25.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-12_01_2026-03-19.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4189</v>
+        <v>9468</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5332700</v>
+        <v>13197300</v>
       </c>
       <c r="G42" t="n">
-        <v>14369804000</v>
+        <v>39531520000</v>
       </c>
       <c r="H42" t="n">
-        <v>2694.658240666079</v>
+        <v>2995.424821743842</v>
       </c>
       <c r="I42" t="n">
-        <v>14.35</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S100Z2V7.zip</t>
+          <t>S100XRXF.zip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-03-09_02_2026-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E08827-000_2026-03-11_01_2026-03-18.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>ダルトン・インベストメンツ・エルエルシー</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4189</v>
+        <v>3132</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4878200</v>
+        <v>14653542</v>
       </c>
       <c r="G43" t="n">
-        <v>13041315000</v>
+        <v>23038030000</v>
       </c>
       <c r="H43" t="n">
-        <v>2673.3867000123</v>
+        <v>1572.181660925393</v>
       </c>
       <c r="I43" t="n">
-        <v>13.13</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S100XPGG.zip</t>
+          <t>S100Z3AR.zip</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-03-10_02_2026-09-25.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6594</v>
+        <v>4189</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>80322406</v>
+        <v>5332700</v>
       </c>
       <c r="G44" t="n">
-        <v>178330543000</v>
+        <v>14369804000</v>
       </c>
       <c r="H44" t="n">
-        <v>2220.184278344451</v>
+        <v>2694.658240666079</v>
       </c>
       <c r="I44" t="n">
-        <v>6.74</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S100XO30.zip</t>
+          <t>S100Z2V7.zip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-03-09_02_2026-09-24.csv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1721</v>
+        <v>4189</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>7462000</v>
+        <v>4878200</v>
       </c>
       <c r="G45" t="n">
-        <v>27875864000</v>
+        <v>13041315000</v>
       </c>
       <c r="H45" t="n">
-        <v>3735.709461270437</v>
+        <v>2673.3867000123</v>
       </c>
       <c r="I45" t="n">
-        <v>5.609999999999999</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S100Z2US.zip</t>
+          <t>S100XPGG.zip</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-19_02_2026-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-03-04_01_2026-03-11.csv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4189</v>
+        <v>6594</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4482100</v>
+        <v>80322406</v>
       </c>
       <c r="G46" t="n">
-        <v>11882173000</v>
+        <v>178330543000</v>
       </c>
       <c r="H46" t="n">
-        <v>2651.028089511613</v>
+        <v>2220.184278344451</v>
       </c>
       <c r="I46" t="n">
-        <v>12.07</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S100Z2JM.zip</t>
+          <t>S100XO30.zip</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-17_02_2026-09-18.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-26_01_2026-03-03.csv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4189</v>
+        <v>1721</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4476500</v>
+        <v>7462000</v>
       </c>
       <c r="G47" t="n">
-        <v>11865379000</v>
+        <v>27875864000</v>
       </c>
       <c r="H47" t="n">
-        <v>2650.592873897018</v>
+        <v>3735.709461270437</v>
       </c>
       <c r="I47" t="n">
-        <v>12.05</v>
+        <v>5.609999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S100XL07.zip</t>
+          <t>S100Z2US.zip</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-19_02_2026-09-24.csv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6675</v>
+        <v>4189</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>314400</v>
+        <v>4482100</v>
       </c>
       <c r="G48" t="n">
-        <v>1717778000</v>
+        <v>11882173000</v>
       </c>
       <c r="H48" t="n">
-        <v>5463.67048346056</v>
+        <v>2651.028089511613</v>
       </c>
       <c r="I48" t="n">
-        <v>5.029999999999999</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S100XMTS.zip</t>
+          <t>S100Z2JM.zip</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-17_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3549</v>
+        <v>4189</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>13408159</v>
+        <v>4476500</v>
       </c>
       <c r="G49" t="n">
-        <v>40855887000</v>
+        <v>11865379000</v>
       </c>
       <c r="H49" t="n">
-        <v>3047.091476167608</v>
+        <v>2650.592873897018</v>
       </c>
       <c r="I49" t="n">
-        <v>14.02</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S100Z2IH.zip</t>
+          <t>S100XL07.zip</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-09_02_2026-09-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-02-12_01_2026-02-19.csv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4189</v>
+        <v>6675</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4054500</v>
+        <v>314400</v>
       </c>
       <c r="G50" t="n">
-        <v>10605706000</v>
+        <v>1717778000</v>
       </c>
       <c r="H50" t="n">
-        <v>2615.786410161549</v>
+        <v>5463.67048346056</v>
       </c>
       <c r="I50" t="n">
-        <v>10.91</v>
+        <v>5.029999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S100Z1ZH.zip</t>
+          <t>S100XMTS.zip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-003_E31883-000_2026-02-12_01_2026-02-24.csv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3765</v>
+        <v>3549</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6673200</v>
+        <v>13408159</v>
       </c>
       <c r="G51" t="n">
-        <v>19362129000</v>
+        <v>40855887000</v>
       </c>
       <c r="H51" t="n">
-        <v>2901.475903614458</v>
+        <v>3047.091476167608</v>
       </c>
       <c r="I51" t="n">
-        <v>9.65</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S100XJQ9.zip</t>
+          <t>S100Z2IH.zip</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-09_02_2026-09-18.csv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2330,35 +2330,35 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7745</v>
+        <v>4189</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1458700</v>
+        <v>4054500</v>
       </c>
       <c r="G52" t="n">
-        <v>3040190000</v>
+        <v>10605706000</v>
       </c>
       <c r="H52" t="n">
-        <v>2084.177692465894</v>
+        <v>2615.786410161549</v>
       </c>
       <c r="I52" t="n">
-        <v>5.24</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S100Z2CJ.zip</t>
+          <t>S100Z1ZH.zip</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-06_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2367,72 +2367,72 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4189</v>
+        <v>3765</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2917700</v>
+        <v>6673200</v>
       </c>
       <c r="G53" t="n">
-        <v>7487288000</v>
+        <v>19362129000</v>
       </c>
       <c r="H53" t="n">
-        <v>2566.161017239607</v>
+        <v>2901.475903614458</v>
       </c>
       <c r="I53" t="n">
-        <v>7.85</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S100XJKA.zip</t>
+          <t>S100XJQ9.zip</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-05_01_2026-02-13.csv</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9072</v>
+        <v>7745</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>8985002</v>
+        <v>1458700</v>
       </c>
       <c r="G54" t="n">
-        <v>24970571000</v>
+        <v>3040190000</v>
       </c>
       <c r="H54" t="n">
-        <v>2779.139169918938</v>
+        <v>2084.177692465894</v>
       </c>
       <c r="I54" t="n">
-        <v>7.1</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S100Z1ZF.zip</t>
+          <t>S100Z2CJ.zip</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-04_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2441,72 +2441,72 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3765</v>
+        <v>4189</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6600700</v>
+        <v>2917700</v>
       </c>
       <c r="G55" t="n">
-        <v>19175476000</v>
+        <v>7487288000</v>
       </c>
       <c r="H55" t="n">
-        <v>2905.067038344418</v>
+        <v>2566.161017239607</v>
       </c>
       <c r="I55" t="n">
-        <v>9.539999999999999</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S100Z2BC.zip</t>
+          <t>S100XJKA.zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-02-03_01_2026-02-10.csv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4189</v>
+        <v>9072</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2040400</v>
+        <v>8985002</v>
       </c>
       <c r="G56" t="n">
-        <v>5203426000</v>
+        <v>24970571000</v>
       </c>
       <c r="H56" t="n">
-        <v>2550.198980592041</v>
+        <v>2779.139169918938</v>
       </c>
       <c r="I56" t="n">
-        <v>5.489999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S100XJ0M.zip</t>
+          <t>S100Z1ZF.zip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
+          <t>jplvh010000-lvh-002_E27325-000_2026-02-02_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4189</v>
+        <v>3765</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2523,656 +2523,656 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2040400</v>
+        <v>6600700</v>
       </c>
       <c r="G57" t="n">
-        <v>5203426000</v>
+        <v>19175476000</v>
       </c>
       <c r="H57" t="n">
-        <v>2550.198980592041</v>
+        <v>2905.067038344418</v>
       </c>
       <c r="I57" t="n">
-        <v>5.489999999999999</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S100XHKT.zip</t>
+          <t>S100Z2BC.zip</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_02_2026-09-17.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6794</v>
+        <v>4189</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1252600</v>
+        <v>2040400</v>
       </c>
       <c r="G58" t="n">
-        <v>3359425000</v>
+        <v>5203426000</v>
       </c>
       <c r="H58" t="n">
-        <v>2681.96152003832</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I58" t="n">
-        <v>5.01</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S100XH38.zip</t>
+          <t>S100XJ0M.zip</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-02-02_01_2026-02-09.csv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2972</v>
+        <v>4189</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2040400</v>
       </c>
       <c r="G59" t="n">
-        <v>125000</v>
+        <v>5203426000</v>
       </c>
       <c r="H59" t="n">
-        <v>125000</v>
+        <v>2550.198980592041</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>5.489999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S100XGAJ.zip</t>
+          <t>S100XHKT.zip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2026-01-22_01_2026-01-29.csv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2175</v>
+        <v>6794</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>6792424</v>
+        <v>1252600</v>
       </c>
       <c r="G60" t="n">
-        <v>10040067000</v>
+        <v>3359425000</v>
       </c>
       <c r="H60" t="n">
-        <v>1478.127248828989</v>
+        <v>2681.96152003832</v>
       </c>
       <c r="I60" t="n">
-        <v>7.76</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S100Z1ZC.zip</t>
+          <t>S100XH38.zip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2026-01-16_01_2026-01-23.csv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3765</v>
+        <v>2972</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>6336400</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>18726232000</v>
+        <v>125000</v>
       </c>
       <c r="H61" t="n">
-        <v>2955.342465753425</v>
+        <v>125000</v>
       </c>
       <c r="I61" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S100XE1B.zip</t>
+          <t>S100XGAJ.zip</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2026-01-14_01_2026-01-21.csv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3106</v>
+        <v>2175</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>853156</v>
+        <v>6792424</v>
       </c>
       <c r="G62" t="n">
-        <v>4849339000</v>
+        <v>10040067000</v>
       </c>
       <c r="H62" t="n">
-        <v>5684.0003469471</v>
+        <v>1478.127248828989</v>
       </c>
       <c r="I62" t="n">
-        <v>5.02</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S100XGW4.zip</t>
+          <t>S100Z1ZC.zip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2026-01-13_02_2026-09-16.csv</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8233</v>
+        <v>3765</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>261400</v>
+        <v>6336400</v>
       </c>
       <c r="G63" t="n">
-        <v>287906000</v>
+        <v>18726232000</v>
       </c>
       <c r="H63" t="n">
-        <v>1101.400153022188</v>
+        <v>2955.342465753425</v>
       </c>
       <c r="I63" t="n">
-        <v>0.08</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S100XBZC.zip</t>
+          <t>S100XE1B.zip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-29_01_2026-01-09.csv</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2371</v>
+        <v>3106</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10372003</v>
+        <v>853156</v>
       </c>
       <c r="G64" t="n">
-        <v>24045569000</v>
+        <v>4849339000</v>
       </c>
       <c r="H64" t="n">
-        <v>2318.314890576102</v>
+        <v>5684.0003469471</v>
       </c>
       <c r="I64" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S100XB07.zip</t>
+          <t>S100XGW4.zip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-26_02_2026-01-22.csv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7378</v>
+        <v>8233</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>500400</v>
+        <v>261400</v>
       </c>
       <c r="G65" t="n">
-        <v>698873000</v>
+        <v>287906000</v>
       </c>
       <c r="H65" t="n">
-        <v>1396.628697042366</v>
+        <v>1101.400153022188</v>
       </c>
       <c r="I65" t="n">
-        <v>6.78</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S100XAWN.zip</t>
+          <t>S100XBZC.zip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-18_01_2025-12-25.csv</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2432</v>
+        <v>2371</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>100</v>
+        <v>10372003</v>
       </c>
       <c r="G66" t="n">
-        <v>226000</v>
+        <v>24045569000</v>
       </c>
       <c r="H66" t="n">
-        <v>2260</v>
+        <v>2318.314890576102</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S100XA4N.zip</t>
+          <t>S100XB07.zip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8570</v>
+        <v>7378</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>11014402</v>
+        <v>500400</v>
       </c>
       <c r="G67" t="n">
-        <v>14194389000</v>
+        <v>698873000</v>
       </c>
       <c r="H67" t="n">
-        <v>1288.711724885291</v>
+        <v>1396.628697042366</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S100XAP1.zip</t>
+          <t>S100XAWN.zip</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-12-12_01_2025-12-19.csv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6890</v>
+        <v>2432</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>4038389</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>15954609000</v>
+        <v>226000</v>
       </c>
       <c r="H68" t="n">
-        <v>3950.736048458928</v>
+        <v>2260</v>
       </c>
       <c r="I68" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S100X9IB.zip</t>
+          <t>S100XA4N.zip</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-11_01_2025-12-18.csv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>9742</v>
+        <v>8570</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1048500</v>
+        <v>11014402</v>
       </c>
       <c r="G69" t="n">
-        <v>1970276000</v>
+        <v>14194389000</v>
       </c>
       <c r="H69" t="n">
-        <v>1879.137815927515</v>
+        <v>1288.711724885291</v>
       </c>
       <c r="I69" t="n">
-        <v>5.02</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S100X96D.zip</t>
+          <t>S100XAP1.zip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-12-10_01_2025-12-17.csv</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6201</v>
+        <v>6890</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>16322100</v>
+        <v>4038389</v>
       </c>
       <c r="G70" t="n">
-        <v>268179335457000</v>
+        <v>15954609000</v>
       </c>
       <c r="H70" t="n">
-        <v>16430443.10823975</v>
+        <v>3950.736048458928</v>
       </c>
       <c r="I70" t="n">
-        <v>5.01</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S100X9NR.zip</t>
+          <t>S100X9IB.zip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-12-05_01_2025-12-12.csv</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6201</v>
+        <v>9742</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>16322100</v>
+        <v>1048500</v>
       </c>
       <c r="G71" t="n">
-        <v>268179335000</v>
+        <v>1970276000</v>
       </c>
       <c r="H71" t="n">
-        <v>16430.4430802409</v>
+        <v>1879.137815927515</v>
       </c>
       <c r="I71" t="n">
-        <v>5.01</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S100X89B.zip</t>
+          <t>S100X96D.zip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_01_2025-12-10.csv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6856</v>
+        <v>6201</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4180400</v>
+        <v>16322100</v>
       </c>
       <c r="G72" t="n">
-        <v>49662804000</v>
+        <v>268179335457000</v>
       </c>
       <c r="H72" t="n">
-        <v>11879.91675437757</v>
+        <v>16430443.10823975</v>
       </c>
       <c r="I72" t="n">
-        <v>9.9</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S100X894.zip</t>
+          <t>S100X9NR.zip</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E35450-000_2025-12-03_02_2025-12-11.csv</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>アセット・バリュー・インベスターズ・リミテッド</t>
+          <t>エリオット・インベストメント・マネージメント・エルピー（Ｅｌｌｉｏｔｔ　Ｉｎｖｅｓｔｍｅｎｔ　Ｍａｎａｇｅｍｅｎｔ　Ｌ．Ｐ．）</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8011</v>
+        <v>6201</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>551300</v>
+        <v>16322100</v>
       </c>
       <c r="G73" t="n">
-        <v>1831405000</v>
+        <v>268179335000</v>
       </c>
       <c r="H73" t="n">
-        <v>3321.975331035734</v>
+        <v>16430.4430802409</v>
       </c>
       <c r="I73" t="n">
-        <v>5.36</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S100Z16D.zip</t>
+          <t>S100X89B.zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
+          <t>jplvh010000-lvh-001_E31883-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>Ｏａｓｉｓ　Ｍａｎａｇｅｍｅｎｔ　Ｃｏｍｐａｎｙ　Ｌｔｄ．</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1882</v>
+        <v>6856</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1998200</v>
+        <v>4180400</v>
       </c>
       <c r="G74" t="n">
-        <v>2358382000</v>
+        <v>49662804000</v>
       </c>
       <c r="H74" t="n">
-        <v>1180.253227905114</v>
+        <v>11879.91675437757</v>
       </c>
       <c r="I74" t="n">
-        <v>3.97</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S100X8JJ.zip</t>
+          <t>S100X894.zip</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-28_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3181,109 +3181,109 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4549</v>
+        <v>8011</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2546351</v>
+        <v>551300</v>
       </c>
       <c r="G75" t="n">
-        <v>4958319000</v>
+        <v>1831405000</v>
       </c>
       <c r="H75" t="n">
-        <v>1947.225264702313</v>
+        <v>3321.975331035734</v>
       </c>
       <c r="I75" t="n">
-        <v>7.37</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S100X1A3.zip</t>
+          <t>S100Z16D.zip</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-11-26_02_2026-09-11.csv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7940</v>
+        <v>1882</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>100</v>
+        <v>1998200</v>
       </c>
       <c r="G76" t="n">
-        <v>101000</v>
+        <v>2358382000</v>
       </c>
       <c r="H76" t="n">
-        <v>1010</v>
+        <v>1180.253227905114</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S100Z0YS.zip</t>
+          <t>S100X8JJ.zip</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
+          <t>jplvh010000-lvh-001_E34595-000_2025-11-26_01_2025-12-05.csv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>アセット・バリュー・インベスターズ・リミテッド</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1882</v>
+        <v>4549</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2528200</v>
+        <v>2546351</v>
       </c>
       <c r="G77" t="n">
-        <v>2984068000</v>
+        <v>4958319000</v>
       </c>
       <c r="H77" t="n">
-        <v>1180.31326635551</v>
+        <v>1947.225264702313</v>
       </c>
       <c r="I77" t="n">
-        <v>5.02</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S100WWWV.zip</t>
+          <t>S100X1A3.zip</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-11-05_01_2025-11-12.csv</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3292,21 +3292,21 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6890</v>
+        <v>7940</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>100</v>
       </c>
       <c r="G78" t="n">
-        <v>203000</v>
+        <v>101000</v>
       </c>
       <c r="H78" t="n">
-        <v>2030</v>
+        <v>1010</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -3315,49 +3315,49 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S100WWOW.zip</t>
+          <t>S100Z0YS.zip</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
+          <t>jplvh010000-lvh-001_E27325-000_2025-10-30_02_2026-09-10.csv</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
+          <t>株式会社ストラテジックキャピタル</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2432</v>
+        <v>1882</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>100</v>
+        <v>2528200</v>
       </c>
       <c r="G79" t="n">
-        <v>226000</v>
+        <v>2984068000</v>
       </c>
       <c r="H79" t="n">
-        <v>2260</v>
+        <v>1180.31326635551</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S100WSIC.zip</t>
+          <t>S100WWWV.zip</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-22_01_2025-10-29.csv</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3366,21 +3366,21 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6875</v>
+        <v>6890</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>100</v>
       </c>
       <c r="G80" t="n">
-        <v>487000</v>
+        <v>203000</v>
       </c>
       <c r="H80" t="n">
-        <v>4870</v>
+        <v>2030</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -3389,12 +3389,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S100WQFH.zip</t>
+          <t>S100WWOW.zip</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-10-20_01_2025-10-27.csv</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3403,21 +3403,21 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4917</v>
+        <v>2432</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>100</v>
       </c>
       <c r="G81" t="n">
-        <v>204000</v>
+        <v>226000</v>
       </c>
       <c r="H81" t="n">
-        <v>2040</v>
+        <v>2260</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3426,12 +3426,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S100WQ4O.zip</t>
+          <t>S100WSIC.zip</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-24_01_2025-10-01.csv</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3440,294 +3440,294 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>8233</v>
+        <v>6875</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>261400</v>
+        <v>100</v>
       </c>
       <c r="G82" t="n">
-        <v>287906000</v>
+        <v>487000</v>
       </c>
       <c r="H82" t="n">
-        <v>1101.400153022188</v>
+        <v>4870</v>
       </c>
       <c r="I82" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S100Z0TS.zip</t>
+          <t>S100WQFH.zip</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E27325-000_2025-09-09_02_2026-09-09.csv</t>
+          <t>jplvh010000-lvh-001_E35393-000_2025-09-16_01_2025-09-24.csv</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社ストラテジックキャピタル</t>
+          <t>株式会社シティインデックスイレブンス代表取締役　福島啓修</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1882</v>
+        <v>4917</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4275700</v>
+        <v>100</v>
       </c>
       <c r="G83" t="n">
-        <v>5047062000</v>
+        <v>204000</v>
       </c>
       <c r="H83" t="n">
-        <v>1180.406015389293</v>
+        <v>2040</v>
       </c>
       <c r="I83" t="n">
-        <v>8.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S100WO9C.zip</t>
+          <t>S100WQ4O.zip</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jplvh010000-lvh-001_E31883-000_2025-09-09_01_2025-09-16.csv</t>
+          <t>jplvh010000-lvh-002_E35393-000_2025-09-12_01_2025-09-22.csv</t>
         </is>